--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45385</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>44237</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44245</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44785</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44489</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>44439</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44454</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>44476</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44979</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44558</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44958</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>43591</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>43643</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>43686</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44057</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>44876</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>45324</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>45343</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>43613</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>43640</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>44489</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>44575</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>44785</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>44827</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>44853</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>45118</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>45254</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>43674</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>43719</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>43796</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>44302</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>44369</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>44785</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>44802</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44896</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44951</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>45105</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>45105</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>45125</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>43605</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>43614</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>43680</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>43717</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>43731</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>43734</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>43854</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>43927</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43928</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>43999</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44053</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44069</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>44103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>44152</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44246</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>44260</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44279</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44378</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>44466</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>44482</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44487</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44489</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44517</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>44575</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>44726</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>44830</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>44915</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>44928</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>44931</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>44949</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>44991</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>45007</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>45042</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45063</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>45069</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45117</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>45119</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>45167</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>45243</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>45275</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>45324</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>45362</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>43556</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>43558</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>43558</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>43559</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>43566</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>43567</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>43570</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>43578</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>43581</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>43581</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>43584</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>43585</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>43587</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>43591</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>43591</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>43591</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>43592</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>43600</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>43605</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>43606</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>43612</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>43612</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>43613</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>43613</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>43613</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>43613</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>43620</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>43625</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>43629</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>43634</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>43634</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>43640</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>43640</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>43640</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>43640</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>43643</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>43648</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>43656</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>43662</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>43668</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>43668</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>43668</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>43668</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>43675</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>43678</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>43679</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>43680</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>43680</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>43680</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>43680</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>43681</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>43682</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>43683</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>43683</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>43683</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>43684</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>43689</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>43689</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>43691</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>43691</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>43691</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>43691</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>43691</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>43692</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>43693</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>43696</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>43698</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>43698</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>43699</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>43699</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>43702</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>43703</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>43704</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>43704</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>43705</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>43705</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>43705</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>43706</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>43707</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>43710</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>43711</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>43712</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>43712</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>43712</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>43713</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>43714</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>43717</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>43717</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>43717</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>43718</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>43718</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>43718</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>43718</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>43719</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>43719</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>43720</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>43721</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>43721</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>43724</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>43726</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>43727</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>43727</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>43727</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>43728</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>43728</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>43732</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>43733</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>43746</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>43749</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>43755</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>43756</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>43756</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>43761</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>43763</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>43763</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>43763</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>43766</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>43769</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>43774</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>43776</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>43776</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>43777</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>43777</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>43777</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>43777</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>43780</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>43780</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>43782</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>43784</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>43784</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>43784</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>43784</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>43787</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>43791</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>43796</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>43796</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>43803</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>43803</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>43803</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>43815</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>43815</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>43815</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>43815</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>43817</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>43829</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>43832</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>43832</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>43832</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>43832</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>43832</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>43832</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>43832</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>43832</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>43840</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>43844</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         <v>43846</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>43846</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>43859</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>43865</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>43865</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>43867</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>43867</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>43867</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>43871</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>43871</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>43872</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>43873</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>43873</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>43873</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>43875</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>43875</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>43880</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43881</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>43886</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>43887</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>43887</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>43887</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>43894</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>43894</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>43899</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18949,7 +18949,7 @@
         <v>43900</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>43907</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>43907</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>43909</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>43914</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>43915</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19291,7 +19291,7 @@
         <v>43916</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>43916</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>43917</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>43929</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>43936</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>43941</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>43949</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>43950</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>43956</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>43963</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>43977</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>43983</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>43984</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>44007</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>44020</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>44032</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>44041</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>44041</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>44047</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>44047</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>44047</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>44048</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>44053</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>44053</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20716,7 +20716,7 @@
         <v>44055</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>44055</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>44055</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>44055</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44060</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>44060</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>44061</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>44061</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44061</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>44062</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>44062</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>44074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>44074</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>44074</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>44075</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>44075</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>44077</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>44082</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>44082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>44084</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>44089</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>44089</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44089</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>44089</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>44090</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>44095</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>44095</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44095</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44098</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44104</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44104</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>44105</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44105</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44109</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44110</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44110</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44111</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44112</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44112</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44119</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44120</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44126</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44130</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44131</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>44136</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>44138</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>44139</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>44140</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44141</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44144</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44145</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>44145</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44147</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44151</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>44151</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>44151</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>44151</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>44151</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44151</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>44154</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44159</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44160</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44178</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>44182</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>44182</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>44186</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>44187</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>44188</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>44192</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>44193</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44193</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>44201</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>44209</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>44210</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>44210</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>44214</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>44214</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>44214</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>44215</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44217</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44218</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44220</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>44229</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>44230</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>44230</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>44230</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>44230</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>44230</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>44230</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>44236</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>44236</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>44236</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>44236</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>44238</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>44241</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>44243</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>44243</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>44244</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>44264</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>44264</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>44267</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>44271</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>44271</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>44271</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44271</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44273</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>44273</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>44277</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>44279</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>44280</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>44285</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44287</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44301</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44302</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44302</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>44312</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44312</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>44320</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         <v>44322</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>44326</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>44326</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>44327</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>44333</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>44336</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>44341</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>44341</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44342</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>44345</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>44348</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>44351</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>44351</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>44356</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>44356</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>44357</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>44357</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>44363</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>44364</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44369</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44371</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44375</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44378</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44379</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44382</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44384</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>44385</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>44385</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44385</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44386</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44386</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>44405</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44407</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>44407</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44413</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44417</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44418</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>44419</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44421</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44432</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>44433</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>44434</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>44435</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>44437</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>44438</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>44438</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>44446</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>44447</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>44448</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>44448</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>44448</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>44454</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>44454</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>44455</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>44455</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>44456</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>44457</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>44460</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44461</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>44461</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>44462</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>44467</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>44474</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>44475</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>44475</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>44476</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>44477</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44477</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>44477</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>44480</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>44482</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>44482</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>44482</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>44482</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>44482</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>44484</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>44489</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>44489</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>44496</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44497</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>44497</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>44497</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>44497</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>44498</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>44498</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>44502</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>44502</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>44502</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>44505</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>44511</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>44517</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>44522</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>44522</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>44525</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>44529</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>44531</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>44543</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
         <v>44544</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>44544</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>44552</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>44564</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>44564</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>44566</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>44574</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>44581</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>44581</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>44581</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44586</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>44587</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44588</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44595</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>44602</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>44615</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>44617</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>44617</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>44618</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34468,7 +34468,7 @@
         <v>44620</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34525,7 +34525,7 @@
         <v>44620</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34582,7 +34582,7 @@
         <v>44623</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>44623</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34696,7 +34696,7 @@
         <v>44625</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>44629</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>44629</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>44636</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>44643</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44645</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>44655</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>44656</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44659</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44679</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>44679</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>44683</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>44684</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44686</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>44690</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>44712</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>44712</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35665,7 +35665,7 @@
         <v>44722</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>44732</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>44732</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>44733</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>44740</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>44740</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36007,7 +36007,7 @@
         <v>44782</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>44782</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>44784</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>44784</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44790</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44796</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44796</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44804</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44810</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>44810</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>44810</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         <v>44816</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>44818</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>44819</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>44820</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44823</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44823</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44823</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44823</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>44823</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44823</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44824</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44830</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44831</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44841</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44845</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>44846</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37757,7 +37757,7 @@
         <v>44846</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37814,7 +37814,7 @@
         <v>44846</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>44847</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>44848</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>44851</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38042,7 +38042,7 @@
         <v>44852</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>44855</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>44855</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>44855</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>44858</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>44858</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         <v>44858</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>44858</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>44858</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>44858</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>44858</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38731,7 +38731,7 @@
         <v>44861</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38788,7 +38788,7 @@
         <v>44861</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38845,7 +38845,7 @@
         <v>44862</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38902,7 +38902,7 @@
         <v>44864</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38959,7 +38959,7 @@
         <v>44865</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>44865</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39073,7 +39073,7 @@
         <v>44872</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>44874</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39187,7 +39187,7 @@
         <v>44882</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39244,7 +39244,7 @@
         <v>44895</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39301,7 +39301,7 @@
         <v>44895</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>44895</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>44895</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44895</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>44901</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>44904</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>44909</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>44909</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>44914</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>44914</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>44914</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>44914</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>44914</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>44915</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40099,7 +40099,7 @@
         <v>44915</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>44915</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>44924</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44924</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>44924</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>44924</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>44930</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44931</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44939</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>44939</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44949</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>44949</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>44952</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44955</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44959</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40959,7 +40959,7 @@
         <v>44963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41016,7 +41016,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>44965</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>44965</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>44966</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41301,7 +41301,7 @@
         <v>44970</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41358,7 +41358,7 @@
         <v>44971</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>44971</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>44971</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>44973</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>44973</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>44978</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>44979</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>44979</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>44984</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>44984</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41948,7 +41948,7 @@
         <v>44984</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>44988</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42062,7 +42062,7 @@
         <v>44988</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42119,7 +42119,7 @@
         <v>44991</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42176,7 +42176,7 @@
         <v>44993</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44993</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>44993</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>44993</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>44993</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>44994</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>44994</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44994</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>45001</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>45001</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>45001</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>45001</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>45001</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>45001</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>45001</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>45006</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>45007</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>45007</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45019</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45027</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45028</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>45028</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>45028</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>45034</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43735,7 +43735,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>45036</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43849,7 +43849,7 @@
         <v>45042</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43906,7 +43906,7 @@
         <v>45042</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43963,7 +43963,7 @@
         <v>45044</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44020,7 +44020,7 @@
         <v>45044</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>45050</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>45058</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>45061</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>45063</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>45067</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45070</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>45070</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>45070</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>45070</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44610,7 +44610,7 @@
         <v>45071</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
         <v>45071</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44724,7 +44724,7 @@
         <v>45071</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44781,7 +44781,7 @@
         <v>45072</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>45072</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>45075</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45075</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>45075</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>45075</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45075</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>45076</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>45077</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>45082</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>45082</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>45083</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45470,7 +45470,7 @@
         <v>45086</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45584,7 +45584,7 @@
         <v>45089</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45090</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45698,7 +45698,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>45090</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>45090</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>45091</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>45091</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45092</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>45093</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45093</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>45096</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>45096</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45097</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46496,7 +46496,7 @@
         <v>45097</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>45097</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45097</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45099</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46952,7 +46952,7 @@
         <v>45103</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47009,7 +47009,7 @@
         <v>45103</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47066,7 +47066,7 @@
         <v>45104</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>45104</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>45104</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>45104</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45104</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>45104</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47418,7 +47418,7 @@
         <v>45104</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47475,7 +47475,7 @@
         <v>45107</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>45110</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45110</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45110</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45113</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45113</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45114</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>45114</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>45114</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47998,7 +47998,7 @@
         <v>45114</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>45114</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>45114</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48169,7 +48169,7 @@
         <v>45118</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48226,7 +48226,7 @@
         <v>45118</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48283,7 +48283,7 @@
         <v>45118</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48340,7 +48340,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48397,7 +48397,7 @@
         <v>45118</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48511,7 +48511,7 @@
         <v>45118</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48568,7 +48568,7 @@
         <v>45119</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>45119</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48682,7 +48682,7 @@
         <v>45119</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48739,7 +48739,7 @@
         <v>45125</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45125</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48853,7 +48853,7 @@
         <v>45125</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48910,7 +48910,7 @@
         <v>45125</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48967,7 +48967,7 @@
         <v>45126</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49024,7 +49024,7 @@
         <v>45126</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49081,7 +49081,7 @@
         <v>45131</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49138,7 +49138,7 @@
         <v>45134</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49195,7 +49195,7 @@
         <v>45141</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49252,7 +49252,7 @@
         <v>45145</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>45146</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45146</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>45148</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>45148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49537,7 +49537,7 @@
         <v>45148</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49594,7 +49594,7 @@
         <v>45148</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49651,7 +49651,7 @@
         <v>45149</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49708,7 +49708,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49822,7 +49822,7 @@
         <v>45153</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49879,7 +49879,7 @@
         <v>45153</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45153</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49993,7 +49993,7 @@
         <v>45153</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50050,7 +50050,7 @@
         <v>45153</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>45154</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>45159</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50335,7 +50335,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50392,7 +50392,7 @@
         <v>45161</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>45161</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50506,7 +50506,7 @@
         <v>45163</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>45163</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50640,7 +50640,7 @@
         <v>45165</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50697,7 +50697,7 @@
         <v>45166</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50754,7 +50754,7 @@
         <v>45167</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50811,7 +50811,7 @@
         <v>45167</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>45167</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50925,7 +50925,7 @@
         <v>45169</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
         <v>45169</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45169</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>45169</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51153,7 +51153,7 @@
         <v>45169</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51210,7 +51210,7 @@
         <v>45170</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51267,7 +51267,7 @@
         <v>45170</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51324,7 +51324,7 @@
         <v>45173</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51381,7 +51381,7 @@
         <v>45173</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51438,7 +51438,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51495,7 +51495,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51552,7 +51552,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51609,7 +51609,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45174</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51780,7 +51780,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51837,7 +51837,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>45180</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51951,7 +51951,7 @@
         <v>45180</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52008,7 +52008,7 @@
         <v>45180</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52065,7 +52065,7 @@
         <v>45180</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52122,7 +52122,7 @@
         <v>45181</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52179,7 +52179,7 @@
         <v>45182</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52236,7 +52236,7 @@
         <v>45182</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52293,7 +52293,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52350,7 +52350,7 @@
         <v>45183</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52407,7 +52407,7 @@
         <v>45188</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52464,7 +52464,7 @@
         <v>45189</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52521,7 +52521,7 @@
         <v>45189</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>45190</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52635,7 +52635,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52692,7 +52692,7 @@
         <v>45190</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45195</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52863,7 +52863,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52920,7 +52920,7 @@
         <v>45198</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52977,7 +52977,7 @@
         <v>45198</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53034,7 +53034,7 @@
         <v>45198</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45202</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45202</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45202</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>45202</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45205</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>45205</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45205</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45205</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45205</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>45208</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>45208</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45209</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45209</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53832,7 +53832,7 @@
         <v>45209</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53889,7 +53889,7 @@
         <v>45212</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>45212</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45212</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>45212</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54117,7 +54117,7 @@
         <v>45215</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54174,7 +54174,7 @@
         <v>45218</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54231,7 +54231,7 @@
         <v>45218</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>45218</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54345,7 +54345,7 @@
         <v>45219</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54402,7 +54402,7 @@
         <v>45219</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54459,7 +54459,7 @@
         <v>45219</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54516,7 +54516,7 @@
         <v>45219</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54573,7 +54573,7 @@
         <v>45222</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54630,7 +54630,7 @@
         <v>45223</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54687,7 +54687,7 @@
         <v>45223</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54744,7 +54744,7 @@
         <v>45226</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54801,7 +54801,7 @@
         <v>45229</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54858,7 +54858,7 @@
         <v>45229</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54915,7 +54915,7 @@
         <v>45229</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54972,7 +54972,7 @@
         <v>45229</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55029,7 +55029,7 @@
         <v>45229</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55086,7 +55086,7 @@
         <v>45229</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55143,7 +55143,7 @@
         <v>45230</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55200,7 +55200,7 @@
         <v>45230</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55257,7 +55257,7 @@
         <v>45232</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>45232</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55371,7 +55371,7 @@
         <v>45233</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55428,7 +55428,7 @@
         <v>45233</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55485,7 +55485,7 @@
         <v>45233</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55542,7 +55542,7 @@
         <v>45233</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55599,7 +55599,7 @@
         <v>45233</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55656,7 +55656,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55713,7 +55713,7 @@
         <v>45233</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55770,7 +55770,7 @@
         <v>45233</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55827,7 +55827,7 @@
         <v>45233</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55884,7 +55884,7 @@
         <v>45236</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55941,7 +55941,7 @@
         <v>45237</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55998,7 +55998,7 @@
         <v>45239</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>45243</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         <v>45243</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>45244</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56231,7 +56231,7 @@
         <v>45246</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         <v>45246</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56516,7 +56516,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56630,7 +56630,7 @@
         <v>45246</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56687,7 +56687,7 @@
         <v>45247</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45250</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>45250</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56858,7 +56858,7 @@
         <v>45252</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56915,7 +56915,7 @@
         <v>45252</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56972,7 +56972,7 @@
         <v>45252</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57029,7 +57029,7 @@
         <v>45253</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57086,7 +57086,7 @@
         <v>45254</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57143,7 +57143,7 @@
         <v>45254</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57200,7 +57200,7 @@
         <v>45254</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57257,7 +57257,7 @@
         <v>45254</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57314,7 +57314,7 @@
         <v>45260</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>45260</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57428,7 +57428,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57485,7 +57485,7 @@
         <v>45261</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57542,7 +57542,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>45266</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>45267</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45268</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45268</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>45268</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45271</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45271</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>45272</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58132,7 +58132,7 @@
         <v>45272</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>45272</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
         <v>45273</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58303,7 +58303,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58360,7 +58360,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58417,7 +58417,7 @@
         <v>45274</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45281</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45286</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45301</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>45302</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45306</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58759,7 +58759,7 @@
         <v>45306</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58821,7 +58821,7 @@
         <v>45307</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58878,7 +58878,7 @@
         <v>45307</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58935,7 +58935,7 @@
         <v>45307</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58992,7 +58992,7 @@
         <v>45308</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59049,7 +59049,7 @@
         <v>45308</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59106,7 +59106,7 @@
         <v>45313</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
         <v>45313</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59220,7 +59220,7 @@
         <v>45313</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59277,7 +59277,7 @@
         <v>45313</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59334,7 +59334,7 @@
         <v>45314</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59391,7 +59391,7 @@
         <v>45314</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59448,7 +59448,7 @@
         <v>45314</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59505,7 +59505,7 @@
         <v>45314</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59562,7 +59562,7 @@
         <v>45314</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59619,7 +59619,7 @@
         <v>45319</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59676,7 +59676,7 @@
         <v>45323</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59733,7 +59733,7 @@
         <v>45323</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59790,7 +59790,7 @@
         <v>45323</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59847,7 +59847,7 @@
         <v>45324</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59904,7 +59904,7 @@
         <v>45324</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59961,7 +59961,7 @@
         <v>45327</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60018,7 +60018,7 @@
         <v>45327</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60075,7 +60075,7 @@
         <v>45329</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60132,7 +60132,7 @@
         <v>45329</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60189,7 +60189,7 @@
         <v>45331</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60246,7 +60246,7 @@
         <v>45331</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60303,7 +60303,7 @@
         <v>45331</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60360,7 +60360,7 @@
         <v>45334</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60417,7 +60417,7 @@
         <v>45335</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60479,7 +60479,7 @@
         <v>45335</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60536,7 +60536,7 @@
         <v>45335</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60598,7 +60598,7 @@
         <v>45335</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60660,7 +60660,7 @@
         <v>45335</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60717,7 +60717,7 @@
         <v>45335</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60779,7 +60779,7 @@
         <v>45335</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60841,7 +60841,7 @@
         <v>45336</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60898,7 +60898,7 @@
         <v>45336</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60955,7 +60955,7 @@
         <v>45336</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61012,7 +61012,7 @@
         <v>45336</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61069,7 +61069,7 @@
         <v>45337</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61126,7 +61126,7 @@
         <v>45337</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61183,7 +61183,7 @@
         <v>45338</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61240,7 +61240,7 @@
         <v>45338</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61297,7 +61297,7 @@
         <v>45341</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61354,7 +61354,7 @@
         <v>45341</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61411,7 +61411,7 @@
         <v>45341</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61468,7 +61468,7 @@
         <v>45344</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61525,7 +61525,7 @@
         <v>45345</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61582,7 +61582,7 @@
         <v>45349</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61639,7 +61639,7 @@
         <v>45349</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61696,7 +61696,7 @@
         <v>45351</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61753,7 +61753,7 @@
         <v>45356</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61810,7 +61810,7 @@
         <v>45356</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61867,7 +61867,7 @@
         <v>45362</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61924,7 +61924,7 @@
         <v>45363</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61981,7 +61981,7 @@
         <v>45363</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -62038,7 +62038,7 @@
         <v>45363</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -62095,7 +62095,7 @@
         <v>45363</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62172,7 +62172,7 @@
         <v>45363</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62229,7 +62229,7 @@
         <v>45363</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62286,7 +62286,7 @@
         <v>45364</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62343,7 +62343,7 @@
         <v>45364</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62400,7 +62400,7 @@
         <v>45364</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62457,7 +62457,7 @@
         <v>45370</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62514,7 +62514,7 @@
         <v>45372</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62571,7 +62571,7 @@
         <v>45378</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62628,7 +62628,7 @@
         <v>45378</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62685,7 +62685,7 @@
         <v>45378</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62742,7 +62742,7 @@
         <v>45384</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62799,7 +62799,7 @@
         <v>45384</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62856,7 +62856,7 @@
         <v>45384</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62913,7 +62913,7 @@
         <v>45385</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62975,7 +62975,7 @@
         <v>45385</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -63032,7 +63032,7 @@
         <v>45387</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -63089,7 +63089,7 @@
         <v>45387</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -63146,7 +63146,7 @@
         <v>45387</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63203,7 +63203,7 @@
         <v>45387</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63260,7 +63260,7 @@
         <v>45387</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63317,7 +63317,7 @@
         <v>45391</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63374,7 +63374,7 @@
         <v>45398</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63431,7 +63431,7 @@
         <v>45400</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63488,7 +63488,7 @@
         <v>45400</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63545,7 +63545,7 @@
         <v>45400</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63602,7 +63602,7 @@
         <v>45401</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63659,7 +63659,7 @@
         <v>45401</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63716,7 +63716,7 @@
         <v>45402</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45404</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>45406</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63892,7 +63892,7 @@
         <v>45407</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45411</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -64006,7 +64006,7 @@
         <v>45411</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -64063,7 +64063,7 @@
         <v>45412</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -64120,7 +64120,7 @@
         <v>45412</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -64177,7 +64177,7 @@
         <v>45414</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64234,7 +64234,7 @@
         <v>45418</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>45420</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64348,7 +64348,7 @@
         <v>45429</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64405,7 +64405,7 @@
         <v>45429</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64462,7 +64462,7 @@
         <v>45433</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64519,7 +64519,7 @@
         <v>45439</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64576,7 +64576,7 @@
         <v>45441</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64633,7 +64633,7 @@
         <v>45441</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64690,7 +64690,7 @@
         <v>45442</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64740,14 +64740,14 @@
     <row r="1076" ht="15" customHeight="1">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>A 21964-2024</t>
+          <t>A 21962-2024</t>
         </is>
       </c>
       <c r="B1076" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64760,7 +64760,7 @@
         </is>
       </c>
       <c r="G1076" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="H1076" t="n">
         <v>0</v>
@@ -64797,14 +64797,14 @@
     <row r="1077" ht="15" customHeight="1">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>A 21962-2024</t>
+          <t>A 21964-2024</t>
         </is>
       </c>
       <c r="B1077" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64817,7 +64817,7 @@
         </is>
       </c>
       <c r="G1077" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="H1077" t="n">
         <v>0</v>
@@ -64861,7 +64861,7 @@
         <v>45446</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64918,7 +64918,7 @@
         <v>45453</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -64968,14 +64968,14 @@
     <row r="1080" ht="15" customHeight="1">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>A 23664-2024</t>
+          <t>A 23662-2024</t>
         </is>
       </c>
       <c r="B1080" s="1" t="n">
         <v>45454</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -64988,7 +64988,7 @@
         </is>
       </c>
       <c r="G1080" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="H1080" t="n">
         <v>0</v>
@@ -65025,14 +65025,14 @@
     <row r="1081" ht="15" customHeight="1">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>A 23662-2024</t>
+          <t>A 23673-2024</t>
         </is>
       </c>
       <c r="B1081" s="1" t="n">
         <v>45454</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -65044,8 +65044,13 @@
           <t>KALMAR</t>
         </is>
       </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1081" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="H1081" t="n">
         <v>0</v>
@@ -65082,14 +65087,14 @@
     <row r="1082" ht="15" customHeight="1">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>A 23673-2024</t>
+          <t>A 23664-2024</t>
         </is>
       </c>
       <c r="B1082" s="1" t="n">
         <v>45454</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -65101,13 +65106,8 @@
           <t>KALMAR</t>
         </is>
       </c>
-      <c r="F1082" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1082" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="H1082" t="n">
         <v>0</v>
@@ -65144,14 +65144,14 @@
     <row r="1083" ht="15" customHeight="1">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>A 24646-2024</t>
+          <t>A 24643-2024</t>
         </is>
       </c>
       <c r="B1083" s="1" t="n">
         <v>45460</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65164,7 +65164,7 @@
         </is>
       </c>
       <c r="G1083" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="H1083" t="n">
         <v>0</v>
@@ -65201,14 +65201,14 @@
     <row r="1084" ht="15" customHeight="1">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>A 24643-2024</t>
+          <t>A 24646-2024</t>
         </is>
       </c>
       <c r="B1084" s="1" t="n">
         <v>45460</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65221,7 +65221,7 @@
         </is>
       </c>
       <c r="G1084" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="H1084" t="n">
         <v>0</v>
@@ -65265,7 +65265,7 @@
         <v>45460</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -65322,7 +65322,7 @@
         <v>45462</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -65379,7 +65379,7 @@
         <v>45462</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -65436,7 +65436,7 @@
         <v>45463</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -65493,7 +65493,7 @@
         <v>45463</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -65550,7 +65550,7 @@
         <v>45470</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45472</v>
+        <v>45473</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45385</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>44237</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44245</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44785</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44489</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>44439</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44454</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>44476</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44979</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44558</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44958</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>43591</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>43643</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>43686</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44057</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>44876</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>45324</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>45343</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>43613</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>43640</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>44489</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>44575</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>44785</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>44827</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>44853</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>45118</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>45254</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>43674</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>43719</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>43796</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>44302</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>44369</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>44785</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>44802</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44896</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44951</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>45105</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>45105</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>45125</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>43605</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>43614</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>43680</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>43717</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>43731</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>43734</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>43854</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>43927</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43928</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>43999</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44053</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44069</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>44103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>44152</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44246</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>44260</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44279</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44378</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>44466</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>44482</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44487</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44489</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44517</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>44575</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>44726</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>44830</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>44915</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>44928</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>44931</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>44949</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>44991</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>45007</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>45042</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45063</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>45069</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45117</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>45119</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>45167</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>45243</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>45275</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>45324</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>45362</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>43556</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>43558</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>43558</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>43559</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>43566</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>43567</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>43570</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>43578</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>43581</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>43581</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>43584</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>43585</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>43587</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>43591</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>43591</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>43591</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>43592</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>43600</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>43605</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>43606</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>43612</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>43612</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>43613</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>43613</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>43613</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>43613</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>43620</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>43625</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>43629</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>43634</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>43634</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>43640</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>43640</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>43640</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>43640</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>43643</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>43648</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>43656</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>43662</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>43668</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>43668</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>43668</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>43668</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>43675</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>43678</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>43679</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>43680</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>43680</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>43680</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>43680</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>43681</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>43682</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>43683</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>43683</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>43683</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>43684</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>43689</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>43689</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>43691</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>43691</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>43691</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>43691</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>43691</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>43692</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>43693</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>43696</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>43698</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>43698</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>43699</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>43699</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>43702</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>43703</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>43704</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>43704</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>43705</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>43705</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>43705</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>43706</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>43707</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>43710</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>43711</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>43712</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>43712</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>43712</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>43713</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>43714</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>43717</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>43717</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>43717</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>43718</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>43718</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>43718</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>43718</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>43719</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>43719</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>43720</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>43721</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>43721</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>43724</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>43726</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>43727</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>43727</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>43727</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>43728</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>43728</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>43732</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>43733</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>43746</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>43749</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>43755</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>43756</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>43756</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>43761</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>43763</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>43763</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>43763</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>43766</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>43769</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>43774</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>43776</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>43776</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>43777</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>43777</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>43777</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>43777</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>43780</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>43780</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>43782</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>43784</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>43784</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>43784</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>43784</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>43787</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>43791</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>43796</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>43796</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>43803</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>43803</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>43803</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>43815</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>43815</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>43815</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>43815</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>43817</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>43829</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>43832</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>43832</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>43832</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>43832</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>43832</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>43832</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>43832</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>43832</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>43840</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>43844</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         <v>43846</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>43846</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>43859</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>43865</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>43865</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>43867</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>43867</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>43867</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>43871</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>43871</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>43872</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>43873</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>43873</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>43873</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>43875</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>43875</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>43880</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43881</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>43886</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>43887</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>43887</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>43887</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>43894</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>43894</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>43899</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18949,7 +18949,7 @@
         <v>43900</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>43907</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>43907</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>43909</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>43914</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>43915</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19291,7 +19291,7 @@
         <v>43916</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>43916</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>43917</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>43929</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>43936</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>43941</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>43949</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>43950</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>43956</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>43963</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>43977</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>43983</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>43984</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>44007</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>44020</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>44032</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>44041</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>44041</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>44047</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>44047</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>44047</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>44048</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>44053</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>44053</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20716,7 +20716,7 @@
         <v>44055</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>44055</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>44055</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>44055</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44060</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>44060</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>44061</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>44061</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44061</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>44062</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>44062</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>44074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>44074</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>44074</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>44075</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>44075</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>44077</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>44082</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>44082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>44084</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>44089</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>44089</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44089</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>44089</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>44090</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>44095</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>44095</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44095</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44098</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44104</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44104</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>44105</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44105</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44109</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44110</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44110</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44111</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44112</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44112</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44119</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44120</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44126</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44130</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44131</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>44136</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>44138</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>44139</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>44140</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44141</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44144</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44145</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>44145</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44147</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44151</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>44151</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>44151</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>44151</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>44151</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44151</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>44154</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44159</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44160</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44178</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>44182</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>44182</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>44186</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>44187</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>44188</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>44192</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>44193</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44193</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>44201</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>44209</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>44210</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>44210</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>44214</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>44214</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>44214</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>44215</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44217</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44218</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44220</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>44229</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>44230</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>44230</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>44230</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>44230</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>44230</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>44230</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>44236</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>44236</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>44236</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>44236</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>44238</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>44241</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>44243</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>44243</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>44244</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>44264</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>44264</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>44267</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>44271</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>44271</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>44271</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44271</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44273</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>44273</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>44277</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>44279</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>44280</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>44285</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44287</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44301</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44302</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44302</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>44312</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44312</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>44320</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         <v>44322</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>44326</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>44326</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>44327</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>44333</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>44336</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>44341</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>44341</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44342</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>44345</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>44348</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>44351</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>44351</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>44356</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>44356</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>44357</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>44357</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>44363</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>44364</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44369</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44371</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44375</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44378</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44379</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44382</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44384</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>44385</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>44385</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44385</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44386</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44386</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>44405</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44407</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>44407</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44413</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44417</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44418</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>44419</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44421</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44432</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>44433</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>44434</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>44435</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>44437</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>44438</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>44438</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>44446</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>44447</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>44448</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>44448</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>44448</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>44454</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>44454</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>44455</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>44455</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>44456</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>44457</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>44460</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44461</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>44461</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>44462</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>44467</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>44474</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>44475</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>44475</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>44476</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>44477</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44477</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>44477</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>44480</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>44482</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>44482</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>44482</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>44482</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>44482</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>44484</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>44489</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>44489</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>44496</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44497</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>44497</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>44497</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>44497</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>44498</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>44498</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>44502</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>44502</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>44502</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>44505</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>44511</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>44517</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>44522</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>44522</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>44525</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>44529</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>44531</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>44543</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
         <v>44544</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>44544</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>44552</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>44564</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>44564</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>44566</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>44574</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>44581</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>44581</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>44581</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44586</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>44587</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44588</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44595</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>44602</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>44615</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>44617</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>44617</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>44618</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34468,7 +34468,7 @@
         <v>44620</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34525,7 +34525,7 @@
         <v>44620</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34582,7 +34582,7 @@
         <v>44623</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>44623</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34696,7 +34696,7 @@
         <v>44625</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>44629</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>44629</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>44636</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>44643</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44645</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>44655</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>44656</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44659</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44679</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>44679</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>44683</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>44684</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44686</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>44690</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>44712</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>44712</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35665,7 +35665,7 @@
         <v>44722</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>44732</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>44732</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>44733</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>44740</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>44740</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36007,7 +36007,7 @@
         <v>44782</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>44782</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>44784</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>44784</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44790</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44796</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44796</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44804</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44810</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>44810</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>44810</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         <v>44816</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>44818</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>44819</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>44820</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44823</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44823</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44823</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44823</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>44823</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44823</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44824</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44830</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44831</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44841</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44845</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>44846</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37757,7 +37757,7 @@
         <v>44846</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37814,7 +37814,7 @@
         <v>44846</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>44847</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>44848</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>44851</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38042,7 +38042,7 @@
         <v>44852</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>44855</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>44855</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>44855</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>44858</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>44858</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         <v>44858</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>44858</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>44858</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>44858</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>44858</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38731,7 +38731,7 @@
         <v>44861</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38788,7 +38788,7 @@
         <v>44861</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38845,7 +38845,7 @@
         <v>44862</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38902,7 +38902,7 @@
         <v>44864</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38959,7 +38959,7 @@
         <v>44865</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>44865</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39073,7 +39073,7 @@
         <v>44872</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>44874</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39187,7 +39187,7 @@
         <v>44882</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39244,7 +39244,7 @@
         <v>44895</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39301,7 +39301,7 @@
         <v>44895</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>44895</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>44895</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44895</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>44901</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>44904</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>44909</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>44909</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>44914</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>44914</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>44914</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>44914</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>44914</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>44915</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40099,7 +40099,7 @@
         <v>44915</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>44915</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>44924</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44924</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>44924</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>44924</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>44930</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44931</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44939</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>44939</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44949</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>44949</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>44952</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44955</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44959</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40959,7 +40959,7 @@
         <v>44963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41016,7 +41016,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>44965</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>44965</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>44966</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41301,7 +41301,7 @@
         <v>44970</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41358,7 +41358,7 @@
         <v>44971</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>44971</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>44971</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>44973</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>44973</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>44978</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>44979</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>44979</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>44984</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>44984</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41948,7 +41948,7 @@
         <v>44984</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>44988</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42062,7 +42062,7 @@
         <v>44988</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42119,7 +42119,7 @@
         <v>44991</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42176,7 +42176,7 @@
         <v>44993</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44993</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>44993</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>44993</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>44993</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>44994</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>44994</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44994</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>45001</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>45001</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>45001</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>45001</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>45001</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>45001</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>45001</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>45006</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>45007</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>45007</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45019</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45027</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45028</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>45028</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>45028</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>45034</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43735,7 +43735,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>45036</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43849,7 +43849,7 @@
         <v>45042</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43906,7 +43906,7 @@
         <v>45042</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43963,7 +43963,7 @@
         <v>45044</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44020,7 +44020,7 @@
         <v>45044</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>45050</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>45058</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>45061</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>45063</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>45067</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45070</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>45070</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>45070</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>45070</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44610,7 +44610,7 @@
         <v>45071</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
         <v>45071</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44724,7 +44724,7 @@
         <v>45071</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44781,7 +44781,7 @@
         <v>45072</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>45072</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>45075</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45075</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>45075</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>45075</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45075</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>45076</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>45077</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>45082</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>45082</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>45083</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45470,7 +45470,7 @@
         <v>45086</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45584,7 +45584,7 @@
         <v>45089</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45090</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45698,7 +45698,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>45090</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>45090</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>45091</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>45091</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45092</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>45093</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45093</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>45096</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>45096</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45097</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46496,7 +46496,7 @@
         <v>45097</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>45097</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45097</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45099</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46952,7 +46952,7 @@
         <v>45103</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47009,7 +47009,7 @@
         <v>45103</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47066,7 +47066,7 @@
         <v>45104</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>45104</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>45104</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>45104</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45104</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>45104</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47418,7 +47418,7 @@
         <v>45104</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47475,7 +47475,7 @@
         <v>45107</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>45110</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45110</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45110</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45113</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45113</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45114</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>45114</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>45114</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47998,7 +47998,7 @@
         <v>45114</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>45114</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>45114</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48169,7 +48169,7 @@
         <v>45118</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48226,7 +48226,7 @@
         <v>45118</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48283,7 +48283,7 @@
         <v>45118</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48340,7 +48340,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48397,7 +48397,7 @@
         <v>45118</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48511,7 +48511,7 @@
         <v>45118</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48568,7 +48568,7 @@
         <v>45119</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>45119</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48682,7 +48682,7 @@
         <v>45119</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48739,7 +48739,7 @@
         <v>45125</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45125</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48853,7 +48853,7 @@
         <v>45125</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48910,7 +48910,7 @@
         <v>45125</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48967,7 +48967,7 @@
         <v>45126</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49024,7 +49024,7 @@
         <v>45126</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49081,7 +49081,7 @@
         <v>45131</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49138,7 +49138,7 @@
         <v>45134</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49195,7 +49195,7 @@
         <v>45141</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49252,7 +49252,7 @@
         <v>45145</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>45146</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45146</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>45148</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>45148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49537,7 +49537,7 @@
         <v>45148</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49594,7 +49594,7 @@
         <v>45148</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49651,7 +49651,7 @@
         <v>45149</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49708,7 +49708,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49822,7 +49822,7 @@
         <v>45153</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49879,7 +49879,7 @@
         <v>45153</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45153</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49993,7 +49993,7 @@
         <v>45153</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50050,7 +50050,7 @@
         <v>45153</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>45154</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>45159</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50335,7 +50335,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50392,7 +50392,7 @@
         <v>45161</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>45161</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50506,7 +50506,7 @@
         <v>45163</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>45163</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50640,7 +50640,7 @@
         <v>45165</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50697,7 +50697,7 @@
         <v>45166</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50754,7 +50754,7 @@
         <v>45167</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50811,7 +50811,7 @@
         <v>45167</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>45167</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50925,7 +50925,7 @@
         <v>45169</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
         <v>45169</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45169</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>45169</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51153,7 +51153,7 @@
         <v>45169</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51210,7 +51210,7 @@
         <v>45170</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51267,7 +51267,7 @@
         <v>45170</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51324,7 +51324,7 @@
         <v>45173</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51381,7 +51381,7 @@
         <v>45173</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51438,7 +51438,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51495,7 +51495,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51552,7 +51552,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51609,7 +51609,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45174</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51780,7 +51780,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51837,7 +51837,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>45180</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51951,7 +51951,7 @@
         <v>45180</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52008,7 +52008,7 @@
         <v>45180</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52065,7 +52065,7 @@
         <v>45180</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52122,7 +52122,7 @@
         <v>45181</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52179,7 +52179,7 @@
         <v>45182</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52236,7 +52236,7 @@
         <v>45182</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52293,7 +52293,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52350,7 +52350,7 @@
         <v>45183</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52407,7 +52407,7 @@
         <v>45188</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52464,7 +52464,7 @@
         <v>45189</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52521,7 +52521,7 @@
         <v>45189</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>45190</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52635,7 +52635,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52692,7 +52692,7 @@
         <v>45190</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45195</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52863,7 +52863,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52920,7 +52920,7 @@
         <v>45198</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52977,7 +52977,7 @@
         <v>45198</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53034,7 +53034,7 @@
         <v>45198</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45202</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45202</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45202</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>45202</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45205</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>45205</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45205</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45205</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45205</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>45208</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>45208</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45209</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45209</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53832,7 +53832,7 @@
         <v>45209</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53889,7 +53889,7 @@
         <v>45212</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>45212</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45212</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>45212</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54117,7 +54117,7 @@
         <v>45215</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54174,7 +54174,7 @@
         <v>45218</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54231,7 +54231,7 @@
         <v>45218</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>45218</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54345,7 +54345,7 @@
         <v>45219</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54402,7 +54402,7 @@
         <v>45219</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54459,7 +54459,7 @@
         <v>45219</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54516,7 +54516,7 @@
         <v>45219</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54573,7 +54573,7 @@
         <v>45222</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54630,7 +54630,7 @@
         <v>45223</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54687,7 +54687,7 @@
         <v>45223</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54744,7 +54744,7 @@
         <v>45226</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54801,7 +54801,7 @@
         <v>45229</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54858,7 +54858,7 @@
         <v>45229</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54915,7 +54915,7 @@
         <v>45229</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54972,7 +54972,7 @@
         <v>45229</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55029,7 +55029,7 @@
         <v>45229</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55086,7 +55086,7 @@
         <v>45229</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55143,7 +55143,7 @@
         <v>45230</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55200,7 +55200,7 @@
         <v>45230</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55257,7 +55257,7 @@
         <v>45232</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>45232</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55371,7 +55371,7 @@
         <v>45233</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55428,7 +55428,7 @@
         <v>45233</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55485,7 +55485,7 @@
         <v>45233</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55542,7 +55542,7 @@
         <v>45233</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55599,7 +55599,7 @@
         <v>45233</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55656,7 +55656,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55713,7 +55713,7 @@
         <v>45233</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55770,7 +55770,7 @@
         <v>45233</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55827,7 +55827,7 @@
         <v>45233</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55884,7 +55884,7 @@
         <v>45236</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55941,7 +55941,7 @@
         <v>45237</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55998,7 +55998,7 @@
         <v>45239</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>45243</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         <v>45243</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>45244</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56231,7 +56231,7 @@
         <v>45246</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         <v>45246</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56516,7 +56516,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56630,7 +56630,7 @@
         <v>45246</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56687,7 +56687,7 @@
         <v>45247</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45250</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>45250</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56858,7 +56858,7 @@
         <v>45252</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56915,7 +56915,7 @@
         <v>45252</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56972,7 +56972,7 @@
         <v>45252</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57029,7 +57029,7 @@
         <v>45253</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57086,7 +57086,7 @@
         <v>45254</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57143,7 +57143,7 @@
         <v>45254</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57200,7 +57200,7 @@
         <v>45254</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57257,7 +57257,7 @@
         <v>45254</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57314,7 +57314,7 @@
         <v>45260</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>45260</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57428,7 +57428,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57485,7 +57485,7 @@
         <v>45261</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57542,7 +57542,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>45266</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>45267</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45268</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45268</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>45268</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45271</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45271</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>45272</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58132,7 +58132,7 @@
         <v>45272</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>45272</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
         <v>45273</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58303,7 +58303,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58360,7 +58360,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58417,7 +58417,7 @@
         <v>45274</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45281</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45286</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45301</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>45302</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45306</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58759,7 +58759,7 @@
         <v>45306</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58821,7 +58821,7 @@
         <v>45307</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58878,7 +58878,7 @@
         <v>45307</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58935,7 +58935,7 @@
         <v>45307</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58992,7 +58992,7 @@
         <v>45308</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59049,7 +59049,7 @@
         <v>45308</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59106,7 +59106,7 @@
         <v>45313</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
         <v>45313</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59220,7 +59220,7 @@
         <v>45313</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59277,7 +59277,7 @@
         <v>45313</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59334,7 +59334,7 @@
         <v>45314</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59391,7 +59391,7 @@
         <v>45314</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59448,7 +59448,7 @@
         <v>45314</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59505,7 +59505,7 @@
         <v>45314</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59562,7 +59562,7 @@
         <v>45314</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59619,7 +59619,7 @@
         <v>45319</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59676,7 +59676,7 @@
         <v>45323</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59733,7 +59733,7 @@
         <v>45323</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59790,7 +59790,7 @@
         <v>45323</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59847,7 +59847,7 @@
         <v>45324</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59904,7 +59904,7 @@
         <v>45324</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59961,7 +59961,7 @@
         <v>45327</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60018,7 +60018,7 @@
         <v>45327</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60075,7 +60075,7 @@
         <v>45329</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60132,7 +60132,7 @@
         <v>45329</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60189,7 +60189,7 @@
         <v>45331</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60246,7 +60246,7 @@
         <v>45331</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60303,7 +60303,7 @@
         <v>45331</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60360,7 +60360,7 @@
         <v>45334</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60417,7 +60417,7 @@
         <v>45335</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60479,7 +60479,7 @@
         <v>45335</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60536,7 +60536,7 @@
         <v>45335</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60598,7 +60598,7 @@
         <v>45335</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60660,7 +60660,7 @@
         <v>45335</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60717,7 +60717,7 @@
         <v>45335</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60779,7 +60779,7 @@
         <v>45335</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60841,7 +60841,7 @@
         <v>45336</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60898,7 +60898,7 @@
         <v>45336</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60955,7 +60955,7 @@
         <v>45336</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61012,7 +61012,7 @@
         <v>45336</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61069,7 +61069,7 @@
         <v>45337</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61126,7 +61126,7 @@
         <v>45337</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61183,7 +61183,7 @@
         <v>45338</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61240,7 +61240,7 @@
         <v>45338</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61297,7 +61297,7 @@
         <v>45341</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61354,7 +61354,7 @@
         <v>45341</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61411,7 +61411,7 @@
         <v>45341</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61468,7 +61468,7 @@
         <v>45344</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61525,7 +61525,7 @@
         <v>45345</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61582,7 +61582,7 @@
         <v>45349</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61639,7 +61639,7 @@
         <v>45349</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61696,7 +61696,7 @@
         <v>45351</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61753,7 +61753,7 @@
         <v>45356</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61810,7 +61810,7 @@
         <v>45356</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61867,7 +61867,7 @@
         <v>45362</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61924,7 +61924,7 @@
         <v>45363</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61981,7 +61981,7 @@
         <v>45363</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -62038,7 +62038,7 @@
         <v>45363</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -62095,7 +62095,7 @@
         <v>45363</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62172,7 +62172,7 @@
         <v>45363</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62229,7 +62229,7 @@
         <v>45363</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62286,7 +62286,7 @@
         <v>45364</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62343,7 +62343,7 @@
         <v>45364</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62400,7 +62400,7 @@
         <v>45364</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62457,7 +62457,7 @@
         <v>45370</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62514,7 +62514,7 @@
         <v>45372</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62571,7 +62571,7 @@
         <v>45378</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62628,7 +62628,7 @@
         <v>45378</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62685,7 +62685,7 @@
         <v>45378</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62742,7 +62742,7 @@
         <v>45384</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62799,7 +62799,7 @@
         <v>45384</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62856,7 +62856,7 @@
         <v>45384</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62913,7 +62913,7 @@
         <v>45385</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62975,7 +62975,7 @@
         <v>45385</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -63032,7 +63032,7 @@
         <v>45387</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -63089,7 +63089,7 @@
         <v>45387</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -63146,7 +63146,7 @@
         <v>45387</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63203,7 +63203,7 @@
         <v>45387</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63260,7 +63260,7 @@
         <v>45387</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63317,7 +63317,7 @@
         <v>45391</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63374,7 +63374,7 @@
         <v>45398</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63431,7 +63431,7 @@
         <v>45400</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63488,7 +63488,7 @@
         <v>45400</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63545,7 +63545,7 @@
         <v>45400</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63602,7 +63602,7 @@
         <v>45401</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63659,7 +63659,7 @@
         <v>45401</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63716,7 +63716,7 @@
         <v>45402</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45404</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>45406</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63892,7 +63892,7 @@
         <v>45407</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45411</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -64006,7 +64006,7 @@
         <v>45411</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -64063,7 +64063,7 @@
         <v>45412</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -64120,7 +64120,7 @@
         <v>45412</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -64177,7 +64177,7 @@
         <v>45414</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64234,7 +64234,7 @@
         <v>45418</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>45420</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64348,7 +64348,7 @@
         <v>45429</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64405,7 +64405,7 @@
         <v>45429</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64462,7 +64462,7 @@
         <v>45433</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64519,7 +64519,7 @@
         <v>45439</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64576,7 +64576,7 @@
         <v>45441</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64633,7 +64633,7 @@
         <v>45441</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64690,7 +64690,7 @@
         <v>45442</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64747,7 +64747,7 @@
         <v>45443</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64804,7 +64804,7 @@
         <v>45443</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64861,7 +64861,7 @@
         <v>45446</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64918,7 +64918,7 @@
         <v>45453</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -64968,14 +64968,14 @@
     <row r="1080" ht="15" customHeight="1">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>A 23662-2024</t>
+          <t>A 23664-2024</t>
         </is>
       </c>
       <c r="B1080" s="1" t="n">
         <v>45454</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -64988,7 +64988,7 @@
         </is>
       </c>
       <c r="G1080" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="H1080" t="n">
         <v>0</v>
@@ -65025,14 +65025,14 @@
     <row r="1081" ht="15" customHeight="1">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>A 23673-2024</t>
+          <t>A 23662-2024</t>
         </is>
       </c>
       <c r="B1081" s="1" t="n">
         <v>45454</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -65044,13 +65044,8 @@
           <t>KALMAR</t>
         </is>
       </c>
-      <c r="F1081" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1081" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="H1081" t="n">
         <v>0</v>
@@ -65087,14 +65082,14 @@
     <row r="1082" ht="15" customHeight="1">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>A 23664-2024</t>
+          <t>A 23673-2024</t>
         </is>
       </c>
       <c r="B1082" s="1" t="n">
         <v>45454</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -65106,8 +65101,13 @@
           <t>KALMAR</t>
         </is>
       </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1082" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="H1082" t="n">
         <v>0</v>
@@ -65144,14 +65144,14 @@
     <row r="1083" ht="15" customHeight="1">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>A 24643-2024</t>
+          <t>A 24649-2024</t>
         </is>
       </c>
       <c r="B1083" s="1" t="n">
         <v>45460</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65164,7 +65164,7 @@
         </is>
       </c>
       <c r="G1083" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="H1083" t="n">
         <v>0</v>
@@ -65201,14 +65201,14 @@
     <row r="1084" ht="15" customHeight="1">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>A 24646-2024</t>
+          <t>A 24643-2024</t>
         </is>
       </c>
       <c r="B1084" s="1" t="n">
         <v>45460</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65221,7 +65221,7 @@
         </is>
       </c>
       <c r="G1084" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="H1084" t="n">
         <v>0</v>
@@ -65258,14 +65258,14 @@
     <row r="1085" ht="15" customHeight="1">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>A 24649-2024</t>
+          <t>A 24646-2024</t>
         </is>
       </c>
       <c r="B1085" s="1" t="n">
         <v>45460</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -65278,7 +65278,7 @@
         </is>
       </c>
       <c r="G1085" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="H1085" t="n">
         <v>0</v>
@@ -65322,7 +65322,7 @@
         <v>45462</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -65379,7 +65379,7 @@
         <v>45462</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -65429,14 +65429,14 @@
     <row r="1088" ht="15" customHeight="1">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>A 25594-2024</t>
+          <t>A 25597-2024</t>
         </is>
       </c>
       <c r="B1088" s="1" t="n">
         <v>45463</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -65449,7 +65449,7 @@
         </is>
       </c>
       <c r="G1088" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="H1088" t="n">
         <v>0</v>
@@ -65486,14 +65486,14 @@
     <row r="1089" ht="15" customHeight="1">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>A 25597-2024</t>
+          <t>A 25594-2024</t>
         </is>
       </c>
       <c r="B1089" s="1" t="n">
         <v>45463</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -65506,7 +65506,7 @@
         </is>
       </c>
       <c r="G1089" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="H1089" t="n">
         <v>0</v>
@@ -65550,7 +65550,7 @@
         <v>45470</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45473</v>
+        <v>45474</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45385</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>44237</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44245</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44785</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44489</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>44439</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44454</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>44476</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44979</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44558</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44958</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>43591</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>43643</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>43686</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44057</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>44876</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>45324</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>45343</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>43613</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>43640</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>44489</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>44575</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>44785</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>44827</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>44853</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>45118</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>45254</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>43674</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>43719</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>43796</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>44302</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>44369</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>44785</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>44802</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44896</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>44951</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>45105</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>45105</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>45125</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>43605</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>43614</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>43680</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>43717</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>43731</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>43734</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>43854</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>43927</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>43928</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>43999</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44053</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44069</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>44103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>44152</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44246</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>44260</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44279</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44378</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>44466</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>44482</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44487</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44489</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44517</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>44575</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>44726</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>44830</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>44915</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>44928</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>44931</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>44949</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>44991</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>45007</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>45042</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45063</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>45069</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45117</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>45119</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>45167</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>45243</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>45275</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>45324</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>45362</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>43556</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>43558</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>43558</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>43559</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>43566</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>43567</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>43570</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>43578</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>43581</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>43581</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>43584</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>43585</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>43587</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>43591</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>43591</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>43591</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>43592</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>43600</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>43605</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>43606</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>43612</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>43612</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>43613</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>43613</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>43613</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>43613</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>43620</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>43625</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>43629</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>43634</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>43634</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>43640</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>43640</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>43640</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>43640</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>43643</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>43648</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>43656</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>43662</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>43668</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>43668</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>43668</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>43668</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>43675</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>43678</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>43679</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>43680</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>43680</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>43680</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>43680</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>43681</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>43682</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>43683</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>43683</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>43683</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>43684</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>43689</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>43689</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>43691</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>43691</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>43691</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>43691</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>43691</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>43692</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>43693</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>43696</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>43698</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>43698</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>43699</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>43699</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>43702</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>43703</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>43704</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>43704</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>43705</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>43705</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>43705</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>43706</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>43707</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>43710</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>43711</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>43712</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>43712</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>43712</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>43713</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>43714</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>43717</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>43717</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>43717</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         <v>43717</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>43718</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>43718</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>43718</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>43718</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>43719</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>43719</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>43720</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>43721</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>43721</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>43724</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>43726</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>43727</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>43727</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>43727</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>43728</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>43728</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>43732</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>43733</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>43746</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>43749</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>43755</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>43756</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>43756</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>43761</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>43763</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>43763</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>43763</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>43766</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>43769</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>43774</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>43776</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>43776</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>43777</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>43777</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>43777</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>43777</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>43780</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>43780</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>43782</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>43784</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>43784</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>43784</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>43784</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>43787</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>43791</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>43796</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>43796</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>43803</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>43803</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>43803</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>43815</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>43815</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>43815</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>43815</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>43817</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>43829</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>43832</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>43832</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>43832</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>43832</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>43832</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>43832</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>43832</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17353,7 +17353,7 @@
         <v>43832</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>43840</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>43844</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         <v>43846</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>43846</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>43859</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>43865</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>43865</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>43867</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>43867</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>43867</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>43871</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>43871</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>43872</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>43873</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>43873</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>43873</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>43875</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>43875</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>43880</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>43881</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>43886</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>43887</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>43887</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>43887</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>43894</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>43894</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>43899</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18949,7 +18949,7 @@
         <v>43900</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>43907</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>43907</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>43909</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>43914</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>43915</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19291,7 +19291,7 @@
         <v>43916</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>43916</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>43917</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>43929</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>43936</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>43941</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>43949</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>43950</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>43956</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>43963</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>43977</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>43983</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>43984</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>44007</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>44020</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>44032</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>44041</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>44041</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>44047</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>44047</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>44047</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>44048</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>44053</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>44053</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20716,7 +20716,7 @@
         <v>44055</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>44055</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>44055</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20887,7 +20887,7 @@
         <v>44055</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44060</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>44060</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>44061</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>44061</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44061</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>44062</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>44062</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>44074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>44074</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>44074</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>44075</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>44075</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>44077</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>44082</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>44082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>44084</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>44089</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>44089</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44089</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>44089</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>44090</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>44095</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>44095</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44095</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>44098</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>44104</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>44104</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>44105</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44105</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44109</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44110</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44110</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>44111</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44112</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44112</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44119</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>44120</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>44126</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44130</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44131</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>44136</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23338,7 +23338,7 @@
         <v>44138</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>44139</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         <v>44140</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44141</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>44144</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44145</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>44145</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44147</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44151</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>44151</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>44151</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>44151</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>44151</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>44151</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>44154</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44159</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44160</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44178</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>44182</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>44182</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>44186</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>44187</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>44188</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>44192</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>44193</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44193</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>44201</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>44209</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         <v>44210</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>44210</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>44214</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>44214</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>44214</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>44215</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44217</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44218</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44220</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>44229</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>44230</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>44230</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>44230</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>44230</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>44230</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>44230</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>44236</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>44236</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>44236</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>44236</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>44238</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>44241</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>44243</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>44243</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>44244</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>44264</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>44264</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         <v>44267</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>44271</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>44271</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>44271</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44271</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44273</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>44273</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>44277</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>44279</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>44280</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>44285</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44287</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44301</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>44302</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44302</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>44312</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>44312</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>44320</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         <v>44322</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>44326</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>44326</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>44327</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>44333</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>44336</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>44341</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>44341</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>44342</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>44345</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>44348</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>44351</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>44351</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>44356</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>44356</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>44357</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>44357</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>44363</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>44364</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>44369</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>44371</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44375</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44378</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44379</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>44382</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44384</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>44385</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29043,7 +29043,7 @@
         <v>44385</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44385</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>44386</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>44386</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29271,7 +29271,7 @@
         <v>44405</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>44407</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>44407</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44413</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>44417</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44418</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>44419</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44421</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44432</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>44433</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>44434</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>44435</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>44437</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>44438</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>44438</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>44446</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>44447</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>44448</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>44448</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>44448</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>44454</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>44454</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>44455</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>44455</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>44456</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>44457</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>44460</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>44461</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>44461</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>44462</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>44467</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>44474</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>44475</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>44475</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>44476</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>44477</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44477</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>44477</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>44480</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>44482</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>44482</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>44482</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>44482</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>44482</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>44484</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>44489</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>44489</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>44496</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44497</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>44497</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>44497</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>44497</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>44498</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>44498</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>44502</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>44502</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>44502</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>44505</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>44511</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>44517</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32758,7 +32758,7 @@
         <v>44522</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>44522</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>44525</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>44529</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>44531</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>44539</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>44543</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
         <v>44544</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>44544</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>44552</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>44564</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>44564</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>44566</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>44574</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>44581</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>44581</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>44581</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44586</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>44587</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>44588</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34069,7 +34069,7 @@
         <v>44595</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>44602</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>44615</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>44617</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>44617</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>44618</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34468,7 +34468,7 @@
         <v>44620</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34525,7 +34525,7 @@
         <v>44620</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34582,7 +34582,7 @@
         <v>44623</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>44623</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34696,7 +34696,7 @@
         <v>44625</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>44629</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>44629</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>44636</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>44643</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44645</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>44655</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>44656</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44659</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>44679</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>44679</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>44683</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>44684</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44686</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>44690</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>44712</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>44712</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35665,7 +35665,7 @@
         <v>44722</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>44732</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>44732</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>44733</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>44740</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>44740</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36007,7 +36007,7 @@
         <v>44782</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>44782</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>44784</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>44784</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>44790</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44796</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>44796</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44804</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>44810</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
         <v>44810</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36582,7 +36582,7 @@
         <v>44810</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36639,7 +36639,7 @@
         <v>44816</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>44818</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36810,7 +36810,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36924,7 +36924,7 @@
         <v>44819</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36981,7 +36981,7 @@
         <v>44820</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>44823</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44823</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>44823</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>44823</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>44823</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44823</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>44824</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>44830</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>44831</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44841</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44845</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37700,7 +37700,7 @@
         <v>44846</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37757,7 +37757,7 @@
         <v>44846</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37814,7 +37814,7 @@
         <v>44846</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>44847</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>44848</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         <v>44851</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38042,7 +38042,7 @@
         <v>44852</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>44852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>44855</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>44855</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>44855</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>44858</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>44858</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         <v>44858</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>44858</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>44858</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38617,7 +38617,7 @@
         <v>44858</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>44858</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38731,7 +38731,7 @@
         <v>44861</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38788,7 +38788,7 @@
         <v>44861</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38845,7 +38845,7 @@
         <v>44862</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38902,7 +38902,7 @@
         <v>44864</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38959,7 +38959,7 @@
         <v>44865</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>44865</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39073,7 +39073,7 @@
         <v>44872</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>44874</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39187,7 +39187,7 @@
         <v>44882</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39244,7 +39244,7 @@
         <v>44895</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39301,7 +39301,7 @@
         <v>44895</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>44895</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39415,7 +39415,7 @@
         <v>44895</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>44895</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>44901</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>44904</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>44909</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>44909</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>44914</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>44914</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>44914</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>44914</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>44914</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>44915</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40099,7 +40099,7 @@
         <v>44915</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>44915</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>44924</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44924</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>44924</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>44924</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>44930</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44931</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44939</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>44939</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>44949</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>44949</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>44952</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>44955</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>44959</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40959,7 +40959,7 @@
         <v>44963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41016,7 +41016,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>44965</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41187,7 +41187,7 @@
         <v>44965</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>44966</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41301,7 +41301,7 @@
         <v>44970</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41358,7 +41358,7 @@
         <v>44971</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>44971</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>44971</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>44973</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>44973</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>44978</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>44979</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>44979</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>44984</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>44984</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41948,7 +41948,7 @@
         <v>44984</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42005,7 +42005,7 @@
         <v>44988</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42062,7 +42062,7 @@
         <v>44988</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42119,7 +42119,7 @@
         <v>44991</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42176,7 +42176,7 @@
         <v>44993</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44993</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>44993</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>44993</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>44993</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>44994</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>44994</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>44994</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>45001</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>45001</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>45001</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>45001</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>45001</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>45001</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>45001</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>45006</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>45007</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>45007</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>45019</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45027</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43450,7 +43450,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45028</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>45028</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43621,7 +43621,7 @@
         <v>45028</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>45034</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43735,7 +43735,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>45036</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43849,7 +43849,7 @@
         <v>45042</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43906,7 +43906,7 @@
         <v>45042</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43963,7 +43963,7 @@
         <v>45044</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44020,7 +44020,7 @@
         <v>45044</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44077,7 +44077,7 @@
         <v>45050</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>45058</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>45061</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>45063</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>45067</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45070</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44429,7 +44429,7 @@
         <v>45070</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>45070</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>45070</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44610,7 +44610,7 @@
         <v>45071</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
         <v>45071</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44724,7 +44724,7 @@
         <v>45071</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44781,7 +44781,7 @@
         <v>45072</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>45072</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>45075</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>45075</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>45075</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>45075</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45075</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45180,7 +45180,7 @@
         <v>45076</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45242,7 +45242,7 @@
         <v>45077</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>45082</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45356,7 +45356,7 @@
         <v>45082</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>45083</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45470,7 +45470,7 @@
         <v>45086</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45527,7 +45527,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45584,7 +45584,7 @@
         <v>45089</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>45090</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45698,7 +45698,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>45090</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>45090</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>45091</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>45091</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45092</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>45093</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46211,7 +46211,7 @@
         <v>45093</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>45096</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>45096</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45097</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46496,7 +46496,7 @@
         <v>45097</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>45097</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45097</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45099</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46838,7 +46838,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46952,7 +46952,7 @@
         <v>45103</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47009,7 +47009,7 @@
         <v>45103</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47066,7 +47066,7 @@
         <v>45104</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>45104</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>45104</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47247,7 +47247,7 @@
         <v>45104</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47304,7 +47304,7 @@
         <v>45104</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>45104</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47418,7 +47418,7 @@
         <v>45104</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47475,7 +47475,7 @@
         <v>45107</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>45110</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45110</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45110</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45113</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45113</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47827,7 +47827,7 @@
         <v>45114</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>45114</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47941,7 +47941,7 @@
         <v>45114</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47998,7 +47998,7 @@
         <v>45114</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>45114</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>45114</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48169,7 +48169,7 @@
         <v>45118</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48226,7 +48226,7 @@
         <v>45118</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48283,7 +48283,7 @@
         <v>45118</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48340,7 +48340,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48397,7 +48397,7 @@
         <v>45118</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48511,7 +48511,7 @@
         <v>45118</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48568,7 +48568,7 @@
         <v>45119</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>45119</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48682,7 +48682,7 @@
         <v>45119</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48739,7 +48739,7 @@
         <v>45125</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>45125</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48853,7 +48853,7 @@
         <v>45125</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48910,7 +48910,7 @@
         <v>45125</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48967,7 +48967,7 @@
         <v>45126</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49024,7 +49024,7 @@
         <v>45126</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49081,7 +49081,7 @@
         <v>45131</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49138,7 +49138,7 @@
         <v>45134</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49195,7 +49195,7 @@
         <v>45141</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49252,7 +49252,7 @@
         <v>45145</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>45146</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45146</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>45148</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>45148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49537,7 +49537,7 @@
         <v>45148</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49594,7 +49594,7 @@
         <v>45148</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49651,7 +49651,7 @@
         <v>45149</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49708,7 +49708,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49822,7 +49822,7 @@
         <v>45153</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49879,7 +49879,7 @@
         <v>45153</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>45153</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49993,7 +49993,7 @@
         <v>45153</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50050,7 +50050,7 @@
         <v>45153</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>45154</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>45159</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50335,7 +50335,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50392,7 +50392,7 @@
         <v>45161</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>45161</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50506,7 +50506,7 @@
         <v>45163</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>45163</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50640,7 +50640,7 @@
         <v>45165</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50697,7 +50697,7 @@
         <v>45166</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50754,7 +50754,7 @@
         <v>45167</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50811,7 +50811,7 @@
         <v>45167</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>45167</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50925,7 +50925,7 @@
         <v>45169</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
         <v>45169</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45169</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>45169</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51153,7 +51153,7 @@
         <v>45169</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51210,7 +51210,7 @@
         <v>45170</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51267,7 +51267,7 @@
         <v>45170</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51324,7 +51324,7 @@
         <v>45173</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51381,7 +51381,7 @@
         <v>45173</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51438,7 +51438,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51495,7 +51495,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51552,7 +51552,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51609,7 +51609,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45174</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51780,7 +51780,7 @@
         <v>45175</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51837,7 +51837,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>45180</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51951,7 +51951,7 @@
         <v>45180</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52008,7 +52008,7 @@
         <v>45180</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52065,7 +52065,7 @@
         <v>45180</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52122,7 +52122,7 @@
         <v>45181</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52179,7 +52179,7 @@
         <v>45182</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52236,7 +52236,7 @@
         <v>45182</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52293,7 +52293,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52350,7 +52350,7 @@
         <v>45183</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52407,7 +52407,7 @@
         <v>45188</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52464,7 +52464,7 @@
         <v>45189</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52521,7 +52521,7 @@
         <v>45189</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>45190</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52635,7 +52635,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52692,7 +52692,7 @@
         <v>45190</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>45194</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45195</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52863,7 +52863,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52920,7 +52920,7 @@
         <v>45198</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52977,7 +52977,7 @@
         <v>45198</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53034,7 +53034,7 @@
         <v>45198</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>45202</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53148,7 +53148,7 @@
         <v>45202</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45202</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53262,7 +53262,7 @@
         <v>45202</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45205</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>45205</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45205</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>45205</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45205</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>45208</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53661,7 +53661,7 @@
         <v>45208</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>45209</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53775,7 +53775,7 @@
         <v>45209</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53832,7 +53832,7 @@
         <v>45209</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53889,7 +53889,7 @@
         <v>45212</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>45212</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45212</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>45212</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54117,7 +54117,7 @@
         <v>45215</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54174,7 +54174,7 @@
         <v>45218</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54231,7 +54231,7 @@
         <v>45218</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>45218</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54345,7 +54345,7 @@
         <v>45219</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54402,7 +54402,7 @@
         <v>45219</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54459,7 +54459,7 @@
         <v>45219</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54516,7 +54516,7 @@
         <v>45219</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54573,7 +54573,7 @@
         <v>45222</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54630,7 +54630,7 @@
         <v>45223</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54687,7 +54687,7 @@
         <v>45223</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54744,7 +54744,7 @@
         <v>45226</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54801,7 +54801,7 @@
         <v>45229</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54858,7 +54858,7 @@
         <v>45229</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54915,7 +54915,7 @@
         <v>45229</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54972,7 +54972,7 @@
         <v>45229</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55029,7 +55029,7 @@
         <v>45229</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55086,7 +55086,7 @@
         <v>45229</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55143,7 +55143,7 @@
         <v>45230</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55200,7 +55200,7 @@
         <v>45230</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55257,7 +55257,7 @@
         <v>45232</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>45232</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55371,7 +55371,7 @@
         <v>45233</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55428,7 +55428,7 @@
         <v>45233</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55485,7 +55485,7 @@
         <v>45233</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55542,7 +55542,7 @@
         <v>45233</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55599,7 +55599,7 @@
         <v>45233</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55656,7 +55656,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55713,7 +55713,7 @@
         <v>45233</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55770,7 +55770,7 @@
         <v>45233</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55827,7 +55827,7 @@
         <v>45233</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55884,7 +55884,7 @@
         <v>45236</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55941,7 +55941,7 @@
         <v>45237</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55998,7 +55998,7 @@
         <v>45239</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>45243</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         <v>45243</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>45244</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56231,7 +56231,7 @@
         <v>45246</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         <v>45246</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56516,7 +56516,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56630,7 +56630,7 @@
         <v>45246</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56687,7 +56687,7 @@
         <v>45247</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45250</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>45250</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56858,7 +56858,7 @@
         <v>45252</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56915,7 +56915,7 @@
         <v>45252</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56972,7 +56972,7 @@
         <v>45252</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57029,7 +57029,7 @@
         <v>45253</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57086,7 +57086,7 @@
         <v>45254</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57143,7 +57143,7 @@
         <v>45254</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57200,7 +57200,7 @@
         <v>45254</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57257,7 +57257,7 @@
         <v>45254</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57314,7 +57314,7 @@
         <v>45260</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>45260</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57428,7 +57428,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57485,7 +57485,7 @@
         <v>45261</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57542,7 +57542,7 @@
         <v>45264</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>45266</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>45267</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45268</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45268</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>45268</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>45271</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45271</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>45272</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58132,7 +58132,7 @@
         <v>45272</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58189,7 +58189,7 @@
         <v>45272</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58246,7 +58246,7 @@
         <v>45273</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58303,7 +58303,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58360,7 +58360,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58417,7 +58417,7 @@
         <v>45274</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58474,7 +58474,7 @@
         <v>45281</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45286</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45301</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58645,7 +58645,7 @@
         <v>45302</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45306</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58759,7 +58759,7 @@
         <v>45306</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58821,7 +58821,7 @@
         <v>45307</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58878,7 +58878,7 @@
         <v>45307</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58935,7 +58935,7 @@
         <v>45307</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58992,7 +58992,7 @@
         <v>45308</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59049,7 +59049,7 @@
         <v>45308</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59106,7 +59106,7 @@
         <v>45313</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
         <v>45313</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59220,7 +59220,7 @@
         <v>45313</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59277,7 +59277,7 @@
         <v>45313</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59334,7 +59334,7 @@
         <v>45314</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59391,7 +59391,7 @@
         <v>45314</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59448,7 +59448,7 @@
         <v>45314</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59505,7 +59505,7 @@
         <v>45314</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59562,7 +59562,7 @@
         <v>45314</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59619,7 +59619,7 @@
         <v>45319</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59676,7 +59676,7 @@
         <v>45323</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59733,7 +59733,7 @@
         <v>45323</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59790,7 +59790,7 @@
         <v>45323</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59847,7 +59847,7 @@
         <v>45324</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59904,7 +59904,7 @@
         <v>45324</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59961,7 +59961,7 @@
         <v>45327</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60018,7 +60018,7 @@
         <v>45327</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60075,7 +60075,7 @@
         <v>45329</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60132,7 +60132,7 @@
         <v>45329</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60189,7 +60189,7 @@
         <v>45331</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60246,7 +60246,7 @@
         <v>45331</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60303,7 +60303,7 @@
         <v>45331</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60360,7 +60360,7 @@
         <v>45334</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60417,7 +60417,7 @@
         <v>45335</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60479,7 +60479,7 @@
         <v>45335</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60536,7 +60536,7 @@
         <v>45335</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60598,7 +60598,7 @@
         <v>45335</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60660,7 +60660,7 @@
         <v>45335</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60717,7 +60717,7 @@
         <v>45335</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60779,7 +60779,7 @@
         <v>45335</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60841,7 +60841,7 @@
         <v>45336</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60898,7 +60898,7 @@
         <v>45336</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60955,7 +60955,7 @@
         <v>45336</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61012,7 +61012,7 @@
         <v>45336</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61069,7 +61069,7 @@
         <v>45337</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61126,7 +61126,7 @@
         <v>45337</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61183,7 +61183,7 @@
         <v>45338</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61240,7 +61240,7 @@
         <v>45338</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61297,7 +61297,7 @@
         <v>45341</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61354,7 +61354,7 @@
         <v>45341</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61411,7 +61411,7 @@
         <v>45341</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61468,7 +61468,7 @@
         <v>45344</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61525,7 +61525,7 @@
         <v>45345</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61582,7 +61582,7 @@
         <v>45349</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61639,7 +61639,7 @@
         <v>45349</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61696,7 +61696,7 @@
         <v>45351</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61753,7 +61753,7 @@
         <v>45356</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61810,7 +61810,7 @@
         <v>45356</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61867,7 +61867,7 @@
         <v>45362</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61924,7 +61924,7 @@
         <v>45363</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61981,7 +61981,7 @@
         <v>45363</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -62038,7 +62038,7 @@
         <v>45363</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -62095,7 +62095,7 @@
         <v>45363</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62172,7 +62172,7 @@
         <v>45363</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62229,7 +62229,7 @@
         <v>45363</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62286,7 +62286,7 @@
         <v>45364</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62343,7 +62343,7 @@
         <v>45364</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62400,7 +62400,7 @@
         <v>45364</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62457,7 +62457,7 @@
         <v>45370</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62514,7 +62514,7 @@
         <v>45372</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62571,7 +62571,7 @@
         <v>45378</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62628,7 +62628,7 @@
         <v>45378</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62685,7 +62685,7 @@
         <v>45378</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62742,7 +62742,7 @@
         <v>45384</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62799,7 +62799,7 @@
         <v>45384</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62856,7 +62856,7 @@
         <v>45384</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62913,7 +62913,7 @@
         <v>45385</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62975,7 +62975,7 @@
         <v>45385</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -63032,7 +63032,7 @@
         <v>45387</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -63089,7 +63089,7 @@
         <v>45387</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -63146,7 +63146,7 @@
         <v>45387</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63203,7 +63203,7 @@
         <v>45387</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63260,7 +63260,7 @@
         <v>45387</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63317,7 +63317,7 @@
         <v>45391</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63374,7 +63374,7 @@
         <v>45398</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63431,7 +63431,7 @@
         <v>45400</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63488,7 +63488,7 @@
         <v>45400</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63545,7 +63545,7 @@
         <v>45400</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63602,7 +63602,7 @@
         <v>45401</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63659,7 +63659,7 @@
         <v>45401</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63716,7 +63716,7 @@
         <v>45402</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45404</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>45406</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63892,7 +63892,7 @@
         <v>45407</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45411</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -64006,7 +64006,7 @@
         <v>45411</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -64063,7 +64063,7 @@
         <v>45412</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -64120,7 +64120,7 @@
         <v>45412</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -64177,7 +64177,7 @@
         <v>45414</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64234,7 +64234,7 @@
         <v>45418</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>45420</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64348,7 +64348,7 @@
         <v>45429</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64405,7 +64405,7 @@
         <v>45429</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64462,7 +64462,7 @@
         <v>45433</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64519,7 +64519,7 @@
         <v>45439</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64576,7 +64576,7 @@
         <v>45441</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64633,7 +64633,7 @@
         <v>45441</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64690,7 +64690,7 @@
         <v>45442</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64747,7 +64747,7 @@
         <v>45443</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64804,7 +64804,7 @@
         <v>45443</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64861,7 +64861,7 @@
         <v>45446</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64918,7 +64918,7 @@
         <v>45453</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -64975,7 +64975,7 @@
         <v>45454</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -65025,14 +65025,14 @@
     <row r="1081" ht="15" customHeight="1">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>A 23662-2024</t>
+          <t>A 23673-2024</t>
         </is>
       </c>
       <c r="B1081" s="1" t="n">
         <v>45454</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -65044,8 +65044,13 @@
           <t>KALMAR</t>
         </is>
       </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="G1081" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="H1081" t="n">
         <v>0</v>
@@ -65082,14 +65087,14 @@
     <row r="1082" ht="15" customHeight="1">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>A 23673-2024</t>
+          <t>A 23662-2024</t>
         </is>
       </c>
       <c r="B1082" s="1" t="n">
         <v>45454</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -65101,13 +65106,8 @@
           <t>KALMAR</t>
         </is>
       </c>
-      <c r="F1082" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="G1082" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="H1082" t="n">
         <v>0</v>
@@ -65144,14 +65144,14 @@
     <row r="1083" ht="15" customHeight="1">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>A 24649-2024</t>
+          <t>A 24646-2024</t>
         </is>
       </c>
       <c r="B1083" s="1" t="n">
         <v>45460</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65164,7 +65164,7 @@
         </is>
       </c>
       <c r="G1083" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="H1083" t="n">
         <v>0</v>
@@ -65201,14 +65201,14 @@
     <row r="1084" ht="15" customHeight="1">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>A 24643-2024</t>
+          <t>A 24649-2024</t>
         </is>
       </c>
       <c r="B1084" s="1" t="n">
         <v>45460</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65221,7 +65221,7 @@
         </is>
       </c>
       <c r="G1084" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="H1084" t="n">
         <v>0</v>
@@ -65258,14 +65258,14 @@
     <row r="1085" ht="15" customHeight="1">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>A 24646-2024</t>
+          <t>A 24643-2024</t>
         </is>
       </c>
       <c r="B1085" s="1" t="n">
         <v>45460</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -65278,7 +65278,7 @@
         </is>
       </c>
       <c r="G1085" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="H1085" t="n">
         <v>0</v>
@@ -65322,7 +65322,7 @@
         <v>45462</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -65379,7 +65379,7 @@
         <v>45462</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -65429,14 +65429,14 @@
     <row r="1088" ht="15" customHeight="1">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>A 25597-2024</t>
+          <t>A 25594-2024</t>
         </is>
       </c>
       <c r="B1088" s="1" t="n">
         <v>45463</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -65449,7 +65449,7 @@
         </is>
       </c>
       <c r="G1088" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="H1088" t="n">
         <v>0</v>
@@ -65486,14 +65486,14 @@
     <row r="1089" ht="15" customHeight="1">
       <c r="A1089" t="inlineStr">
         <is>
-          <t>A 25594-2024</t>
+          <t>A 25597-2024</t>
         </is>
       </c>
       <c r="B1089" s="1" t="n">
         <v>45463</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -65506,7 +65506,7 @@
         </is>
       </c>
       <c r="G1089" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="H1089" t="n">
         <v>0</v>
@@ -65550,7 +65550,7 @@
         <v>45470</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45385</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>44237</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44245</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44785</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44439</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44489</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>44454</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>44476</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>44979</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>44558</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>44958</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>43591</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>43643</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>43686</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>44057</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>44876</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>45324</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45343</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>43613</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>43640</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>44489</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>44575</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>44785</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>44827</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>44853</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45118</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>45254</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>43674</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>43719</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>43796</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44302</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>44369</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44785</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44802</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>44896</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>44951</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>45105</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>45105</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45125</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43605</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>43614</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>43680</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>43717</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>43731</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>43734</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>43854</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>43927</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>43928</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>43999</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44053</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44069</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>44103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>44152</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>44246</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44260</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44279</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44378</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>44466</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44482</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>44487</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44489</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>44517</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44575</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44726</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>44830</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44915</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>44928</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44931</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44949</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>44991</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>45007</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>45042</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>45063</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45069</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>45117</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>45119</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>45167</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>45243</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45275</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>45324</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45362</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>45475</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>43556</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>43558</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>43558</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>43559</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>43566</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>43567</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>43570</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>43581</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>43581</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>43584</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>43585</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>43587</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>43591</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>43591</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43592</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43600</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43605</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43612</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43612</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43613</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43613</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43613</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43613</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43620</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43625</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43629</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43634</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43634</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43640</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43640</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43640</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43640</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>43643</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>43648</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>43656</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>43662</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>43668</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>43668</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>43668</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>43668</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>43675</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43678</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>43679</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43680</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43680</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>43680</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>43680</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>43681</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>43683</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>43683</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>43683</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>43684</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>43689</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>43689</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>43691</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>43691</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43691</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43691</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43691</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43692</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43693</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>43696</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>43698</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>43698</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>43699</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>43699</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>43702</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>43703</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>43704</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>43704</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>43705</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>43705</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>43705</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>43706</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>43707</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>43710</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>43711</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>43712</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>43712</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>43714</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>43717</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>43717</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>43717</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>43717</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>43718</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>43718</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43718</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43718</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43719</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>43719</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>43720</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>43721</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>43721</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>43724</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>43726</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>43727</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>43727</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>43727</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>43728</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>43728</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>43732</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>43733</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>43746</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>43749</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>43755</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>43756</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>43756</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>43761</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>43763</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>43763</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>43763</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>43766</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>43769</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>43774</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>43776</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>43776</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>43777</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43777</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43777</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43777</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43780</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43780</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43782</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>43784</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>43784</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>43784</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43784</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>43787</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>43791</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>43796</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>43796</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>43803</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>43803</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>43803</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>43815</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>43815</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>43815</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>43815</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>43817</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>43829</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>43832</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>43832</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>43832</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>43832</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>43832</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>43832</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>43832</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>43832</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>43840</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>43844</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>43846</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>43846</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>43859</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>43865</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43865</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>43867</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>43867</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>43867</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>43871</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>43871</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>43872</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>43873</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>43873</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>43873</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>43875</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>43875</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>43880</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>43881</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>43886</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>43887</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>43887</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>43887</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>43894</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>43894</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>43899</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>43900</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>43907</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>43907</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>43909</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>43914</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>43915</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>43916</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>43916</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>43917</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>43929</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>43936</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>43941</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>43949</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>43950</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>43956</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>43963</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>43977</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>43983</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>43984</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>44007</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>44020</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>44032</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>44041</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>44041</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>44047</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>44047</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>44047</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>44048</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>44053</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>44053</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>44055</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>44055</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>44055</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>44055</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44060</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44060</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44061</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44061</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44061</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44062</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44062</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>44074</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>44074</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>44074</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>44075</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>44075</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>44077</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>44082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>44082</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>44084</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>44089</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>44089</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44089</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44089</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44090</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44095</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>44095</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>44095</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>44098</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>44104</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>44104</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>44105</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>44105</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>44109</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>44110</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>44110</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44111</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>44112</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>44112</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>44119</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>44120</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>44126</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44130</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>44131</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>44136</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44138</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>44139</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>44140</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>44141</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>44144</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>44145</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>44145</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>44147</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>44151</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>44151</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>44151</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>44151</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>44151</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44151</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44154</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44159</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44160</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44178</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44182</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>44182</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>44186</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44187</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44188</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>44192</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>44193</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>44193</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>44201</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>44209</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>44210</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>44210</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>44214</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>44214</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>44214</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>44215</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>44217</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>44218</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>44220</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44229</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>44230</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>44230</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>44230</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44230</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44230</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>44230</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44236</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44236</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>44236</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>44236</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>44238</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>44241</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>44243</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>44243</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>44244</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>44264</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>44264</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44267</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44271</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>44271</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>44271</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>44271</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44273</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44273</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>44277</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>44279</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>44280</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>44285</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>44287</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>44301</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>44302</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>44302</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>44312</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>44312</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>44320</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>44322</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>44326</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>44326</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44327</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>44333</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>44336</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>44341</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>44341</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>44342</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>44345</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>44348</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>44351</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>44351</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>44356</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44356</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>44357</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44357</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44363</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44364</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44369</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44371</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44375</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44378</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44379</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44382</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44384</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44385</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44385</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44385</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44386</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44386</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44405</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44407</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44407</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44413</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44417</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44418</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44419</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44421</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44432</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44433</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44434</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44435</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44437</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44438</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>44438</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>44446</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44447</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>44448</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>44448</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>44448</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>44454</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>44454</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>44455</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>44455</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>44456</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>44457</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>44460</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>44461</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>44461</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>44462</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>44467</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>44474</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>44475</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>44475</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>44476</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>44477</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>44477</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>44477</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>44480</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31590,7 +31590,7 @@
         <v>44482</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44482</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44482</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44482</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>44482</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44484</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>44489</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>44489</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>44496</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44497</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>44497</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>44497</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44497</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44498</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44498</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44502</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>44502</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>44502</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>44505</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44511</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>44517</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         <v>44522</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>44522</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>44525</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>44529</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>44531</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44543</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44544</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44544</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44552</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44564</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44564</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44566</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44574</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44581</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44581</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>44581</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44587</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>44588</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44595</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44602</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44615</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>44617</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44617</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44618</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44620</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44620</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44623</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44623</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44625</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44629</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44629</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44636</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44643</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44645</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>44655</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44656</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44659</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>44679</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44679</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44683</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44684</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44686</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44690</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44712</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44712</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44722</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>44732</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44732</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44733</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44740</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44740</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44782</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44782</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44784</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44784</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44790</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44796</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44796</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44804</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>44810</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44810</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44810</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44816</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44818</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44819</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44820</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44823</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44823</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44823</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44823</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>44823</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>44823</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>44824</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44830</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>44831</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>44841</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>44845</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>44846</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>44846</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>44846</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44847</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>44848</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>44851</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>44852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>44852</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>44855</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>44855</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>44855</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44858</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>44858</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>44858</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>44858</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>44858</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>44858</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>44858</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>44861</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38874,7 +38874,7 @@
         <v>44861</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>44862</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>44864</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39045,7 +39045,7 @@
         <v>44865</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>44865</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>44872</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>44874</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>44882</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>44895</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>44895</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44895</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>44895</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39558,7 +39558,7 @@
         <v>44895</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>44901</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>44904</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>44909</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>44909</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>44914</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>44914</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         <v>44914</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>44914</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>44914</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40128,7 +40128,7 @@
         <v>44915</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>44915</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40242,7 +40242,7 @@
         <v>44915</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>44924</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44924</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>44924</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44924</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44930</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>44931</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44939</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>44939</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>44949</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>44949</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>44952</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>44955</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>44959</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41045,7 +41045,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>44963</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>44965</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44965</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>44966</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>44970</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         <v>44971</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>44971</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>44971</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         <v>44973</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>44973</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>44978</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>44979</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41843,7 +41843,7 @@
         <v>44979</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44984</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>44984</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>44984</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>44988</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>44988</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>44991</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>44993</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>44993</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>44993</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>44993</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>44993</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>44994</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>44994</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44994</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45001</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45001</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>45001</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>45001</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>45001</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43023,7 +43023,7 @@
         <v>45001</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>45001</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>45006</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45007</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43308,7 +43308,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>45007</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>45019</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45027</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45028</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45028</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45028</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43764,7 +43764,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>45034</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43878,7 +43878,7 @@
         <v>45036</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43935,7 +43935,7 @@
         <v>45042</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45042</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45044</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45044</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45050</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45058</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45061</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45063</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44396,7 +44396,7 @@
         <v>45067</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>45070</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>45070</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45070</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>45070</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>45071</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>45071</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45071</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>45072</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>45072</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>45075</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>45075</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>45075</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45075</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45075</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45076</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45077</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45082</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45082</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45083</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45086</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>45089</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>45090</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45090</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45090</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45955,7 +45955,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46069,7 +46069,7 @@
         <v>45091</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46126,7 +46126,7 @@
         <v>45091</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
         <v>45092</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46240,7 +46240,7 @@
         <v>45093</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>45093</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45096</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>45096</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45097</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45097</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>45097</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>45097</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45099</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45103</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45103</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45104</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47214,7 +47214,7 @@
         <v>45104</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45104</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47333,7 +47333,7 @@
         <v>45104</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45104</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45104</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45104</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45107</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47618,7 +47618,7 @@
         <v>45110</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45110</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47737,7 +47737,7 @@
         <v>45110</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45113</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45113</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45114</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45114</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45114</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>45114</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45114</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48255,7 +48255,7 @@
         <v>45118</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45118</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48369,7 +48369,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48426,7 +48426,7 @@
         <v>45118</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48540,7 +48540,7 @@
         <v>45118</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48597,7 +48597,7 @@
         <v>45118</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45119</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48711,7 +48711,7 @@
         <v>45119</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>45119</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>45125</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>45125</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45125</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>45125</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45126</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45126</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>45131</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45134</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>45141</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45145</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>45146</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49452,7 +49452,7 @@
         <v>45146</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>45148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>45148</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>45148</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45148</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49794,7 +49794,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49851,7 +49851,7 @@
         <v>45149</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49908,7 +49908,7 @@
         <v>45153</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49965,7 +49965,7 @@
         <v>45153</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50022,7 +50022,7 @@
         <v>45153</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>45153</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50136,7 +50136,7 @@
         <v>45153</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50193,7 +50193,7 @@
         <v>45154</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50250,7 +50250,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45156</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50421,7 +50421,7 @@
         <v>45159</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50478,7 +50478,7 @@
         <v>45161</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>45161</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45163</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50669,7 +50669,7 @@
         <v>45163</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>45165</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50783,7 +50783,7 @@
         <v>45166</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50840,7 +50840,7 @@
         <v>45167</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>45167</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         <v>45167</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51011,7 +51011,7 @@
         <v>45169</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45169</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45169</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45169</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45169</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45170</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45170</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45173</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51581,7 +51581,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51638,7 +51638,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51695,7 +51695,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51752,7 +51752,7 @@
         <v>45173</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45174</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51866,7 +51866,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51980,7 +51980,7 @@
         <v>45180</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45180</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45180</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45180</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>45181</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52265,7 +52265,7 @@
         <v>45182</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52322,7 +52322,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>45182</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52436,7 +52436,7 @@
         <v>45183</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>45188</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45189</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45189</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45190</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45190</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45194</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45195</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53006,7 +53006,7 @@
         <v>45198</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53063,7 +53063,7 @@
         <v>45198</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45202</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45202</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45202</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45202</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45205</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45205</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45205</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45205</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45205</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45208</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45208</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45209</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45209</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45209</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>45212</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45212</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45212</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45212</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45215</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45218</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45218</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45218</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45219</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45219</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45219</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45219</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45222</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45223</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45223</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45226</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45229</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45229</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45229</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45229</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45229</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45229</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55229,7 +55229,7 @@
         <v>45230</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>45230</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>45232</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>45232</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55457,7 +55457,7 @@
         <v>45233</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55514,7 +55514,7 @@
         <v>45233</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55571,7 +55571,7 @@
         <v>45233</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55628,7 +55628,7 @@
         <v>45233</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55685,7 +55685,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>45233</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>45233</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55856,7 +55856,7 @@
         <v>45233</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55913,7 +55913,7 @@
         <v>45233</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55970,7 +55970,7 @@
         <v>45236</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56027,7 +56027,7 @@
         <v>45237</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56084,7 +56084,7 @@
         <v>45239</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56146,7 +56146,7 @@
         <v>45243</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56203,7 +56203,7 @@
         <v>45243</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56260,7 +56260,7 @@
         <v>45244</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56317,7 +56317,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56374,7 +56374,7 @@
         <v>45246</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56431,7 +56431,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56545,7 +56545,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56602,7 +56602,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45246</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56716,7 +56716,7 @@
         <v>45246</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56773,7 +56773,7 @@
         <v>45247</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>45250</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56887,7 +56887,7 @@
         <v>45250</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45252</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57001,7 +57001,7 @@
         <v>45252</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45252</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45254</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57229,7 +57229,7 @@
         <v>45254</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>45254</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57343,7 +57343,7 @@
         <v>45254</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>45260</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45260</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>45261</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57628,7 +57628,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57705,7 +57705,7 @@
         <v>45264</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57762,7 +57762,7 @@
         <v>45266</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45267</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57876,7 +57876,7 @@
         <v>45268</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57933,7 +57933,7 @@
         <v>45268</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57990,7 +57990,7 @@
         <v>45268</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58047,7 +58047,7 @@
         <v>45271</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>45271</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58161,7 +58161,7 @@
         <v>45272</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58218,7 +58218,7 @@
         <v>45272</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58275,7 +58275,7 @@
         <v>45272</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45273</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58503,7 +58503,7 @@
         <v>45274</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45281</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58617,7 +58617,7 @@
         <v>45286</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58674,7 +58674,7 @@
         <v>45301</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58731,7 +58731,7 @@
         <v>45302</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58788,7 +58788,7 @@
         <v>45306</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58845,7 +58845,7 @@
         <v>45306</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>45307</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58964,7 +58964,7 @@
         <v>45307</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59021,7 +59021,7 @@
         <v>45307</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59078,7 +59078,7 @@
         <v>45308</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>45308</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59192,7 +59192,7 @@
         <v>45313</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59249,7 +59249,7 @@
         <v>45313</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59306,7 +59306,7 @@
         <v>45313</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59363,7 +59363,7 @@
         <v>45313</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59420,7 +59420,7 @@
         <v>45314</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59477,7 +59477,7 @@
         <v>45314</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59534,7 +59534,7 @@
         <v>45314</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59591,7 +59591,7 @@
         <v>45314</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59648,7 +59648,7 @@
         <v>45314</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59705,7 +59705,7 @@
         <v>45319</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59762,7 +59762,7 @@
         <v>45323</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59819,7 +59819,7 @@
         <v>45323</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59876,7 +59876,7 @@
         <v>45323</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59933,7 +59933,7 @@
         <v>45324</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59990,7 +59990,7 @@
         <v>45324</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60047,7 +60047,7 @@
         <v>45327</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60104,7 +60104,7 @@
         <v>45327</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60161,7 +60161,7 @@
         <v>45329</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60218,7 +60218,7 @@
         <v>45329</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60275,7 +60275,7 @@
         <v>45331</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60332,7 +60332,7 @@
         <v>45331</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60389,7 +60389,7 @@
         <v>45331</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60446,7 +60446,7 @@
         <v>45334</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60503,7 +60503,7 @@
         <v>45335</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>45335</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60622,7 +60622,7 @@
         <v>45335</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60684,7 +60684,7 @@
         <v>45335</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60746,7 +60746,7 @@
         <v>45335</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60803,7 +60803,7 @@
         <v>45335</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60865,7 +60865,7 @@
         <v>45335</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60927,7 +60927,7 @@
         <v>45336</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60984,7 +60984,7 @@
         <v>45336</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61041,7 +61041,7 @@
         <v>45336</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61098,7 +61098,7 @@
         <v>45336</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61155,7 +61155,7 @@
         <v>45337</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61212,7 +61212,7 @@
         <v>45337</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45338</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61326,7 +61326,7 @@
         <v>45338</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61383,7 +61383,7 @@
         <v>45341</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61440,7 +61440,7 @@
         <v>45341</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>45341</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61554,7 +61554,7 @@
         <v>45344</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61611,7 +61611,7 @@
         <v>45345</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61668,7 +61668,7 @@
         <v>45349</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61725,7 +61725,7 @@
         <v>45349</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61782,7 +61782,7 @@
         <v>45351</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61839,7 +61839,7 @@
         <v>45356</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61896,7 +61896,7 @@
         <v>45356</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61953,7 +61953,7 @@
         <v>45362</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -62010,7 +62010,7 @@
         <v>45363</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -62067,7 +62067,7 @@
         <v>45363</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -62124,7 +62124,7 @@
         <v>45363</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62181,7 +62181,7 @@
         <v>45363</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62258,7 +62258,7 @@
         <v>45363</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62315,7 +62315,7 @@
         <v>45363</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62372,7 +62372,7 @@
         <v>45364</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>45364</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62486,7 +62486,7 @@
         <v>45364</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45370</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>45372</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62657,7 +62657,7 @@
         <v>45378</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62714,7 +62714,7 @@
         <v>45378</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62771,7 +62771,7 @@
         <v>45378</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62828,7 +62828,7 @@
         <v>45384</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62885,7 +62885,7 @@
         <v>45384</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62942,7 +62942,7 @@
         <v>45384</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62999,7 +62999,7 @@
         <v>45385</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -63061,7 +63061,7 @@
         <v>45385</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -63118,7 +63118,7 @@
         <v>45387</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -63175,7 +63175,7 @@
         <v>45387</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63232,7 +63232,7 @@
         <v>45387</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63289,7 +63289,7 @@
         <v>45387</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63346,7 +63346,7 @@
         <v>45387</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63403,7 +63403,7 @@
         <v>45391</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63460,7 +63460,7 @@
         <v>45398</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63517,7 +63517,7 @@
         <v>45400</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63574,7 +63574,7 @@
         <v>45400</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63631,7 +63631,7 @@
         <v>45400</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63688,7 +63688,7 @@
         <v>45401</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63745,7 +63745,7 @@
         <v>45401</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63802,7 +63802,7 @@
         <v>45402</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63864,7 +63864,7 @@
         <v>45404</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63921,7 +63921,7 @@
         <v>45406</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63978,7 +63978,7 @@
         <v>45407</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -64035,7 +64035,7 @@
         <v>45411</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45411</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45412</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>45412</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64263,7 +64263,7 @@
         <v>45414</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64320,7 +64320,7 @@
         <v>45418</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64377,7 +64377,7 @@
         <v>45420</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64434,7 +64434,7 @@
         <v>45429</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>45429</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64548,7 +64548,7 @@
         <v>45433</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64605,7 +64605,7 @@
         <v>45439</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64662,7 +64662,7 @@
         <v>45441</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64719,7 +64719,7 @@
         <v>45441</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64776,7 +64776,7 @@
         <v>45442</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64833,7 +64833,7 @@
         <v>45443</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64890,7 +64890,7 @@
         <v>45443</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64947,7 +64947,7 @@
         <v>45446</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -65004,7 +65004,7 @@
         <v>45453</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -65061,7 +65061,7 @@
         <v>45454</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>45454</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -65175,7 +65175,7 @@
         <v>45454</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65237,7 +65237,7 @@
         <v>45460</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>45460</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -65351,7 +65351,7 @@
         <v>45460</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -65408,7 +65408,7 @@
         <v>45462</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -65465,7 +65465,7 @@
         <v>45462</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -65522,7 +65522,7 @@
         <v>45463</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -65579,7 +65579,7 @@
         <v>45463</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -65636,7 +65636,7 @@
         <v>45470</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -65693,7 +65693,7 @@
         <v>45476</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -65750,7 +65750,7 @@
         <v>45478</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -65807,7 +65807,7 @@
         <v>45478</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -65864,7 +65864,7 @@
         <v>45488</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -65921,7 +65921,7 @@
         <v>45488</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -65978,7 +65978,7 @@
         <v>45489</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -66035,7 +66035,7 @@
         <v>45491</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -66092,7 +66092,7 @@
         <v>45492</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -66149,7 +66149,7 @@
         <v>45492</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -66206,7 +66206,7 @@
         <v>45503</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45385</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>44237</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44245</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44785</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44439</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44489</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>44454</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>44476</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>44979</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>44558</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>44958</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>43591</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>43643</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>43686</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>44057</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>44876</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>45324</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45343</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>43613</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>43640</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>44489</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>44575</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>44785</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>44827</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>44853</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45118</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>45254</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>43674</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>43719</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>43796</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44302</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>44369</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44785</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44802</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>44896</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>44951</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>45105</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>45105</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45125</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43605</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>43614</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>43680</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>43717</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>43731</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>43734</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>43854</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>43927</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>43928</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>43999</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44053</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44069</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>44103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>44152</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>44246</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44260</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44279</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44378</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>44466</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44482</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>44487</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44489</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>44517</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44575</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44726</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>44830</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44915</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>44928</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44931</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44949</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>44991</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>45007</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>45042</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>45063</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45069</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>45117</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>45119</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>45167</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>45243</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45275</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>45324</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45362</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>45475</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>43556</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>43558</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>43558</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>43559</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>43566</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>43567</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>43570</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>43581</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>43581</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>43584</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>43585</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>43587</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>43591</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>43591</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43592</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43600</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43605</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43612</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43612</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43613</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43613</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43613</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43613</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43620</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43625</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43629</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43634</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43634</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43640</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43640</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43640</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43640</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>43643</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>43648</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>43656</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>43662</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>43668</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>43668</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>43668</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>43668</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>43675</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43678</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>43679</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43680</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43680</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>43680</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>43680</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>43681</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>43683</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>43683</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>43683</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>43684</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>43689</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>43689</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>43691</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>43691</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43691</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43691</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43691</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43692</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43693</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>43696</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>43698</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>43698</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>43699</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>43699</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>43702</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>43703</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>43704</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>43704</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>43705</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>43705</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>43705</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>43706</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>43707</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>43710</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>43711</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>43712</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>43712</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>43714</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>43717</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>43717</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>43717</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>43717</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>43718</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>43718</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43718</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43718</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43719</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>43719</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>43720</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>43721</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>43721</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>43724</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>43726</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>43727</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>43727</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>43727</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>43728</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>43728</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>43732</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>43733</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>43746</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>43749</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>43755</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>43756</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>43756</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>43761</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>43763</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>43763</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>43763</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>43766</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>43769</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>43774</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>43776</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>43776</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>43777</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43777</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43777</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43777</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43780</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43780</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43782</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>43784</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>43784</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>43784</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43784</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>43787</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>43791</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>43796</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>43796</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>43803</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>43803</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>43803</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>43815</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>43815</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>43815</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>43815</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>43817</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>43829</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>43832</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>43832</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>43832</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>43832</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>43832</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>43832</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>43832</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>43832</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>43840</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>43844</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>43846</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>43846</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>43859</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>43865</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43865</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>43867</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>43867</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>43867</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>43871</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>43871</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>43872</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>43873</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>43873</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>43873</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>43875</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>43875</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>43880</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>43881</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>43886</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>43887</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>43887</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>43887</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>43894</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>43894</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>43899</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>43900</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>43907</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>43907</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>43909</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>43914</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>43915</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>43916</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>43916</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>43917</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>43929</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>43936</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>43941</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>43949</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>43950</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>43956</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>43963</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>43977</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>43983</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>43984</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>44007</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>44020</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>44032</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>44041</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>44041</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>44047</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>44047</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>44047</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>44048</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>44053</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>44053</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>44055</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>44055</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>44055</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>44055</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44060</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44060</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44061</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44061</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44061</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44062</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44062</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>44074</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>44074</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>44074</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>44075</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>44075</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>44077</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>44082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>44082</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>44084</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>44089</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>44089</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44089</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44089</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44090</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44095</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>44095</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>44095</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>44098</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>44104</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>44104</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>44105</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>44105</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>44109</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>44110</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>44110</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44111</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>44112</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>44112</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>44119</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>44120</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>44126</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44130</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>44131</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>44136</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44138</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>44139</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>44140</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>44141</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>44144</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>44145</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>44145</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>44147</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>44151</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>44151</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>44151</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>44151</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>44151</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44151</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44154</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44159</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44160</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44178</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44182</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>44182</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>44186</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44187</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44188</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>44192</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>44193</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>44193</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>44201</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>44209</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>44210</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>44210</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>44214</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>44214</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>44214</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>44215</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>44217</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>44218</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>44220</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44229</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>44230</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>44230</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>44230</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44230</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44230</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>44230</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44236</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44236</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>44236</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>44236</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>44238</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>44241</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>44243</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>44243</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>44244</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>44264</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>44264</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44267</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44271</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>44271</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>44271</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>44271</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44273</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44273</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>44277</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>44279</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>44280</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>44285</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>44287</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>44301</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>44302</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>44302</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>44312</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>44312</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>44320</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>44322</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>44326</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>44326</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44327</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>44333</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>44336</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>44341</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>44341</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>44342</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>44345</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>44348</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>44351</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>44351</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>44356</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44356</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>44357</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44357</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44363</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44364</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44369</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44371</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44375</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44378</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44379</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44382</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44384</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44385</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44385</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44385</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44386</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44386</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44405</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44407</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44407</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44413</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44417</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44418</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44419</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44421</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44432</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44433</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44434</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44435</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44437</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44438</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>44438</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>44446</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44447</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>44448</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>44448</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>44448</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>44454</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>44454</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>44455</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>44455</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>44456</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>44457</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>44460</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>44461</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>44461</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>44462</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>44467</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>44474</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>44475</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>44475</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>44476</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>44477</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>44477</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>44477</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>44480</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31590,7 +31590,7 @@
         <v>44482</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44482</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44482</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44482</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>44482</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44484</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>44489</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>44489</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>44496</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44497</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>44497</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>44497</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44497</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44498</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44498</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44502</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>44502</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>44502</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>44505</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44511</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>44517</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         <v>44522</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>44522</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>44525</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>44529</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>44531</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44543</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44544</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44544</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44552</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44564</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44564</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44566</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44574</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44581</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44581</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>44581</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44587</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>44588</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44595</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44602</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44615</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>44617</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44617</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44618</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44620</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44620</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44623</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44623</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44625</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44629</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44629</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44636</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44643</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44645</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>44655</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44656</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44659</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>44679</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44679</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44683</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44684</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44686</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44690</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44712</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44712</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44722</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>44732</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44732</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44733</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44740</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44740</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44782</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44782</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44784</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44784</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44790</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44796</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44796</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44804</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>44810</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44810</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44810</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44816</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44818</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44819</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44820</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44823</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44823</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44823</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44823</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>44823</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>44823</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>44824</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44830</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>44831</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>44841</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>44845</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>44846</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>44846</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>44846</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44847</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>44848</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>44851</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>44852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>44852</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>44855</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>44855</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>44855</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44858</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>44858</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>44858</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>44858</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>44858</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>44858</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>44858</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>44861</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38874,7 +38874,7 @@
         <v>44861</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>44862</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>44864</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39045,7 +39045,7 @@
         <v>44865</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>44865</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>44872</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>44874</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>44882</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>44895</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>44895</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44895</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>44895</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39558,7 +39558,7 @@
         <v>44895</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>44901</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>44904</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>44909</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>44909</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>44914</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>44914</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         <v>44914</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>44914</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>44914</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40128,7 +40128,7 @@
         <v>44915</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>44915</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40242,7 +40242,7 @@
         <v>44915</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>44924</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44924</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>44924</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44924</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44930</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>44931</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44939</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>44939</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>44949</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>44949</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>44952</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>44955</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>44959</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41045,7 +41045,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>44963</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>44965</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44965</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>44966</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>44970</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         <v>44971</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>44971</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>44971</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         <v>44973</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>44973</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>44978</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>44979</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41843,7 +41843,7 @@
         <v>44979</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44984</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>44984</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>44984</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>44988</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>44988</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>44991</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>44993</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>44993</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>44993</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>44993</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>44993</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>44994</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>44994</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44994</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45001</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45001</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>45001</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>45001</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>45001</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43023,7 +43023,7 @@
         <v>45001</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>45001</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>45006</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45007</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43308,7 +43308,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>45007</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>45019</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45027</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45028</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45028</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45028</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43764,7 +43764,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>45034</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43878,7 +43878,7 @@
         <v>45036</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43935,7 +43935,7 @@
         <v>45042</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45042</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45044</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45044</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45050</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45058</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45061</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45063</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44396,7 +44396,7 @@
         <v>45067</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>45070</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>45070</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45070</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>45070</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>45071</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>45071</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45071</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>45072</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>45072</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>45075</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>45075</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>45075</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45075</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45075</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45076</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45077</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45082</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45082</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45083</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45086</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>45089</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>45090</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45090</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45090</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45955,7 +45955,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46069,7 +46069,7 @@
         <v>45091</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46126,7 +46126,7 @@
         <v>45091</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
         <v>45092</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46240,7 +46240,7 @@
         <v>45093</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>45093</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45096</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>45096</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45097</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45097</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>45097</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>45097</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45099</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45103</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45103</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45104</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47214,7 +47214,7 @@
         <v>45104</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45104</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47333,7 +47333,7 @@
         <v>45104</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45104</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45104</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45104</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45107</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47618,7 +47618,7 @@
         <v>45110</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45110</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47737,7 +47737,7 @@
         <v>45110</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45113</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45113</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45114</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45114</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45114</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>45114</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45114</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48255,7 +48255,7 @@
         <v>45118</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45118</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48369,7 +48369,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48426,7 +48426,7 @@
         <v>45118</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48540,7 +48540,7 @@
         <v>45118</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48597,7 +48597,7 @@
         <v>45118</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45119</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48711,7 +48711,7 @@
         <v>45119</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>45119</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>45125</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>45125</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45125</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>45125</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45126</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45126</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>45131</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45134</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>45141</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45145</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>45146</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49452,7 +49452,7 @@
         <v>45146</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>45148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>45148</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>45148</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45148</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49794,7 +49794,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49851,7 +49851,7 @@
         <v>45149</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49908,7 +49908,7 @@
         <v>45153</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49965,7 +49965,7 @@
         <v>45153</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50022,7 +50022,7 @@
         <v>45153</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>45153</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50136,7 +50136,7 @@
         <v>45153</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50193,7 +50193,7 @@
         <v>45154</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50250,7 +50250,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45156</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50421,7 +50421,7 @@
         <v>45159</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50478,7 +50478,7 @@
         <v>45161</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>45161</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45163</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50669,7 +50669,7 @@
         <v>45163</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>45165</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50783,7 +50783,7 @@
         <v>45166</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50840,7 +50840,7 @@
         <v>45167</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>45167</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         <v>45167</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51011,7 +51011,7 @@
         <v>45169</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45169</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45169</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45169</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45169</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45170</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45170</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45173</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51581,7 +51581,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51638,7 +51638,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51695,7 +51695,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51752,7 +51752,7 @@
         <v>45173</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45174</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51866,7 +51866,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51980,7 +51980,7 @@
         <v>45180</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45180</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45180</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45180</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>45181</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52265,7 +52265,7 @@
         <v>45182</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52322,7 +52322,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>45182</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52436,7 +52436,7 @@
         <v>45183</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>45188</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45189</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45189</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45190</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45190</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45194</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45195</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53006,7 +53006,7 @@
         <v>45198</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53063,7 +53063,7 @@
         <v>45198</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45202</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45202</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45202</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45202</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45205</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45205</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45205</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45205</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45205</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45208</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45208</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45209</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45209</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45209</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>45212</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45212</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45212</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45212</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45215</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45218</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45218</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45218</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45219</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45219</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45219</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45219</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45222</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45223</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45223</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45226</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45229</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45229</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45229</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45229</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45229</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45229</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55229,7 +55229,7 @@
         <v>45230</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>45230</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>45232</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>45232</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55457,7 +55457,7 @@
         <v>45233</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55514,7 +55514,7 @@
         <v>45233</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55571,7 +55571,7 @@
         <v>45233</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55628,7 +55628,7 @@
         <v>45233</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55685,7 +55685,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>45233</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>45233</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55856,7 +55856,7 @@
         <v>45233</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55913,7 +55913,7 @@
         <v>45233</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55970,7 +55970,7 @@
         <v>45236</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56027,7 +56027,7 @@
         <v>45237</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56084,7 +56084,7 @@
         <v>45239</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56146,7 +56146,7 @@
         <v>45243</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56203,7 +56203,7 @@
         <v>45243</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56260,7 +56260,7 @@
         <v>45244</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56317,7 +56317,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56374,7 +56374,7 @@
         <v>45246</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56431,7 +56431,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56545,7 +56545,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56602,7 +56602,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45246</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56716,7 +56716,7 @@
         <v>45246</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56773,7 +56773,7 @@
         <v>45247</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>45250</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56887,7 +56887,7 @@
         <v>45250</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45252</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57001,7 +57001,7 @@
         <v>45252</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45252</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45254</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57229,7 +57229,7 @@
         <v>45254</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>45254</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57343,7 +57343,7 @@
         <v>45254</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>45260</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45260</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>45261</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57628,7 +57628,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57705,7 +57705,7 @@
         <v>45264</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57762,7 +57762,7 @@
         <v>45266</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45267</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57876,7 +57876,7 @@
         <v>45268</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57933,7 +57933,7 @@
         <v>45268</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57990,7 +57990,7 @@
         <v>45268</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58047,7 +58047,7 @@
         <v>45271</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>45271</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58161,7 +58161,7 @@
         <v>45272</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58218,7 +58218,7 @@
         <v>45272</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58275,7 +58275,7 @@
         <v>45272</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45273</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58503,7 +58503,7 @@
         <v>45274</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45281</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58617,7 +58617,7 @@
         <v>45286</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58674,7 +58674,7 @@
         <v>45301</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58731,7 +58731,7 @@
         <v>45302</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58788,7 +58788,7 @@
         <v>45306</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58845,7 +58845,7 @@
         <v>45306</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>45307</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58964,7 +58964,7 @@
         <v>45307</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59021,7 +59021,7 @@
         <v>45307</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59078,7 +59078,7 @@
         <v>45308</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>45308</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59192,7 +59192,7 @@
         <v>45313</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59249,7 +59249,7 @@
         <v>45313</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59306,7 +59306,7 @@
         <v>45313</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59363,7 +59363,7 @@
         <v>45313</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59420,7 +59420,7 @@
         <v>45314</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59477,7 +59477,7 @@
         <v>45314</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59534,7 +59534,7 @@
         <v>45314</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59591,7 +59591,7 @@
         <v>45314</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59648,7 +59648,7 @@
         <v>45314</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59705,7 +59705,7 @@
         <v>45319</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59762,7 +59762,7 @@
         <v>45323</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59819,7 +59819,7 @@
         <v>45323</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59876,7 +59876,7 @@
         <v>45323</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59933,7 +59933,7 @@
         <v>45324</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59990,7 +59990,7 @@
         <v>45324</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60047,7 +60047,7 @@
         <v>45327</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60104,7 +60104,7 @@
         <v>45327</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60161,7 +60161,7 @@
         <v>45329</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60218,7 +60218,7 @@
         <v>45329</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60275,7 +60275,7 @@
         <v>45331</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60332,7 +60332,7 @@
         <v>45331</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60389,7 +60389,7 @@
         <v>45331</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60446,7 +60446,7 @@
         <v>45334</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60503,7 +60503,7 @@
         <v>45335</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>45335</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60622,7 +60622,7 @@
         <v>45335</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60684,7 +60684,7 @@
         <v>45335</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60746,7 +60746,7 @@
         <v>45335</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60803,7 +60803,7 @@
         <v>45335</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60865,7 +60865,7 @@
         <v>45335</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60927,7 +60927,7 @@
         <v>45336</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60984,7 +60984,7 @@
         <v>45336</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61041,7 +61041,7 @@
         <v>45336</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61098,7 +61098,7 @@
         <v>45336</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61155,7 +61155,7 @@
         <v>45337</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61212,7 +61212,7 @@
         <v>45337</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45338</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61326,7 +61326,7 @@
         <v>45338</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61383,7 +61383,7 @@
         <v>45341</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61440,7 +61440,7 @@
         <v>45341</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>45341</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61554,7 +61554,7 @@
         <v>45344</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61611,7 +61611,7 @@
         <v>45345</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61668,7 +61668,7 @@
         <v>45349</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61725,7 +61725,7 @@
         <v>45349</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61782,7 +61782,7 @@
         <v>45351</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61839,7 +61839,7 @@
         <v>45356</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61896,7 +61896,7 @@
         <v>45356</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61953,7 +61953,7 @@
         <v>45362</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -62010,7 +62010,7 @@
         <v>45363</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -62067,7 +62067,7 @@
         <v>45363</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -62124,7 +62124,7 @@
         <v>45363</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62181,7 +62181,7 @@
         <v>45363</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62258,7 +62258,7 @@
         <v>45363</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62315,7 +62315,7 @@
         <v>45363</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62372,7 +62372,7 @@
         <v>45364</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>45364</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62486,7 +62486,7 @@
         <v>45364</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45370</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>45372</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62657,7 +62657,7 @@
         <v>45378</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62714,7 +62714,7 @@
         <v>45378</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62771,7 +62771,7 @@
         <v>45378</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62828,7 +62828,7 @@
         <v>45384</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62885,7 +62885,7 @@
         <v>45384</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62942,7 +62942,7 @@
         <v>45384</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62999,7 +62999,7 @@
         <v>45385</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -63061,7 +63061,7 @@
         <v>45385</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -63118,7 +63118,7 @@
         <v>45387</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -63175,7 +63175,7 @@
         <v>45387</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63232,7 +63232,7 @@
         <v>45387</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63289,7 +63289,7 @@
         <v>45387</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63346,7 +63346,7 @@
         <v>45387</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63403,7 +63403,7 @@
         <v>45391</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63460,7 +63460,7 @@
         <v>45398</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63517,7 +63517,7 @@
         <v>45400</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63574,7 +63574,7 @@
         <v>45400</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63631,7 +63631,7 @@
         <v>45400</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63688,7 +63688,7 @@
         <v>45401</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63745,7 +63745,7 @@
         <v>45401</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63802,7 +63802,7 @@
         <v>45402</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63864,7 +63864,7 @@
         <v>45404</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63921,7 +63921,7 @@
         <v>45406</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63978,7 +63978,7 @@
         <v>45407</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -64035,7 +64035,7 @@
         <v>45411</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45411</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45412</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>45412</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64263,7 +64263,7 @@
         <v>45414</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64320,7 +64320,7 @@
         <v>45418</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64377,7 +64377,7 @@
         <v>45420</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64434,7 +64434,7 @@
         <v>45429</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>45429</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64548,7 +64548,7 @@
         <v>45433</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64605,7 +64605,7 @@
         <v>45439</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64662,7 +64662,7 @@
         <v>45441</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64719,7 +64719,7 @@
         <v>45441</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64776,7 +64776,7 @@
         <v>45442</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64833,7 +64833,7 @@
         <v>45443</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64890,7 +64890,7 @@
         <v>45443</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64947,7 +64947,7 @@
         <v>45446</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -65004,7 +65004,7 @@
         <v>45453</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -65061,7 +65061,7 @@
         <v>45454</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>45454</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -65175,7 +65175,7 @@
         <v>45454</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65237,7 +65237,7 @@
         <v>45460</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>45460</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -65351,7 +65351,7 @@
         <v>45460</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -65408,7 +65408,7 @@
         <v>45462</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -65465,7 +65465,7 @@
         <v>45462</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -65522,7 +65522,7 @@
         <v>45463</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -65579,7 +65579,7 @@
         <v>45463</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -65636,7 +65636,7 @@
         <v>45470</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -65693,7 +65693,7 @@
         <v>45476</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -65750,7 +65750,7 @@
         <v>45478</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -65807,7 +65807,7 @@
         <v>45478</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -65864,7 +65864,7 @@
         <v>45488</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -65921,7 +65921,7 @@
         <v>45488</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -65978,7 +65978,7 @@
         <v>45489</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -66035,7 +66035,7 @@
         <v>45491</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -66092,7 +66092,7 @@
         <v>45492</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -66149,7 +66149,7 @@
         <v>45492</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -66206,7 +66206,7 @@
         <v>45503</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45506</v>
+        <v>45507</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45385</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>44237</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44245</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44785</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44439</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44489</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>44454</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>44476</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>44979</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>44558</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>44958</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>43591</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>43643</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>43686</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>44057</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>44876</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>45324</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45343</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>43613</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>43640</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>44489</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>44575</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>44785</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>44827</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>44853</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45118</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>45254</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>43674</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>43719</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>43796</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44302</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>44369</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44785</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44802</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>44896</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>44951</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>45105</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>45105</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45125</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43605</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>43614</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>43680</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>43717</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>43731</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>43734</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>43854</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>43927</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>43928</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>43999</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44053</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44069</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>44103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>44152</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>44246</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44260</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44279</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44378</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>44466</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44482</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>44487</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44489</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>44517</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44575</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44726</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>44830</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44915</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>44928</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44931</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44949</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>44991</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>45007</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>45042</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>45063</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45069</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>45117</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>45119</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>45167</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>45243</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45275</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>45324</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45362</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>45475</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>43556</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>43558</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>43558</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>43559</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>43566</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>43567</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>43570</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>43581</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>43581</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>43584</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>43585</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>43587</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>43591</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>43591</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43592</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43600</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43605</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43612</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43612</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43613</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43613</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43613</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43613</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43620</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43625</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43629</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43634</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43634</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43640</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43640</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43640</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43640</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>43643</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>43648</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>43656</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>43662</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>43668</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>43668</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>43668</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>43668</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>43675</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43678</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>43679</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43680</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43680</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>43680</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>43680</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>43681</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>43683</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>43683</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>43683</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>43684</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>43689</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>43689</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>43691</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>43691</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43691</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43691</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43691</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43692</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43693</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>43696</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>43698</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>43698</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>43699</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>43699</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>43702</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>43703</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>43704</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>43704</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>43705</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>43705</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>43705</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>43706</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>43707</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>43710</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>43711</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>43712</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>43712</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>43714</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>43717</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>43717</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>43717</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>43717</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>43718</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>43718</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43718</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43718</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43719</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>43719</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>43720</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>43721</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>43721</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>43724</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>43726</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>43727</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>43727</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>43727</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>43728</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>43728</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>43732</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>43733</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>43746</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>43749</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>43755</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>43756</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>43756</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>43761</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>43763</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>43763</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>43763</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>43766</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>43769</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>43774</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>43776</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>43776</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>43777</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43777</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43777</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43777</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43780</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43780</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43782</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>43784</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>43784</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>43784</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43784</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>43787</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>43791</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>43796</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>43796</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>43803</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>43803</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>43803</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>43815</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>43815</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>43815</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>43815</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>43817</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>43829</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>43832</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>43832</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>43832</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>43832</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>43832</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>43832</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>43832</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>43832</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>43840</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>43844</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>43846</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>43846</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>43859</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>43865</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43865</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>43867</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>43867</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>43867</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>43871</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>43871</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>43872</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>43873</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>43873</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>43873</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>43875</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>43875</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>43880</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>43881</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>43886</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>43887</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>43887</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>43887</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>43894</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>43894</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>43899</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>43900</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>43907</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>43907</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>43909</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>43914</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>43915</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>43916</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>43916</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>43917</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>43929</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>43936</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>43941</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>43949</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>43950</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>43956</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>43963</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>43977</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>43983</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>43984</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>44007</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>44020</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>44032</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>44041</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>44041</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>44047</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>44047</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>44047</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>44048</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>44053</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>44053</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>44055</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>44055</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>44055</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>44055</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44060</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44060</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44061</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44061</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44061</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44062</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44062</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>44074</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>44074</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>44074</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>44075</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>44075</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>44077</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>44082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>44082</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>44084</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>44089</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>44089</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44089</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44089</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44090</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44095</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>44095</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>44095</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>44098</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>44104</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>44104</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>44105</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>44105</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>44109</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>44110</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>44110</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44111</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>44112</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>44112</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>44119</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>44120</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>44126</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44130</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>44131</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>44136</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44138</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>44139</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>44140</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>44141</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>44144</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>44145</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>44145</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>44147</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>44151</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>44151</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>44151</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>44151</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>44151</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44151</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44154</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44159</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44160</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44178</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44182</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>44182</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>44186</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44187</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44188</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>44192</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>44193</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>44193</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>44201</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>44209</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>44210</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>44210</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>44214</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>44214</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>44214</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>44215</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>44217</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>44218</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>44220</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44229</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>44230</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>44230</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>44230</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44230</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44230</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>44230</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44236</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44236</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>44236</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>44236</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>44238</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>44241</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>44243</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>44243</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>44244</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>44264</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>44264</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44267</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44271</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>44271</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>44271</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>44271</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44273</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44273</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>44277</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>44279</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>44280</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>44285</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>44287</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>44301</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>44302</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>44302</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>44312</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>44312</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>44320</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>44322</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>44326</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>44326</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44327</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>44333</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>44336</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>44341</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>44341</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>44342</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>44345</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>44348</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>44351</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>44351</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>44356</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44356</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>44357</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44357</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44363</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44364</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44369</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44371</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44375</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44378</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44379</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44382</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44384</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44385</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44385</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44385</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44386</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44386</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44405</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44407</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44407</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44413</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44417</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44418</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44419</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44421</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44432</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44433</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44434</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44435</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44437</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44438</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>44438</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>44446</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44447</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>44448</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>44448</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>44448</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>44454</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>44454</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>44455</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>44455</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>44456</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>44457</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>44460</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>44461</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>44461</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>44462</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>44467</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>44474</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>44475</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>44475</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>44476</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>44477</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>44477</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>44477</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>44480</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31590,7 +31590,7 @@
         <v>44482</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44482</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44482</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44482</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>44482</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44484</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>44489</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>44489</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>44496</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44497</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>44497</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>44497</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44497</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44498</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44498</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44502</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>44502</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>44502</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>44505</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44511</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>44517</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         <v>44522</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>44522</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>44525</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>44529</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>44531</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44543</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44544</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44544</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44552</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44564</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44564</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44566</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44574</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44581</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44581</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>44581</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44587</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>44588</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44595</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44602</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44615</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>44617</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44617</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44618</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44620</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44620</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44623</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44623</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44625</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44629</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44629</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44636</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44643</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44645</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>44655</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44656</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44659</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>44679</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44679</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44683</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44684</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44686</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44690</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44712</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44712</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44722</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>44732</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44732</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44733</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44740</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44740</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44782</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44782</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44784</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44784</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44790</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44796</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44796</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44804</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>44810</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44810</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44810</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44816</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44818</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44819</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44820</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44823</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44823</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44823</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44823</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>44823</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>44823</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>44824</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44830</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>44831</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>44841</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>44845</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>44846</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>44846</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>44846</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44847</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>44848</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>44851</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>44852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>44852</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>44855</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>44855</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>44855</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44858</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>44858</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>44858</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>44858</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>44858</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>44858</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>44858</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>44861</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38874,7 +38874,7 @@
         <v>44861</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>44862</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>44864</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39045,7 +39045,7 @@
         <v>44865</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>44865</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>44872</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>44874</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>44882</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>44895</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>44895</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44895</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>44895</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39558,7 +39558,7 @@
         <v>44895</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>44901</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>44904</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>44909</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>44909</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>44914</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>44914</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         <v>44914</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>44914</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>44914</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40128,7 +40128,7 @@
         <v>44915</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>44915</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40242,7 +40242,7 @@
         <v>44915</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>44924</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44924</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>44924</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44924</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44930</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>44931</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44939</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>44939</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>44949</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>44949</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>44952</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>44955</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>44959</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41045,7 +41045,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>44963</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>44965</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44965</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>44966</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>44970</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         <v>44971</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>44971</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>44971</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         <v>44973</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>44973</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>44978</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>44979</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41843,7 +41843,7 @@
         <v>44979</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44984</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>44984</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>44984</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>44988</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>44988</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>44991</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>44993</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>44993</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>44993</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>44993</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>44993</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>44994</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>44994</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44994</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45001</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45001</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>45001</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>45001</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>45001</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43023,7 +43023,7 @@
         <v>45001</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>45001</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>45006</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45007</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43308,7 +43308,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>45007</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>45019</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45027</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45028</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45028</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45028</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43764,7 +43764,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>45034</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43878,7 +43878,7 @@
         <v>45036</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43935,7 +43935,7 @@
         <v>45042</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45042</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45044</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45044</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45050</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45058</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45061</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45063</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44396,7 +44396,7 @@
         <v>45067</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>45070</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>45070</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45070</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>45070</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>45071</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>45071</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45071</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>45072</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>45072</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>45075</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>45075</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>45075</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45075</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45075</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45076</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45077</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45082</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45082</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45083</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45086</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>45089</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>45090</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45090</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45090</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45955,7 +45955,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46069,7 +46069,7 @@
         <v>45091</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46126,7 +46126,7 @@
         <v>45091</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
         <v>45092</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46240,7 +46240,7 @@
         <v>45093</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>45093</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45096</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>45096</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45097</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45097</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>45097</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>45097</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45099</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45103</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45103</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45104</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47214,7 +47214,7 @@
         <v>45104</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45104</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47333,7 +47333,7 @@
         <v>45104</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45104</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45104</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45104</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45107</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47618,7 +47618,7 @@
         <v>45110</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45110</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47737,7 +47737,7 @@
         <v>45110</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45113</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45113</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45114</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45114</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45114</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>45114</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45114</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48255,7 +48255,7 @@
         <v>45118</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45118</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48369,7 +48369,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48426,7 +48426,7 @@
         <v>45118</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48540,7 +48540,7 @@
         <v>45118</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48597,7 +48597,7 @@
         <v>45118</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45119</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48711,7 +48711,7 @@
         <v>45119</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>45119</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>45125</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>45125</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45125</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>45125</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45126</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45126</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>45131</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45134</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>45141</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45145</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>45146</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49452,7 +49452,7 @@
         <v>45146</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>45148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>45148</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>45148</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45148</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49794,7 +49794,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49851,7 +49851,7 @@
         <v>45149</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49908,7 +49908,7 @@
         <v>45153</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49965,7 +49965,7 @@
         <v>45153</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50022,7 +50022,7 @@
         <v>45153</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>45153</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50136,7 +50136,7 @@
         <v>45153</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50193,7 +50193,7 @@
         <v>45154</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50250,7 +50250,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45156</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50421,7 +50421,7 @@
         <v>45159</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50478,7 +50478,7 @@
         <v>45161</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>45161</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45163</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50669,7 +50669,7 @@
         <v>45163</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>45165</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50783,7 +50783,7 @@
         <v>45166</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50840,7 +50840,7 @@
         <v>45167</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>45167</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         <v>45167</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51011,7 +51011,7 @@
         <v>45169</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45169</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45169</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45169</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45169</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45170</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45170</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45173</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51581,7 +51581,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51638,7 +51638,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51695,7 +51695,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51752,7 +51752,7 @@
         <v>45173</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45174</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51866,7 +51866,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51980,7 +51980,7 @@
         <v>45180</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45180</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45180</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45180</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>45181</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52265,7 +52265,7 @@
         <v>45182</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52322,7 +52322,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>45182</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52436,7 +52436,7 @@
         <v>45183</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>45188</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45189</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45189</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45190</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45190</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45194</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45195</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53006,7 +53006,7 @@
         <v>45198</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53063,7 +53063,7 @@
         <v>45198</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45202</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45202</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45202</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45202</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45205</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45205</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45205</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45205</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45205</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45208</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45208</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45209</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45209</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45209</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>45212</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45212</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45212</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45212</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45215</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45218</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45218</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45218</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45219</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45219</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45219</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45219</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45222</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45223</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45223</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45226</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45229</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45229</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45229</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45229</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45229</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45229</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55229,7 +55229,7 @@
         <v>45230</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>45230</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>45232</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>45232</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55457,7 +55457,7 @@
         <v>45233</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55514,7 +55514,7 @@
         <v>45233</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55571,7 +55571,7 @@
         <v>45233</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55628,7 +55628,7 @@
         <v>45233</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55685,7 +55685,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>45233</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>45233</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55856,7 +55856,7 @@
         <v>45233</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55913,7 +55913,7 @@
         <v>45233</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55970,7 +55970,7 @@
         <v>45236</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56027,7 +56027,7 @@
         <v>45237</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56084,7 +56084,7 @@
         <v>45239</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56146,7 +56146,7 @@
         <v>45243</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56203,7 +56203,7 @@
         <v>45243</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56260,7 +56260,7 @@
         <v>45244</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56317,7 +56317,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56374,7 +56374,7 @@
         <v>45246</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56431,7 +56431,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56545,7 +56545,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56602,7 +56602,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45246</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56716,7 +56716,7 @@
         <v>45246</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56773,7 +56773,7 @@
         <v>45247</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>45250</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56887,7 +56887,7 @@
         <v>45250</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45252</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57001,7 +57001,7 @@
         <v>45252</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45252</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45254</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57229,7 +57229,7 @@
         <v>45254</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>45254</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57343,7 +57343,7 @@
         <v>45254</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>45260</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45260</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>45261</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57628,7 +57628,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57705,7 +57705,7 @@
         <v>45264</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57762,7 +57762,7 @@
         <v>45266</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45267</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57876,7 +57876,7 @@
         <v>45268</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57933,7 +57933,7 @@
         <v>45268</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57990,7 +57990,7 @@
         <v>45268</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58047,7 +58047,7 @@
         <v>45271</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>45271</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58161,7 +58161,7 @@
         <v>45272</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58218,7 +58218,7 @@
         <v>45272</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58275,7 +58275,7 @@
         <v>45272</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45273</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58503,7 +58503,7 @@
         <v>45274</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45281</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58617,7 +58617,7 @@
         <v>45286</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58674,7 +58674,7 @@
         <v>45301</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58731,7 +58731,7 @@
         <v>45302</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58788,7 +58788,7 @@
         <v>45306</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58845,7 +58845,7 @@
         <v>45306</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>45307</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58964,7 +58964,7 @@
         <v>45307</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59021,7 +59021,7 @@
         <v>45307</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59078,7 +59078,7 @@
         <v>45308</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>45308</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59192,7 +59192,7 @@
         <v>45313</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59249,7 +59249,7 @@
         <v>45313</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59306,7 +59306,7 @@
         <v>45313</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59363,7 +59363,7 @@
         <v>45313</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59420,7 +59420,7 @@
         <v>45314</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59477,7 +59477,7 @@
         <v>45314</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59534,7 +59534,7 @@
         <v>45314</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59591,7 +59591,7 @@
         <v>45314</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59648,7 +59648,7 @@
         <v>45314</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59705,7 +59705,7 @@
         <v>45319</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59762,7 +59762,7 @@
         <v>45323</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59819,7 +59819,7 @@
         <v>45323</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59876,7 +59876,7 @@
         <v>45323</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59933,7 +59933,7 @@
         <v>45324</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59990,7 +59990,7 @@
         <v>45324</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60047,7 +60047,7 @@
         <v>45327</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60104,7 +60104,7 @@
         <v>45327</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60161,7 +60161,7 @@
         <v>45329</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60218,7 +60218,7 @@
         <v>45329</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60275,7 +60275,7 @@
         <v>45331</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60332,7 +60332,7 @@
         <v>45331</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60389,7 +60389,7 @@
         <v>45331</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60446,7 +60446,7 @@
         <v>45334</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60503,7 +60503,7 @@
         <v>45335</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>45335</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60622,7 +60622,7 @@
         <v>45335</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60684,7 +60684,7 @@
         <v>45335</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60746,7 +60746,7 @@
         <v>45335</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60803,7 +60803,7 @@
         <v>45335</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60865,7 +60865,7 @@
         <v>45335</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60927,7 +60927,7 @@
         <v>45336</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60984,7 +60984,7 @@
         <v>45336</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61041,7 +61041,7 @@
         <v>45336</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61098,7 +61098,7 @@
         <v>45336</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61155,7 +61155,7 @@
         <v>45337</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61212,7 +61212,7 @@
         <v>45337</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45338</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61326,7 +61326,7 @@
         <v>45338</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61383,7 +61383,7 @@
         <v>45341</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61440,7 +61440,7 @@
         <v>45341</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>45341</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61554,7 +61554,7 @@
         <v>45344</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61611,7 +61611,7 @@
         <v>45345</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61668,7 +61668,7 @@
         <v>45349</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61725,7 +61725,7 @@
         <v>45349</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61782,7 +61782,7 @@
         <v>45351</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61839,7 +61839,7 @@
         <v>45356</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61896,7 +61896,7 @@
         <v>45356</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61953,7 +61953,7 @@
         <v>45362</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -62010,7 +62010,7 @@
         <v>45363</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -62067,7 +62067,7 @@
         <v>45363</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -62124,7 +62124,7 @@
         <v>45363</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62181,7 +62181,7 @@
         <v>45363</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62258,7 +62258,7 @@
         <v>45363</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62315,7 +62315,7 @@
         <v>45363</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62372,7 +62372,7 @@
         <v>45364</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>45364</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62486,7 +62486,7 @@
         <v>45364</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45370</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>45372</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62657,7 +62657,7 @@
         <v>45378</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62714,7 +62714,7 @@
         <v>45378</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62771,7 +62771,7 @@
         <v>45378</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62828,7 +62828,7 @@
         <v>45384</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62885,7 +62885,7 @@
         <v>45384</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62942,7 +62942,7 @@
         <v>45384</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62999,7 +62999,7 @@
         <v>45385</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -63061,7 +63061,7 @@
         <v>45385</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -63118,7 +63118,7 @@
         <v>45387</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -63175,7 +63175,7 @@
         <v>45387</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63232,7 +63232,7 @@
         <v>45387</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63289,7 +63289,7 @@
         <v>45387</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63346,7 +63346,7 @@
         <v>45387</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63403,7 +63403,7 @@
         <v>45391</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63460,7 +63460,7 @@
         <v>45398</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63517,7 +63517,7 @@
         <v>45400</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63574,7 +63574,7 @@
         <v>45400</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63631,7 +63631,7 @@
         <v>45400</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63688,7 +63688,7 @@
         <v>45401</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63745,7 +63745,7 @@
         <v>45401</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63802,7 +63802,7 @@
         <v>45402</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63864,7 +63864,7 @@
         <v>45404</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63921,7 +63921,7 @@
         <v>45406</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63978,7 +63978,7 @@
         <v>45407</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -64035,7 +64035,7 @@
         <v>45411</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45411</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45412</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>45412</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64263,7 +64263,7 @@
         <v>45414</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64320,7 +64320,7 @@
         <v>45418</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64377,7 +64377,7 @@
         <v>45420</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64434,7 +64434,7 @@
         <v>45429</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>45429</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64548,7 +64548,7 @@
         <v>45433</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64605,7 +64605,7 @@
         <v>45439</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64662,7 +64662,7 @@
         <v>45441</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64719,7 +64719,7 @@
         <v>45441</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64776,7 +64776,7 @@
         <v>45442</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64833,7 +64833,7 @@
         <v>45443</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64890,7 +64890,7 @@
         <v>45443</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64947,7 +64947,7 @@
         <v>45446</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -65004,7 +65004,7 @@
         <v>45453</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -65061,7 +65061,7 @@
         <v>45454</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>45454</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -65175,7 +65175,7 @@
         <v>45454</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65237,7 +65237,7 @@
         <v>45460</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>45460</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -65351,7 +65351,7 @@
         <v>45460</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -65408,7 +65408,7 @@
         <v>45462</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -65465,7 +65465,7 @@
         <v>45462</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -65522,7 +65522,7 @@
         <v>45463</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -65579,7 +65579,7 @@
         <v>45463</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -65636,7 +65636,7 @@
         <v>45470</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -65693,7 +65693,7 @@
         <v>45476</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -65750,7 +65750,7 @@
         <v>45478</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -65807,7 +65807,7 @@
         <v>45478</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -65864,7 +65864,7 @@
         <v>45488</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -65921,7 +65921,7 @@
         <v>45488</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -65978,7 +65978,7 @@
         <v>45489</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -66035,7 +66035,7 @@
         <v>45491</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -66092,7 +66092,7 @@
         <v>45492</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -66149,7 +66149,7 @@
         <v>45492</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -66206,7 +66206,7 @@
         <v>45503</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45507</v>
+        <v>45508</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45385</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>44237</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44245</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44785</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44439</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44489</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>44454</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>44476</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>44979</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>44558</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>44958</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>43591</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>43643</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>43686</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>44057</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>44876</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>45324</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45343</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>43613</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>43640</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>44489</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>44575</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>44785</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>44827</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>44853</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45118</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>45254</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>43674</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>43719</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>43796</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44302</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>44369</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44785</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44802</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>44896</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>44951</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>45105</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>45105</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45125</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43605</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>43614</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>43680</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>43717</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>43731</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>43734</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>43854</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>43927</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>43928</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>43999</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44053</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44069</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>44103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>44152</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>44246</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44260</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44279</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44378</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>44466</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44482</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>44487</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44489</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>44517</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44575</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44726</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>44830</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44915</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>44928</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44931</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44949</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>44991</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>45007</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>45042</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>45063</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45069</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>45117</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>45119</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>45167</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>45243</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45275</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>45324</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45362</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>45475</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>43556</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>43558</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>43558</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>43559</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>43566</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>43567</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>43570</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>43581</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>43581</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>43584</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>43585</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>43587</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>43591</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>43591</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43592</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43600</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43605</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43612</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43612</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43613</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43613</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43613</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43613</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43620</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43625</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43629</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43634</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43634</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43640</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43640</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43640</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43640</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>43643</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>43648</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>43656</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>43662</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>43668</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>43668</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>43668</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>43668</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>43675</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43678</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>43679</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43680</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43680</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>43680</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>43680</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>43681</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>43683</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>43683</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>43683</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>43684</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>43689</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>43689</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>43691</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>43691</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43691</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43691</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43691</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43692</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43693</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>43696</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>43698</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>43698</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>43699</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>43699</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>43702</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>43703</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>43704</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>43704</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>43705</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>43705</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>43705</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>43706</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>43707</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>43710</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>43711</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>43712</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>43712</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>43714</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>43717</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>43717</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>43717</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>43717</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>43718</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>43718</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43718</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43718</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43719</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>43719</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>43720</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>43721</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>43721</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>43724</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>43726</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>43727</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>43727</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>43727</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>43728</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>43728</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>43732</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>43733</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>43746</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>43749</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>43755</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>43756</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>43756</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>43761</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>43763</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>43763</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>43763</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>43766</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>43769</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>43774</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>43776</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>43776</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>43777</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43777</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43777</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43777</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43780</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43780</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43782</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>43784</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>43784</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>43784</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43784</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>43787</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>43791</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>43796</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>43796</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>43803</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>43803</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>43803</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>43815</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>43815</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>43815</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>43815</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>43817</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>43829</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>43832</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>43832</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>43832</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>43832</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>43832</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>43832</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>43832</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>43832</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>43840</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>43844</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>43846</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>43846</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>43859</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>43865</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43865</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>43867</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>43867</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>43867</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>43871</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>43871</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>43872</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>43873</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>43873</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>43873</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>43875</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>43875</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>43880</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>43881</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>43886</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>43887</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>43887</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>43887</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>43894</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>43894</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>43899</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>43900</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>43907</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>43907</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>43909</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>43914</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>43915</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>43916</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>43916</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>43917</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>43929</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>43936</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>43941</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>43949</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>43950</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>43956</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>43963</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>43977</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>43983</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>43984</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>44007</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>44020</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>44032</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>44041</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>44041</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>44047</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>44047</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>44047</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>44048</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>44053</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>44053</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>44055</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>44055</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>44055</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>44055</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44060</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44060</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44061</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44061</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44061</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44062</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44062</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>44074</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>44074</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>44074</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>44075</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>44075</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>44077</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>44082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>44082</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>44084</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>44089</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>44089</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44089</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44089</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44090</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44095</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>44095</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>44095</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>44098</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>44104</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>44104</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>44105</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>44105</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>44109</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>44110</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>44110</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44111</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>44112</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>44112</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>44119</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>44120</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>44126</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44130</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>44131</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>44136</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44138</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>44139</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>44140</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>44141</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>44144</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>44145</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>44145</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>44147</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>44151</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>44151</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>44151</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>44151</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>44151</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44151</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44154</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44159</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44160</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44178</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44182</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>44182</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>44186</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44187</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44188</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>44192</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>44193</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>44193</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>44201</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>44209</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>44210</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>44210</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>44214</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>44214</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>44214</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>44215</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>44217</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>44218</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>44220</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44229</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>44230</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>44230</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>44230</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44230</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44230</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>44230</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44236</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44236</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>44236</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>44236</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>44238</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>44241</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>44243</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>44243</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>44244</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>44264</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>44264</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44267</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44271</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>44271</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>44271</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>44271</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44273</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44273</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>44277</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>44279</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>44280</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>44285</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>44287</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>44301</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>44302</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>44302</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>44312</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>44312</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>44320</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>44322</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>44326</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>44326</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44327</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>44333</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>44336</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>44341</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>44341</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>44342</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>44345</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>44348</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>44351</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>44351</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>44356</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44356</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>44357</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44357</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44363</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44364</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44369</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44371</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44375</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44378</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44379</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44382</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44384</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44385</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44385</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44385</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44386</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44386</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44405</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44407</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44407</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44413</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44417</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44418</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44419</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44421</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44432</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44433</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44434</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44435</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44437</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44438</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>44438</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>44446</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44447</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>44448</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>44448</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>44448</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>44454</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>44454</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>44455</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>44455</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>44456</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>44457</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>44460</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>44461</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>44461</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>44462</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>44467</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>44474</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>44475</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>44475</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>44476</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>44477</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>44477</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>44477</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>44480</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31590,7 +31590,7 @@
         <v>44482</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44482</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44482</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44482</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>44482</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44484</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>44489</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>44489</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>44496</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44497</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>44497</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>44497</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44497</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44498</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44498</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44502</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>44502</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>44502</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>44505</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44511</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>44517</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         <v>44522</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>44522</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>44525</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>44529</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>44531</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44543</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44544</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44544</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44552</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44564</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44564</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44566</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44574</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44581</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44581</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>44581</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44587</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>44588</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44595</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44602</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44615</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>44617</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44617</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44618</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44620</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44620</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44623</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44623</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44625</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44629</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44629</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44636</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44643</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44645</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>44655</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44656</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44659</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>44679</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44679</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44683</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44684</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44686</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44690</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44712</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44712</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44722</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>44732</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44732</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44733</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44740</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44740</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44782</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44782</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44784</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44784</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44790</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44796</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44796</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44804</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>44810</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44810</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44810</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44816</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44818</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44819</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44820</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44823</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44823</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44823</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44823</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>44823</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>44823</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>44824</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44830</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>44831</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>44841</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>44845</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>44846</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>44846</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>44846</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44847</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>44848</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>44851</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>44852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>44852</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>44855</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>44855</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>44855</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44858</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>44858</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>44858</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>44858</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>44858</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>44858</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>44858</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>44861</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38874,7 +38874,7 @@
         <v>44861</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>44862</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>44864</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39045,7 +39045,7 @@
         <v>44865</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>44865</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>44872</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>44874</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>44882</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>44895</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>44895</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44895</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>44895</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39558,7 +39558,7 @@
         <v>44895</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>44901</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>44904</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>44909</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>44909</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>44914</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>44914</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         <v>44914</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>44914</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>44914</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40128,7 +40128,7 @@
         <v>44915</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>44915</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40242,7 +40242,7 @@
         <v>44915</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>44924</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44924</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>44924</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44924</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44930</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>44931</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44939</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>44939</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>44949</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>44949</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>44952</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>44955</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>44959</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41045,7 +41045,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>44963</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>44965</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44965</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>44966</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>44970</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         <v>44971</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>44971</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>44971</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         <v>44973</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>44973</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>44978</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>44979</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41843,7 +41843,7 @@
         <v>44979</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44984</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>44984</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>44984</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>44988</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>44988</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>44991</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>44993</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>44993</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>44993</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>44993</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>44993</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>44994</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>44994</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44994</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45001</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45001</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>45001</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>45001</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>45001</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43023,7 +43023,7 @@
         <v>45001</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>45001</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>45006</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45007</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43308,7 +43308,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>45007</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>45019</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45027</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45028</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45028</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45028</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43764,7 +43764,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>45034</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43878,7 +43878,7 @@
         <v>45036</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43935,7 +43935,7 @@
         <v>45042</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45042</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45044</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45044</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45050</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45058</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45061</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45063</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44396,7 +44396,7 @@
         <v>45067</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>45070</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>45070</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45070</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>45070</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>45071</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>45071</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45071</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>45072</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>45072</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>45075</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>45075</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>45075</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45075</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45075</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45076</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45077</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45082</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45082</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45083</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45086</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>45089</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>45090</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45090</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45090</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45955,7 +45955,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46069,7 +46069,7 @@
         <v>45091</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46126,7 +46126,7 @@
         <v>45091</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
         <v>45092</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46240,7 +46240,7 @@
         <v>45093</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>45093</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45096</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>45096</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45097</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45097</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>45097</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>45097</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45099</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45103</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45103</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45104</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47214,7 +47214,7 @@
         <v>45104</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45104</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47333,7 +47333,7 @@
         <v>45104</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45104</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45104</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45104</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45107</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47618,7 +47618,7 @@
         <v>45110</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45110</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47737,7 +47737,7 @@
         <v>45110</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45113</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45113</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45114</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45114</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45114</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>45114</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45114</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48255,7 +48255,7 @@
         <v>45118</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45118</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48369,7 +48369,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48426,7 +48426,7 @@
         <v>45118</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48540,7 +48540,7 @@
         <v>45118</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48597,7 +48597,7 @@
         <v>45118</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45119</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48711,7 +48711,7 @@
         <v>45119</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>45119</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>45125</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>45125</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45125</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>45125</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45126</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45126</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>45131</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45134</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>45141</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45145</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>45146</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49452,7 +49452,7 @@
         <v>45146</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>45148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>45148</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>45148</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45148</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49794,7 +49794,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49851,7 +49851,7 @@
         <v>45149</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49908,7 +49908,7 @@
         <v>45153</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49965,7 +49965,7 @@
         <v>45153</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50022,7 +50022,7 @@
         <v>45153</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>45153</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50136,7 +50136,7 @@
         <v>45153</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50193,7 +50193,7 @@
         <v>45154</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50250,7 +50250,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45156</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50421,7 +50421,7 @@
         <v>45159</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50478,7 +50478,7 @@
         <v>45161</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>45161</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45163</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50669,7 +50669,7 @@
         <v>45163</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>45165</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50783,7 +50783,7 @@
         <v>45166</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50840,7 +50840,7 @@
         <v>45167</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>45167</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         <v>45167</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51011,7 +51011,7 @@
         <v>45169</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45169</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45169</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45169</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45169</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45170</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45170</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45173</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51581,7 +51581,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51638,7 +51638,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51695,7 +51695,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51752,7 +51752,7 @@
         <v>45173</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45174</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51866,7 +51866,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51980,7 +51980,7 @@
         <v>45180</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45180</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45180</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45180</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>45181</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52265,7 +52265,7 @@
         <v>45182</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52322,7 +52322,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>45182</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52436,7 +52436,7 @@
         <v>45183</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>45188</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45189</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45189</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45190</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45190</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45194</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45195</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53006,7 +53006,7 @@
         <v>45198</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53063,7 +53063,7 @@
         <v>45198</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45202</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45202</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45202</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45202</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45205</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45205</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45205</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45205</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45205</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45208</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45208</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45209</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45209</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45209</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>45212</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45212</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45212</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45212</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45215</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45218</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45218</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45218</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45219</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45219</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45219</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45219</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45222</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45223</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45223</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45226</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45229</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45229</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45229</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45229</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45229</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45229</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55229,7 +55229,7 @@
         <v>45230</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>45230</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>45232</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>45232</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55457,7 +55457,7 @@
         <v>45233</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55514,7 +55514,7 @@
         <v>45233</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55571,7 +55571,7 @@
         <v>45233</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55628,7 +55628,7 @@
         <v>45233</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55685,7 +55685,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>45233</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>45233</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55856,7 +55856,7 @@
         <v>45233</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55913,7 +55913,7 @@
         <v>45233</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55970,7 +55970,7 @@
         <v>45236</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56027,7 +56027,7 @@
         <v>45237</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56084,7 +56084,7 @@
         <v>45239</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56146,7 +56146,7 @@
         <v>45243</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56203,7 +56203,7 @@
         <v>45243</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56260,7 +56260,7 @@
         <v>45244</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56317,7 +56317,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56374,7 +56374,7 @@
         <v>45246</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56431,7 +56431,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56545,7 +56545,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56602,7 +56602,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45246</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56716,7 +56716,7 @@
         <v>45246</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56773,7 +56773,7 @@
         <v>45247</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>45250</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56887,7 +56887,7 @@
         <v>45250</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45252</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57001,7 +57001,7 @@
         <v>45252</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45252</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45254</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57229,7 +57229,7 @@
         <v>45254</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>45254</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57343,7 +57343,7 @@
         <v>45254</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>45260</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45260</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>45261</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57628,7 +57628,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57705,7 +57705,7 @@
         <v>45264</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57762,7 +57762,7 @@
         <v>45266</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45267</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57876,7 +57876,7 @@
         <v>45268</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57933,7 +57933,7 @@
         <v>45268</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57990,7 +57990,7 @@
         <v>45268</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58047,7 +58047,7 @@
         <v>45271</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>45271</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58161,7 +58161,7 @@
         <v>45272</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58218,7 +58218,7 @@
         <v>45272</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58275,7 +58275,7 @@
         <v>45272</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45273</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58503,7 +58503,7 @@
         <v>45274</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45281</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58617,7 +58617,7 @@
         <v>45286</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58674,7 +58674,7 @@
         <v>45301</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58731,7 +58731,7 @@
         <v>45302</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58788,7 +58788,7 @@
         <v>45306</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58845,7 +58845,7 @@
         <v>45306</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>45307</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58964,7 +58964,7 @@
         <v>45307</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59021,7 +59021,7 @@
         <v>45307</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59078,7 +59078,7 @@
         <v>45308</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>45308</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59192,7 +59192,7 @@
         <v>45313</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59249,7 +59249,7 @@
         <v>45313</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59306,7 +59306,7 @@
         <v>45313</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59363,7 +59363,7 @@
         <v>45313</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59420,7 +59420,7 @@
         <v>45314</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59477,7 +59477,7 @@
         <v>45314</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59534,7 +59534,7 @@
         <v>45314</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59591,7 +59591,7 @@
         <v>45314</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59648,7 +59648,7 @@
         <v>45314</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59705,7 +59705,7 @@
         <v>45319</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59762,7 +59762,7 @@
         <v>45323</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59819,7 +59819,7 @@
         <v>45323</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59876,7 +59876,7 @@
         <v>45323</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59933,7 +59933,7 @@
         <v>45324</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59990,7 +59990,7 @@
         <v>45324</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60047,7 +60047,7 @@
         <v>45327</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60104,7 +60104,7 @@
         <v>45327</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60161,7 +60161,7 @@
         <v>45329</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60218,7 +60218,7 @@
         <v>45329</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60275,7 +60275,7 @@
         <v>45331</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60332,7 +60332,7 @@
         <v>45331</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60389,7 +60389,7 @@
         <v>45331</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60446,7 +60446,7 @@
         <v>45334</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60503,7 +60503,7 @@
         <v>45335</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>45335</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60622,7 +60622,7 @@
         <v>45335</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60684,7 +60684,7 @@
         <v>45335</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60746,7 +60746,7 @@
         <v>45335</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60803,7 +60803,7 @@
         <v>45335</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60865,7 +60865,7 @@
         <v>45335</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60927,7 +60927,7 @@
         <v>45336</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60984,7 +60984,7 @@
         <v>45336</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61041,7 +61041,7 @@
         <v>45336</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61098,7 +61098,7 @@
         <v>45336</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61155,7 +61155,7 @@
         <v>45337</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61212,7 +61212,7 @@
         <v>45337</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45338</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61326,7 +61326,7 @@
         <v>45338</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61383,7 +61383,7 @@
         <v>45341</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61440,7 +61440,7 @@
         <v>45341</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>45341</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61554,7 +61554,7 @@
         <v>45344</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61611,7 +61611,7 @@
         <v>45345</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61668,7 +61668,7 @@
         <v>45349</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61725,7 +61725,7 @@
         <v>45349</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61782,7 +61782,7 @@
         <v>45351</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61839,7 +61839,7 @@
         <v>45356</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61896,7 +61896,7 @@
         <v>45356</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61953,7 +61953,7 @@
         <v>45362</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -62010,7 +62010,7 @@
         <v>45363</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -62067,7 +62067,7 @@
         <v>45363</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -62124,7 +62124,7 @@
         <v>45363</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62181,7 +62181,7 @@
         <v>45363</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62258,7 +62258,7 @@
         <v>45363</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62315,7 +62315,7 @@
         <v>45363</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62372,7 +62372,7 @@
         <v>45364</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>45364</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62486,7 +62486,7 @@
         <v>45364</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45370</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>45372</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62657,7 +62657,7 @@
         <v>45378</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62714,7 +62714,7 @@
         <v>45378</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62771,7 +62771,7 @@
         <v>45378</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62828,7 +62828,7 @@
         <v>45384</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62885,7 +62885,7 @@
         <v>45384</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62942,7 +62942,7 @@
         <v>45384</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62999,7 +62999,7 @@
         <v>45385</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -63061,7 +63061,7 @@
         <v>45385</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -63118,7 +63118,7 @@
         <v>45387</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -63175,7 +63175,7 @@
         <v>45387</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63232,7 +63232,7 @@
         <v>45387</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63289,7 +63289,7 @@
         <v>45387</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63346,7 +63346,7 @@
         <v>45387</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63403,7 +63403,7 @@
         <v>45391</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63460,7 +63460,7 @@
         <v>45398</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63517,7 +63517,7 @@
         <v>45400</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63574,7 +63574,7 @@
         <v>45400</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63631,7 +63631,7 @@
         <v>45400</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63688,7 +63688,7 @@
         <v>45401</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63745,7 +63745,7 @@
         <v>45401</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63802,7 +63802,7 @@
         <v>45402</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63864,7 +63864,7 @@
         <v>45404</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63921,7 +63921,7 @@
         <v>45406</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63978,7 +63978,7 @@
         <v>45407</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -64035,7 +64035,7 @@
         <v>45411</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45411</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45412</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>45412</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64263,7 +64263,7 @@
         <v>45414</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64320,7 +64320,7 @@
         <v>45418</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64377,7 +64377,7 @@
         <v>45420</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64434,7 +64434,7 @@
         <v>45429</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>45429</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64548,7 +64548,7 @@
         <v>45433</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64605,7 +64605,7 @@
         <v>45439</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64662,7 +64662,7 @@
         <v>45441</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64719,7 +64719,7 @@
         <v>45441</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64776,7 +64776,7 @@
         <v>45442</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64833,7 +64833,7 @@
         <v>45443</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64890,7 +64890,7 @@
         <v>45443</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64947,7 +64947,7 @@
         <v>45446</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -65004,7 +65004,7 @@
         <v>45453</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -65061,7 +65061,7 @@
         <v>45454</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>45454</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -65175,7 +65175,7 @@
         <v>45454</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65237,7 +65237,7 @@
         <v>45460</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>45460</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -65351,7 +65351,7 @@
         <v>45460</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -65408,7 +65408,7 @@
         <v>45462</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -65465,7 +65465,7 @@
         <v>45462</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -65522,7 +65522,7 @@
         <v>45463</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -65579,7 +65579,7 @@
         <v>45463</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -65636,7 +65636,7 @@
         <v>45470</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -65693,7 +65693,7 @@
         <v>45476</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -65750,7 +65750,7 @@
         <v>45478</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -65807,7 +65807,7 @@
         <v>45478</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -65864,7 +65864,7 @@
         <v>45488</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -65921,7 +65921,7 @@
         <v>45488</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -65978,7 +65978,7 @@
         <v>45489</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -66035,7 +66035,7 @@
         <v>45491</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -66085,14 +66085,14 @@
     <row r="1099" ht="15" customHeight="1">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>A 30507-2024</t>
+          <t>A 30504-2024</t>
         </is>
       </c>
       <c r="B1099" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -66105,7 +66105,7 @@
         </is>
       </c>
       <c r="G1099" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="H1099" t="n">
         <v>0</v>
@@ -66142,14 +66142,14 @@
     <row r="1100" ht="15" customHeight="1">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>A 30504-2024</t>
+          <t>A 30507-2024</t>
         </is>
       </c>
       <c r="B1100" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -66162,7 +66162,7 @@
         </is>
       </c>
       <c r="G1100" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="H1100" t="n">
         <v>0</v>
@@ -66206,7 +66206,7 @@
         <v>45503</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45508</v>
+        <v>45509</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45385</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>44237</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44245</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44785</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44439</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44489</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>44454</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>44476</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>44979</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>44558</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>44958</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>43591</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>43643</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>43686</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>44057</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>44876</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>45324</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45343</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>43613</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>43640</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>44489</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>44575</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>44785</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>44827</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>44853</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45118</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>45254</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>43674</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>43719</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>43796</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44302</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>44369</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44785</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44802</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>44896</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>44951</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>45105</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>45105</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45125</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43605</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>43614</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>43680</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>43717</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>43731</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>43734</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>43854</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>43927</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>43928</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>43999</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44053</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44069</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>44103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>44152</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>44246</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44260</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44279</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44378</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>44466</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44482</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>44487</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44489</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>44517</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44575</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44726</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>44830</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44915</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>44928</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44931</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44949</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>44991</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>45007</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>45042</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>45063</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45069</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>45117</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>45119</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>45167</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>45243</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45275</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>45324</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45362</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>45475</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>43556</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>43558</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>43558</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>43559</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>43566</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>43567</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>43570</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>43581</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>43581</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>43584</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>43585</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>43587</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>43591</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>43591</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43592</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43600</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43605</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43612</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43612</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43613</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43613</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43613</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43613</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43620</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43625</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43629</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43634</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43634</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43640</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43640</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43640</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43640</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>43643</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>43648</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>43656</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>43662</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>43668</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>43668</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>43668</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>43668</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>43675</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43678</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>43679</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43680</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43680</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>43680</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>43680</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>43681</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>43683</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>43683</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>43683</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>43684</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>43689</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>43689</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>43691</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>43691</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43691</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43691</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43691</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43692</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43693</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>43696</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>43698</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>43698</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>43699</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>43699</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>43702</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>43703</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>43704</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>43704</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>43705</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>43705</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>43705</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>43706</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>43707</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>43710</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>43711</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>43712</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>43712</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>43714</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>43717</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>43717</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>43717</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>43717</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>43718</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>43718</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43718</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43718</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43719</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>43719</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>43720</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>43721</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>43721</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>43724</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>43726</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>43727</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>43727</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>43727</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>43728</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>43728</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>43732</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>43733</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>43746</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>43749</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>43755</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>43756</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>43756</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>43761</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>43763</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>43763</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>43763</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>43766</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>43769</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>43774</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>43776</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>43776</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>43777</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43777</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43777</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43777</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43780</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43780</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43782</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>43784</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>43784</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>43784</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43784</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>43787</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>43791</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>43796</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>43796</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>43803</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>43803</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>43803</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>43815</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>43815</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>43815</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>43815</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>43817</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>43829</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>43832</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>43832</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>43832</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>43832</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>43832</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>43832</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>43832</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>43832</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>43840</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>43844</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>43846</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>43846</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>43859</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>43865</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43865</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>43867</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>43867</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>43867</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>43871</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>43871</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>43872</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>43873</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>43873</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>43873</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>43875</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>43875</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>43880</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>43881</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>43886</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>43887</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>43887</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>43887</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>43894</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>43894</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>43899</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>43900</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>43907</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>43907</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>43909</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>43914</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>43915</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>43916</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>43916</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>43917</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>43929</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>43936</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>43941</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>43949</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>43950</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>43956</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>43963</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>43977</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>43983</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>43984</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>44007</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>44020</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>44032</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>44041</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>44041</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>44047</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>44047</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>44047</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>44048</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>44053</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>44053</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>44055</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>44055</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>44055</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>44055</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44060</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44060</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44061</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44061</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44061</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44062</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44062</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>44074</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>44074</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>44074</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>44075</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>44075</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>44077</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>44082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>44082</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>44084</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>44089</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>44089</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44089</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44089</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44090</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44095</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>44095</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>44095</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>44098</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>44104</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>44104</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>44105</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>44105</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>44109</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>44110</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>44110</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44111</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>44112</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>44112</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>44119</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>44120</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>44126</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44130</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>44131</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>44136</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44138</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>44139</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>44140</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>44141</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>44144</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>44145</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>44145</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>44147</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>44151</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>44151</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>44151</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>44151</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>44151</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44151</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44154</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44159</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44160</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44178</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44182</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>44182</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>44186</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44187</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44188</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>44192</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>44193</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>44193</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>44201</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>44209</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>44210</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>44210</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>44214</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>44214</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>44214</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>44215</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>44217</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>44218</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>44220</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44229</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>44230</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>44230</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>44230</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44230</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44230</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>44230</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44236</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44236</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>44236</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>44236</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>44238</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>44241</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>44243</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>44243</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>44244</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>44264</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>44264</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44267</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44271</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>44271</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>44271</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>44271</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44273</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44273</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>44277</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>44279</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>44280</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>44285</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>44287</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>44301</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>44302</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>44302</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>44312</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>44312</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>44320</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>44322</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>44326</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>44326</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44327</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>44333</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>44336</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>44341</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>44341</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>44342</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>44345</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>44348</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>44351</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>44351</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>44356</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44356</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>44357</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44357</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44363</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44364</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44369</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44371</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44375</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44378</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44379</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44382</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44384</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44385</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44385</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44385</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44386</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44386</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44405</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44407</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44407</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44413</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44417</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44418</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44419</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44421</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44432</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44433</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44434</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44435</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44437</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44438</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>44438</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>44446</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44447</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>44448</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>44448</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>44448</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>44454</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>44454</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>44455</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>44455</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>44456</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>44457</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>44460</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>44461</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>44461</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>44462</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>44467</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>44474</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>44475</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>44475</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>44476</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>44477</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>44477</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>44477</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>44480</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31590,7 +31590,7 @@
         <v>44482</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44482</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44482</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44482</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>44482</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44484</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>44489</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>44489</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>44496</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44497</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>44497</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>44497</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44497</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44498</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44498</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44502</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>44502</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>44502</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>44505</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44511</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>44517</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         <v>44522</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>44522</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>44525</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>44529</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>44531</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44543</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44544</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44544</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44552</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44564</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44564</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44566</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44574</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44581</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44581</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>44581</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44587</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>44588</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44595</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44602</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44615</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>44617</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44617</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44618</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44620</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44620</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44623</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44623</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44625</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44629</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44629</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44636</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44643</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44645</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>44655</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44656</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44659</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>44679</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44679</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44683</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44684</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44686</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44690</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44712</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44712</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44722</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>44732</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44732</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44733</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44740</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44740</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44782</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44782</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44784</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44784</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44790</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44796</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44796</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44804</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>44810</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44810</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44810</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44816</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44818</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44819</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44820</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44823</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44823</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44823</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44823</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>44823</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>44823</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>44824</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44830</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>44831</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>44841</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>44845</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>44846</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>44846</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>44846</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44847</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>44848</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>44851</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>44852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>44852</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>44855</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>44855</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>44855</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44858</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>44858</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>44858</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>44858</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>44858</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>44858</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>44858</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>44861</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38874,7 +38874,7 @@
         <v>44861</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>44862</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>44864</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39045,7 +39045,7 @@
         <v>44865</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>44865</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>44872</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>44874</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>44882</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>44895</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>44895</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44895</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>44895</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39558,7 +39558,7 @@
         <v>44895</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>44901</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>44904</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>44909</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>44909</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>44914</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>44914</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         <v>44914</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>44914</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>44914</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40128,7 +40128,7 @@
         <v>44915</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>44915</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40242,7 +40242,7 @@
         <v>44915</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>44924</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44924</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>44924</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44924</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44930</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>44931</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44939</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>44939</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>44949</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>44949</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>44952</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>44955</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>44959</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41045,7 +41045,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>44963</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>44965</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44965</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>44966</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>44970</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         <v>44971</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>44971</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>44971</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         <v>44973</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>44973</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>44978</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>44979</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41843,7 +41843,7 @@
         <v>44979</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44984</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>44984</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>44984</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>44988</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>44988</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>44991</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>44993</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>44993</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>44993</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>44993</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>44993</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>44994</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>44994</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44994</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45001</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45001</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>45001</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>45001</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>45001</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43023,7 +43023,7 @@
         <v>45001</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>45001</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>45006</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45007</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43308,7 +43308,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>45007</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>45019</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45027</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45028</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45028</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45028</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43764,7 +43764,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>45034</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43878,7 +43878,7 @@
         <v>45036</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43935,7 +43935,7 @@
         <v>45042</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45042</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45044</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45044</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45050</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45058</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45061</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45063</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44396,7 +44396,7 @@
         <v>45067</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>45070</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>45070</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45070</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>45070</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>45071</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>45071</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45071</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>45072</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>45072</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>45075</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>45075</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>45075</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45075</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45075</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45076</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45077</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45082</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45082</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45083</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45086</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>45089</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>45090</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45090</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45090</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45955,7 +45955,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46069,7 +46069,7 @@
         <v>45091</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46126,7 +46126,7 @@
         <v>45091</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
         <v>45092</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46240,7 +46240,7 @@
         <v>45093</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>45093</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45096</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>45096</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45097</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45097</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>45097</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>45097</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45099</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45103</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45103</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45104</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47214,7 +47214,7 @@
         <v>45104</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45104</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47333,7 +47333,7 @@
         <v>45104</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45104</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45104</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45104</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45107</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47618,7 +47618,7 @@
         <v>45110</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45110</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47737,7 +47737,7 @@
         <v>45110</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45113</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45113</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45114</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45114</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45114</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>45114</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45114</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48255,7 +48255,7 @@
         <v>45118</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45118</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48369,7 +48369,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48426,7 +48426,7 @@
         <v>45118</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48540,7 +48540,7 @@
         <v>45118</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48597,7 +48597,7 @@
         <v>45118</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45119</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48711,7 +48711,7 @@
         <v>45119</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>45119</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>45125</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>45125</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45125</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>45125</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45126</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45126</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>45131</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45134</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>45141</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45145</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>45146</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49452,7 +49452,7 @@
         <v>45146</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>45148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>45148</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>45148</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45148</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49794,7 +49794,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49851,7 +49851,7 @@
         <v>45149</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49908,7 +49908,7 @@
         <v>45153</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49965,7 +49965,7 @@
         <v>45153</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50022,7 +50022,7 @@
         <v>45153</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>45153</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50136,7 +50136,7 @@
         <v>45153</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50193,7 +50193,7 @@
         <v>45154</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50250,7 +50250,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45156</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50421,7 +50421,7 @@
         <v>45159</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50478,7 +50478,7 @@
         <v>45161</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>45161</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45163</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50669,7 +50669,7 @@
         <v>45163</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>45165</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50783,7 +50783,7 @@
         <v>45166</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50840,7 +50840,7 @@
         <v>45167</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>45167</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         <v>45167</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51011,7 +51011,7 @@
         <v>45169</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45169</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45169</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45169</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45169</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45170</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45170</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45173</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51581,7 +51581,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51638,7 +51638,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51695,7 +51695,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51752,7 +51752,7 @@
         <v>45173</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45174</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51866,7 +51866,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51980,7 +51980,7 @@
         <v>45180</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45180</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45180</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45180</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>45181</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52265,7 +52265,7 @@
         <v>45182</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52322,7 +52322,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>45182</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52436,7 +52436,7 @@
         <v>45183</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>45188</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45189</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45189</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45190</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45190</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45194</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45195</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53006,7 +53006,7 @@
         <v>45198</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53063,7 +53063,7 @@
         <v>45198</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45202</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45202</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45202</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45202</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45205</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45205</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45205</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45205</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45205</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45208</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45208</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45209</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45209</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45209</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>45212</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45212</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45212</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45212</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45215</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45218</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45218</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45218</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45219</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45219</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45219</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45219</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45222</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45223</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45223</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45226</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45229</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45229</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45229</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45229</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45229</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45229</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55229,7 +55229,7 @@
         <v>45230</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>45230</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>45232</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>45232</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55457,7 +55457,7 @@
         <v>45233</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55514,7 +55514,7 @@
         <v>45233</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55571,7 +55571,7 @@
         <v>45233</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55628,7 +55628,7 @@
         <v>45233</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55685,7 +55685,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>45233</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>45233</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55856,7 +55856,7 @@
         <v>45233</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55913,7 +55913,7 @@
         <v>45233</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55970,7 +55970,7 @@
         <v>45236</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56027,7 +56027,7 @@
         <v>45237</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56084,7 +56084,7 @@
         <v>45239</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56146,7 +56146,7 @@
         <v>45243</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56203,7 +56203,7 @@
         <v>45243</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56260,7 +56260,7 @@
         <v>45244</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56317,7 +56317,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56374,7 +56374,7 @@
         <v>45246</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56431,7 +56431,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56545,7 +56545,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56602,7 +56602,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45246</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56716,7 +56716,7 @@
         <v>45246</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56773,7 +56773,7 @@
         <v>45247</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>45250</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56887,7 +56887,7 @@
         <v>45250</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45252</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57001,7 +57001,7 @@
         <v>45252</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45252</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45254</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57229,7 +57229,7 @@
         <v>45254</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>45254</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57343,7 +57343,7 @@
         <v>45254</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>45260</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45260</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>45261</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57628,7 +57628,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57705,7 +57705,7 @@
         <v>45264</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57762,7 +57762,7 @@
         <v>45266</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45267</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57876,7 +57876,7 @@
         <v>45268</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57933,7 +57933,7 @@
         <v>45268</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57990,7 +57990,7 @@
         <v>45268</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58047,7 +58047,7 @@
         <v>45271</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>45271</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58161,7 +58161,7 @@
         <v>45272</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58218,7 +58218,7 @@
         <v>45272</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58275,7 +58275,7 @@
         <v>45272</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45273</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58503,7 +58503,7 @@
         <v>45274</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45281</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58617,7 +58617,7 @@
         <v>45286</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58674,7 +58674,7 @@
         <v>45301</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58731,7 +58731,7 @@
         <v>45302</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58788,7 +58788,7 @@
         <v>45306</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58845,7 +58845,7 @@
         <v>45306</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>45307</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58964,7 +58964,7 @@
         <v>45307</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59021,7 +59021,7 @@
         <v>45307</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59078,7 +59078,7 @@
         <v>45308</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>45308</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59192,7 +59192,7 @@
         <v>45313</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59249,7 +59249,7 @@
         <v>45313</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59306,7 +59306,7 @@
         <v>45313</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59363,7 +59363,7 @@
         <v>45313</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59420,7 +59420,7 @@
         <v>45314</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59477,7 +59477,7 @@
         <v>45314</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59534,7 +59534,7 @@
         <v>45314</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59591,7 +59591,7 @@
         <v>45314</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59648,7 +59648,7 @@
         <v>45314</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59705,7 +59705,7 @@
         <v>45319</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59762,7 +59762,7 @@
         <v>45323</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59819,7 +59819,7 @@
         <v>45323</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59876,7 +59876,7 @@
         <v>45323</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59933,7 +59933,7 @@
         <v>45324</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59990,7 +59990,7 @@
         <v>45324</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60047,7 +60047,7 @@
         <v>45327</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60104,7 +60104,7 @@
         <v>45327</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60161,7 +60161,7 @@
         <v>45329</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60218,7 +60218,7 @@
         <v>45329</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60275,7 +60275,7 @@
         <v>45331</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60332,7 +60332,7 @@
         <v>45331</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60389,7 +60389,7 @@
         <v>45331</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60446,7 +60446,7 @@
         <v>45334</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60503,7 +60503,7 @@
         <v>45335</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>45335</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60622,7 +60622,7 @@
         <v>45335</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60684,7 +60684,7 @@
         <v>45335</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60746,7 +60746,7 @@
         <v>45335</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60803,7 +60803,7 @@
         <v>45335</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60865,7 +60865,7 @@
         <v>45335</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60927,7 +60927,7 @@
         <v>45336</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60984,7 +60984,7 @@
         <v>45336</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61041,7 +61041,7 @@
         <v>45336</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61098,7 +61098,7 @@
         <v>45336</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61155,7 +61155,7 @@
         <v>45337</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61212,7 +61212,7 @@
         <v>45337</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45338</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61326,7 +61326,7 @@
         <v>45338</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61383,7 +61383,7 @@
         <v>45341</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61440,7 +61440,7 @@
         <v>45341</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>45341</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61554,7 +61554,7 @@
         <v>45344</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61611,7 +61611,7 @@
         <v>45345</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61668,7 +61668,7 @@
         <v>45349</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61725,7 +61725,7 @@
         <v>45349</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61782,7 +61782,7 @@
         <v>45351</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61839,7 +61839,7 @@
         <v>45356</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61896,7 +61896,7 @@
         <v>45356</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61953,7 +61953,7 @@
         <v>45362</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -62010,7 +62010,7 @@
         <v>45363</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -62067,7 +62067,7 @@
         <v>45363</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -62124,7 +62124,7 @@
         <v>45363</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62181,7 +62181,7 @@
         <v>45363</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62258,7 +62258,7 @@
         <v>45363</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62315,7 +62315,7 @@
         <v>45363</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62372,7 +62372,7 @@
         <v>45364</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>45364</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62486,7 +62486,7 @@
         <v>45364</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45370</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>45372</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62657,7 +62657,7 @@
         <v>45378</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62714,7 +62714,7 @@
         <v>45378</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62771,7 +62771,7 @@
         <v>45378</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62828,7 +62828,7 @@
         <v>45384</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62885,7 +62885,7 @@
         <v>45384</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62942,7 +62942,7 @@
         <v>45384</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62999,7 +62999,7 @@
         <v>45385</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -63061,7 +63061,7 @@
         <v>45385</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -63118,7 +63118,7 @@
         <v>45387</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -63175,7 +63175,7 @@
         <v>45387</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63232,7 +63232,7 @@
         <v>45387</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63289,7 +63289,7 @@
         <v>45387</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63346,7 +63346,7 @@
         <v>45387</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63403,7 +63403,7 @@
         <v>45391</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63460,7 +63460,7 @@
         <v>45398</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63517,7 +63517,7 @@
         <v>45400</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63574,7 +63574,7 @@
         <v>45400</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63631,7 +63631,7 @@
         <v>45400</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63688,7 +63688,7 @@
         <v>45401</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63745,7 +63745,7 @@
         <v>45401</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63802,7 +63802,7 @@
         <v>45402</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63864,7 +63864,7 @@
         <v>45404</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63921,7 +63921,7 @@
         <v>45406</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63978,7 +63978,7 @@
         <v>45407</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -64035,7 +64035,7 @@
         <v>45411</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45411</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45412</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>45412</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64263,7 +64263,7 @@
         <v>45414</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64320,7 +64320,7 @@
         <v>45418</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64377,7 +64377,7 @@
         <v>45420</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64434,7 +64434,7 @@
         <v>45429</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>45429</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64548,7 +64548,7 @@
         <v>45433</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64605,7 +64605,7 @@
         <v>45439</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64662,7 +64662,7 @@
         <v>45441</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64719,7 +64719,7 @@
         <v>45441</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64776,7 +64776,7 @@
         <v>45442</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64833,7 +64833,7 @@
         <v>45443</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64890,7 +64890,7 @@
         <v>45443</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64947,7 +64947,7 @@
         <v>45446</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -65004,7 +65004,7 @@
         <v>45453</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -65061,7 +65061,7 @@
         <v>45454</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>45454</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -65175,7 +65175,7 @@
         <v>45454</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65237,7 +65237,7 @@
         <v>45460</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>45460</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -65351,7 +65351,7 @@
         <v>45460</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -65408,7 +65408,7 @@
         <v>45462</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -65465,7 +65465,7 @@
         <v>45462</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -65522,7 +65522,7 @@
         <v>45463</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -65579,7 +65579,7 @@
         <v>45463</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -65636,7 +65636,7 @@
         <v>45470</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -65693,7 +65693,7 @@
         <v>45476</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -65750,7 +65750,7 @@
         <v>45478</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -65807,7 +65807,7 @@
         <v>45478</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -65857,14 +65857,14 @@
     <row r="1095" ht="15" customHeight="1">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>A 30026-2024</t>
+          <t>A 30029-2024</t>
         </is>
       </c>
       <c r="B1095" s="1" t="n">
         <v>45488</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -65877,7 +65877,7 @@
         </is>
       </c>
       <c r="G1095" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="H1095" t="n">
         <v>0</v>
@@ -65914,14 +65914,14 @@
     <row r="1096" ht="15" customHeight="1">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>A 30029-2024</t>
+          <t>A 30026-2024</t>
         </is>
       </c>
       <c r="B1096" s="1" t="n">
         <v>45488</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -65934,7 +65934,7 @@
         </is>
       </c>
       <c r="G1096" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="H1096" t="n">
         <v>0</v>
@@ -65978,7 +65978,7 @@
         <v>45489</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -66035,7 +66035,7 @@
         <v>45491</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -66092,7 +66092,7 @@
         <v>45492</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -66149,7 +66149,7 @@
         <v>45492</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -66206,7 +66206,7 @@
         <v>45503</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45385</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>44237</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>44245</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44785</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44439</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>44489</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>44454</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>44476</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>44979</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>44558</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>44958</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>43591</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>43643</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>43686</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>44057</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>44876</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>45324</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45343</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>43613</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>43640</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>44489</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>44575</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>44785</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>44827</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>44853</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45118</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>45254</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>43674</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>43719</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>43796</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44302</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>44369</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>44785</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44802</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>44896</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>44951</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>45105</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>45105</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>45125</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>43605</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>43614</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>43680</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>43717</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>43731</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>43734</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>43854</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>43927</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>43928</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>43999</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44053</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44069</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>44103</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>44152</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>44246</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44260</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44279</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44378</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>44466</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>44482</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>44487</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>44489</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>44517</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44575</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44726</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>44830</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44915</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>44928</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44931</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44949</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>44991</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>45007</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>45042</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>45063</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45069</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>45117</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>45119</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>45167</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>45243</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45275</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>45324</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45362</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>45475</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>43556</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>43558</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>43558</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>43559</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>43566</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>43567</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>43570</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>43578</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>43578</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>43578</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>43581</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>43581</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>43584</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>43585</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>43587</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>43591</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>43591</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43591</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43592</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43600</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43605</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43606</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43606</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43612</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43612</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43613</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43613</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43613</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43613</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43613</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43620</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43625</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43629</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43634</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43634</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43640</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43640</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43640</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43640</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>43643</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>43648</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>43656</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>43662</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>43668</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>43668</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>43668</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>43668</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>43675</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>43678</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>43679</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>43680</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>43680</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>43680</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>43680</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>43681</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>43682</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>43682</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>43683</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>43683</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>43683</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>43684</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>43689</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>43689</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>43691</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>43691</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>43691</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43691</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43691</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43691</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43691</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43692</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43693</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>43696</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>43698</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>43698</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>43698</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>43698</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>43699</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>43699</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>43702</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>43703</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>43704</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>43704</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>43705</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>43705</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>43705</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>43705</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>43706</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>43707</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>43710</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>43711</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>43712</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>43712</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>43713</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>43714</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>43717</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>43717</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>43717</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>43717</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>43718</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>43718</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>43718</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>43718</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>43719</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>43719</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>43720</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>43721</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>43721</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>43724</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>43726</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>43727</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>43727</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>43727</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>43728</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>43728</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>43732</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>43733</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>43746</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>43749</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>43755</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>43756</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>43756</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>43761</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>43763</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>43763</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>43763</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>43766</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>43769</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>43774</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>43776</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>43776</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>43777</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>43777</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>43777</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>43777</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>43780</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>43780</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>43782</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>43784</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>43784</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>43784</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43784</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>43787</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>43791</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>43796</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>43796</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>43803</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>43803</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>43803</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>43815</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>43815</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>43815</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>43815</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>43817</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
         <v>43829</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>43832</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>43832</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>43832</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>43832</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>43832</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>43832</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>43832</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>43832</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>43840</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>43844</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>43846</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>43846</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>43859</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>43865</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43865</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>43867</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>43867</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>43867</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>43871</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>43871</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>43872</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>43873</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>43873</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>43873</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>43875</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>43875</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>43880</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>43881</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>43886</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>43887</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>43887</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>43887</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>43894</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>43894</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>43899</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>43900</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>43907</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>43907</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>43909</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>43914</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>43915</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>43916</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>43916</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>43917</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>43929</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>43936</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>43941</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>43949</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>43950</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>43956</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>43963</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>43977</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>43983</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>43984</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>44007</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>44020</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>44032</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>44041</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
         <v>44041</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         <v>44047</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>44047</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>44047</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>44048</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>44053</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>44053</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>44053</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>44055</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>44055</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>44055</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>44055</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44060</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44060</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44061</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>44061</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44061</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44062</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>44062</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>44074</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>44074</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>44074</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>44075</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>44075</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>44077</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>44082</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>44082</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>44084</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>44089</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>44089</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44089</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44089</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44090</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44095</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>44095</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>44095</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>44098</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>44104</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>44104</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>44105</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>44105</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>44109</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>44110</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>44110</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44111</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>44112</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>44112</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>44119</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>44120</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>44126</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44130</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>44131</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>44136</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44138</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>44139</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>44140</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>44141</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>44144</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>44145</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>44145</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>44147</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>44151</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>44151</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>44151</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>44151</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>44151</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>44151</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44154</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44159</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44160</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44178</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44182</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>44182</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>44186</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44187</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44188</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>44192</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>44193</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>44193</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>44201</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>44209</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>44210</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>44210</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>44214</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>44214</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>44214</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>44215</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>44217</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>44218</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>44220</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>44229</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>44230</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>44230</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>44230</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>44230</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>44230</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>44230</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44236</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44236</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>44236</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>44236</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>44238</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>44241</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>44243</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>44243</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>44244</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>44264</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>44264</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44267</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44271</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>44271</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>44271</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>44271</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44273</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44273</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>44277</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27020,7 +27020,7 @@
         <v>44279</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>44280</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>44285</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>44287</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>44301</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>44302</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>44302</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>44312</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>44312</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>44320</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>44322</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>44326</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>44326</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>44327</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>44333</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>44336</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         <v>44341</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>44341</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28046,7 +28046,7 @@
         <v>44342</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>44345</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>44348</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>44351</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>44351</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>44356</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44356</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>44357</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44357</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44363</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44364</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44369</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44371</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44375</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44378</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44379</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44382</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44384</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44385</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44385</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44385</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44386</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44386</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44405</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44407</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44407</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44413</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44417</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44418</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44419</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44421</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44432</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44433</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44434</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>44435</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44437</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>44438</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>44438</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>44446</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44447</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>44448</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>44448</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>44448</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>44454</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>44454</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>44455</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>44455</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>44456</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>44457</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>44460</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>44461</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>44461</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>44462</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>44467</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>44474</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>44475</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>44475</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>44476</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>44477</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>44477</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>44477</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>44480</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31590,7 +31590,7 @@
         <v>44482</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>44482</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44482</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44482</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44482</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>44482</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44484</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>44489</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>44489</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>44496</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44497</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>44497</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>44497</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44497</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44498</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44498</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44502</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>44502</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>44502</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>44505</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44511</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>44517</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         <v>44522</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>44522</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>44525</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33015,7 +33015,7 @@
         <v>44529</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>44531</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44539</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44539</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44543</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44544</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44544</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44544</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44552</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44564</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44564</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44566</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44574</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44581</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44581</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>44581</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44586</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44587</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>44588</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44595</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44595</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44602</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44615</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>44617</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44617</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44618</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44620</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44620</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44623</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44623</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44625</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44629</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44629</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44636</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44643</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44645</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>44655</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44656</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44659</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>44679</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44679</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44683</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44684</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44686</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44690</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44712</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44712</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44722</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>44732</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44732</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44733</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44740</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44740</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44782</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44782</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44784</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44784</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44790</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44796</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44796</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44804</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36554,7 +36554,7 @@
         <v>44810</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>44810</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>44810</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>44816</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44818</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44818</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44819</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44820</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44823</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44823</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44823</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44823</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>44823</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37419,7 +37419,7 @@
         <v>44823</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>44824</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>44830</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37590,7 +37590,7 @@
         <v>44831</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>44841</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>44845</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>44846</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>44846</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>44846</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>44847</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>44848</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>44851</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>44852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>44852</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38242,7 +38242,7 @@
         <v>44855</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>44855</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>44855</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44858</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>44858</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>44858</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>44858</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>44858</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>44858</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>44858</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>44861</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38874,7 +38874,7 @@
         <v>44861</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>44862</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>44864</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39045,7 +39045,7 @@
         <v>44865</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>44865</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>44872</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>44874</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>44882</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>44895</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>44895</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44895</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>44895</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39558,7 +39558,7 @@
         <v>44895</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>44901</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>44904</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>44909</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>44909</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>44914</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>44914</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         <v>44914</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>44914</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>44914</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40128,7 +40128,7 @@
         <v>44915</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>44915</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40242,7 +40242,7 @@
         <v>44915</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>44924</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44924</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>44924</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44924</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44930</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>44931</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44939</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>44939</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>44949</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>44949</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>44952</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>44955</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>44959</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41045,7 +41045,7 @@
         <v>44963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>44963</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>44963</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>44965</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44965</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>44966</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>44970</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         <v>44971</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>44971</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41558,7 +41558,7 @@
         <v>44971</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         <v>44973</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>44973</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>44978</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>44979</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41843,7 +41843,7 @@
         <v>44979</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44984</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>44984</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>44984</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>44988</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>44988</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>44991</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>44993</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>44993</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>44993</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>44993</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>44993</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>44994</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>44994</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>44994</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45001</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45001</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>45001</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>45001</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>45001</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43023,7 +43023,7 @@
         <v>45001</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>45001</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>45006</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45007</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>45007</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43308,7 +43308,7 @@
         <v>45007</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>45007</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>45019</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>45027</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45027</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45028</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45028</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45028</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43764,7 +43764,7 @@
         <v>45034</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>45034</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43878,7 +43878,7 @@
         <v>45036</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43935,7 +43935,7 @@
         <v>45042</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45042</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>45044</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45044</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>45050</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45058</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>45061</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45063</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44396,7 +44396,7 @@
         <v>45067</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>45070</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>45070</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45070</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>45070</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>45071</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>45071</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45071</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>45072</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44924,7 +44924,7 @@
         <v>45072</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>45075</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>45075</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45095,7 +45095,7 @@
         <v>45075</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45075</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>45075</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45076</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45077</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45082</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45082</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45083</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45086</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45086</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>45089</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>45090</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>45090</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45090</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45898,7 +45898,7 @@
         <v>45090</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45955,7 +45955,7 @@
         <v>45091</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46012,7 +46012,7 @@
         <v>45091</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46069,7 +46069,7 @@
         <v>45091</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46126,7 +46126,7 @@
         <v>45091</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
         <v>45092</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46240,7 +46240,7 @@
         <v>45093</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>45093</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45096</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45096</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>45096</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45097</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45097</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>45097</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>45097</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45099</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46867,7 +46867,7 @@
         <v>45099</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45099</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46981,7 +46981,7 @@
         <v>45099</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47038,7 +47038,7 @@
         <v>45103</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45103</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45104</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47214,7 +47214,7 @@
         <v>45104</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45104</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47333,7 +47333,7 @@
         <v>45104</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45104</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45104</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>45104</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45107</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47618,7 +47618,7 @@
         <v>45110</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45110</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47737,7 +47737,7 @@
         <v>45110</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45113</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47856,7 +47856,7 @@
         <v>45113</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47913,7 +47913,7 @@
         <v>45114</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45114</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48027,7 +48027,7 @@
         <v>45114</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>45114</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45114</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45114</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48255,7 +48255,7 @@
         <v>45118</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45118</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48369,7 +48369,7 @@
         <v>45118</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48426,7 +48426,7 @@
         <v>45118</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>45118</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48540,7 +48540,7 @@
         <v>45118</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48597,7 +48597,7 @@
         <v>45118</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45119</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48711,7 +48711,7 @@
         <v>45119</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>45119</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>45125</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>45125</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45125</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>45125</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45126</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45126</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>45131</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49224,7 +49224,7 @@
         <v>45134</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>45141</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45145</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>45146</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49452,7 +49452,7 @@
         <v>45146</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>45148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>45148</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>45148</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45148</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>45149</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49794,7 +49794,7 @@
         <v>45149</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49851,7 +49851,7 @@
         <v>45149</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49908,7 +49908,7 @@
         <v>45153</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49965,7 +49965,7 @@
         <v>45153</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -50022,7 +50022,7 @@
         <v>45153</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>45153</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -50136,7 +50136,7 @@
         <v>45153</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -50193,7 +50193,7 @@
         <v>45154</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -50250,7 +50250,7 @@
         <v>45156</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45156</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45159</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50421,7 +50421,7 @@
         <v>45159</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50478,7 +50478,7 @@
         <v>45161</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>45161</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45163</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50669,7 +50669,7 @@
         <v>45163</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>45165</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50783,7 +50783,7 @@
         <v>45166</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50840,7 +50840,7 @@
         <v>45167</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>45167</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         <v>45167</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -51011,7 +51011,7 @@
         <v>45169</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>45169</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45169</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45169</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45169</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>45170</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45170</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45173</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51467,7 +51467,7 @@
         <v>45173</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51524,7 +51524,7 @@
         <v>45173</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51581,7 +51581,7 @@
         <v>45173</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51638,7 +51638,7 @@
         <v>45173</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51695,7 +51695,7 @@
         <v>45173</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51752,7 +51752,7 @@
         <v>45173</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45174</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51866,7 +51866,7 @@
         <v>45175</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45175</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51980,7 +51980,7 @@
         <v>45180</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45180</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -52094,7 +52094,7 @@
         <v>45180</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45180</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>45181</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -52265,7 +52265,7 @@
         <v>45182</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52322,7 +52322,7 @@
         <v>45182</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>45182</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52436,7 +52436,7 @@
         <v>45183</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>45188</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52550,7 +52550,7 @@
         <v>45189</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52607,7 +52607,7 @@
         <v>45189</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>45190</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45190</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>45190</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45194</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45195</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52949,7 +52949,7 @@
         <v>45195</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -53006,7 +53006,7 @@
         <v>45198</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -53063,7 +53063,7 @@
         <v>45198</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>45198</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>45202</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -53234,7 +53234,7 @@
         <v>45202</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>45202</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>45202</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45205</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>45205</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53519,7 +53519,7 @@
         <v>45205</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>45205</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45205</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45208</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45208</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45209</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53861,7 +53861,7 @@
         <v>45209</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53918,7 +53918,7 @@
         <v>45209</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53975,7 +53975,7 @@
         <v>45212</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -54032,7 +54032,7 @@
         <v>45212</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>45212</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45212</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45215</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45218</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45218</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45218</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45219</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45219</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45219</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45219</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>45222</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45223</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45223</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>45226</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45229</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45229</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45229</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45229</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45229</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>45229</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -55229,7 +55229,7 @@
         <v>45230</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>45230</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>45232</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>45232</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55457,7 +55457,7 @@
         <v>45233</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55514,7 +55514,7 @@
         <v>45233</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55571,7 +55571,7 @@
         <v>45233</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55628,7 +55628,7 @@
         <v>45233</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55685,7 +55685,7 @@
         <v>45233</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>45233</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>45233</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55856,7 +55856,7 @@
         <v>45233</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55913,7 +55913,7 @@
         <v>45233</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55970,7 +55970,7 @@
         <v>45236</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -56027,7 +56027,7 @@
         <v>45237</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -56084,7 +56084,7 @@
         <v>45239</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -56146,7 +56146,7 @@
         <v>45243</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -56203,7 +56203,7 @@
         <v>45243</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -56260,7 +56260,7 @@
         <v>45244</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56317,7 +56317,7 @@
         <v>45246</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56374,7 +56374,7 @@
         <v>45246</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56431,7 +56431,7 @@
         <v>45246</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>45246</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56545,7 +56545,7 @@
         <v>45246</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56602,7 +56602,7 @@
         <v>45246</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45246</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56716,7 +56716,7 @@
         <v>45246</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56773,7 +56773,7 @@
         <v>45247</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>45250</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56887,7 +56887,7 @@
         <v>45250</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45252</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -57001,7 +57001,7 @@
         <v>45252</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45252</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -57115,7 +57115,7 @@
         <v>45253</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -57172,7 +57172,7 @@
         <v>45254</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -57229,7 +57229,7 @@
         <v>45254</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>45254</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57343,7 +57343,7 @@
         <v>45254</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57400,7 +57400,7 @@
         <v>45260</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>45260</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45260</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>45261</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57628,7 +57628,7 @@
         <v>45264</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57705,7 +57705,7 @@
         <v>45264</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57762,7 +57762,7 @@
         <v>45266</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45267</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57876,7 +57876,7 @@
         <v>45268</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57933,7 +57933,7 @@
         <v>45268</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57990,7 +57990,7 @@
         <v>45268</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -58047,7 +58047,7 @@
         <v>45271</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>45271</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -58161,7 +58161,7 @@
         <v>45272</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -58218,7 +58218,7 @@
         <v>45272</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -58275,7 +58275,7 @@
         <v>45272</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>45273</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>45273</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58446,7 +58446,7 @@
         <v>45273</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58503,7 +58503,7 @@
         <v>45274</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45281</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58617,7 +58617,7 @@
         <v>45286</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58674,7 +58674,7 @@
         <v>45301</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58731,7 +58731,7 @@
         <v>45302</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58788,7 +58788,7 @@
         <v>45306</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58845,7 +58845,7 @@
         <v>45306</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>45307</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58964,7 +58964,7 @@
         <v>45307</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -59021,7 +59021,7 @@
         <v>45307</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -59078,7 +59078,7 @@
         <v>45308</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>45308</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -59192,7 +59192,7 @@
         <v>45313</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -59249,7 +59249,7 @@
         <v>45313</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59306,7 +59306,7 @@
         <v>45313</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59363,7 +59363,7 @@
         <v>45313</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59420,7 +59420,7 @@
         <v>45314</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59477,7 +59477,7 @@
         <v>45314</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59534,7 +59534,7 @@
         <v>45314</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59591,7 +59591,7 @@
         <v>45314</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59648,7 +59648,7 @@
         <v>45314</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59705,7 +59705,7 @@
         <v>45319</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59762,7 +59762,7 @@
         <v>45323</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59819,7 +59819,7 @@
         <v>45323</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59876,7 +59876,7 @@
         <v>45323</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59933,7 +59933,7 @@
         <v>45324</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59990,7 +59990,7 @@
         <v>45324</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -60047,7 +60047,7 @@
         <v>45327</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -60104,7 +60104,7 @@
         <v>45327</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -60161,7 +60161,7 @@
         <v>45329</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -60218,7 +60218,7 @@
         <v>45329</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -60275,7 +60275,7 @@
         <v>45331</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60332,7 +60332,7 @@
         <v>45331</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60389,7 +60389,7 @@
         <v>45331</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60446,7 +60446,7 @@
         <v>45334</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60503,7 +60503,7 @@
         <v>45335</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>45335</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60622,7 +60622,7 @@
         <v>45335</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60684,7 +60684,7 @@
         <v>45335</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60746,7 +60746,7 @@
         <v>45335</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60803,7 +60803,7 @@
         <v>45335</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60865,7 +60865,7 @@
         <v>45335</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60927,7 +60927,7 @@
         <v>45336</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60984,7 +60984,7 @@
         <v>45336</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -61041,7 +61041,7 @@
         <v>45336</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -61098,7 +61098,7 @@
         <v>45336</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -61155,7 +61155,7 @@
         <v>45337</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -61212,7 +61212,7 @@
         <v>45337</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45338</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61326,7 +61326,7 @@
         <v>45338</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61383,7 +61383,7 @@
         <v>45341</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61440,7 +61440,7 @@
         <v>45341</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>45341</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61554,7 +61554,7 @@
         <v>45344</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61611,7 +61611,7 @@
         <v>45345</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61668,7 +61668,7 @@
         <v>45349</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61725,7 +61725,7 @@
         <v>45349</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61782,7 +61782,7 @@
         <v>45351</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61839,7 +61839,7 @@
         <v>45356</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61896,7 +61896,7 @@
         <v>45356</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61953,7 +61953,7 @@
         <v>45362</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -62010,7 +62010,7 @@
         <v>45363</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -62067,7 +62067,7 @@
         <v>45363</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -62124,7 +62124,7 @@
         <v>45363</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -62181,7 +62181,7 @@
         <v>45363</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -62258,7 +62258,7 @@
         <v>45363</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -62315,7 +62315,7 @@
         <v>45363</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62372,7 +62372,7 @@
         <v>45364</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>45364</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62486,7 +62486,7 @@
         <v>45364</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45370</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>45372</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62657,7 +62657,7 @@
         <v>45378</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62714,7 +62714,7 @@
         <v>45378</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62771,7 +62771,7 @@
         <v>45378</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62828,7 +62828,7 @@
         <v>45384</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62885,7 +62885,7 @@
         <v>45384</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62942,7 +62942,7 @@
         <v>45384</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62999,7 +62999,7 @@
         <v>45385</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -63061,7 +63061,7 @@
         <v>45385</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -63118,7 +63118,7 @@
         <v>45387</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -63175,7 +63175,7 @@
         <v>45387</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -63232,7 +63232,7 @@
         <v>45387</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -63289,7 +63289,7 @@
         <v>45387</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63346,7 +63346,7 @@
         <v>45387</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63403,7 +63403,7 @@
         <v>45391</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63460,7 +63460,7 @@
         <v>45398</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63517,7 +63517,7 @@
         <v>45400</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63574,7 +63574,7 @@
         <v>45400</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63631,7 +63631,7 @@
         <v>45400</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63688,7 +63688,7 @@
         <v>45401</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63745,7 +63745,7 @@
         <v>45401</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63802,7 +63802,7 @@
         <v>45402</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63864,7 +63864,7 @@
         <v>45404</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63921,7 +63921,7 @@
         <v>45406</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63978,7 +63978,7 @@
         <v>45407</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -64035,7 +64035,7 @@
         <v>45411</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45411</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45412</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>45412</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -64263,7 +64263,7 @@
         <v>45414</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -64320,7 +64320,7 @@
         <v>45418</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64377,7 +64377,7 @@
         <v>45420</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64434,7 +64434,7 @@
         <v>45429</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>45429</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64548,7 +64548,7 @@
         <v>45433</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64605,7 +64605,7 @@
         <v>45439</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64662,7 +64662,7 @@
         <v>45441</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64719,7 +64719,7 @@
         <v>45441</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64776,7 +64776,7 @@
         <v>45442</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64833,7 +64833,7 @@
         <v>45443</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64890,7 +64890,7 @@
         <v>45443</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64947,7 +64947,7 @@
         <v>45446</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -65004,7 +65004,7 @@
         <v>45453</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -65061,7 +65061,7 @@
         <v>45454</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -65118,7 +65118,7 @@
         <v>45454</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -65175,7 +65175,7 @@
         <v>45454</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -65237,7 +65237,7 @@
         <v>45460</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -65294,7 +65294,7 @@
         <v>45460</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -65351,7 +65351,7 @@
         <v>45460</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -65408,7 +65408,7 @@
         <v>45462</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -65465,7 +65465,7 @@
         <v>45462</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -65522,7 +65522,7 @@
         <v>45463</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -65579,7 +65579,7 @@
         <v>45463</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -65636,7 +65636,7 @@
         <v>45470</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -65693,7 +65693,7 @@
         <v>45476</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -65750,7 +65750,7 @@
         <v>45478</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -65807,7 +65807,7 @@
         <v>45478</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -65864,7 +65864,7 @@
         <v>45488</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -65921,7 +65921,7 @@
         <v>45488</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -65978,7 +65978,7 @@
         <v>45489</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -66035,7 +66035,7 @@
         <v>45491</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -66085,14 +66085,14 @@
     <row r="1099" ht="15" customHeight="1">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>A 30504-2024</t>
+          <t>A 30507-2024</t>
         </is>
       </c>
       <c r="B1099" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -66105,7 +66105,7 @@
         </is>
       </c>
       <c r="G1099" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="H1099" t="n">
         <v>0</v>
@@ -66142,14 +66142,14 @@
     <row r="1100" ht="15" customHeight="1">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>A 30507-2024</t>
+          <t>A 30504-2024</t>
         </is>
       </c>
       <c r="B1100" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -66162,7 +66162,7 @@
         </is>
       </c>
       <c r="G1100" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="H1100" t="n">
         <v>0</v>
@@ -66206,7 +66206,7 @@
         <v>45503</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45510</v>
+        <v>45511</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>

--- a/Översikt KALMAR.xlsx
+++ b/Översikt KALMAR.xlsx
@@ -567,7 +567,7 @@
         <v>44237</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>44245</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>44785</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>44439</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>44489</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>44979</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44476</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>45664.60489583333</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>45842.47034722222</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>44454</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>45324</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45561</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>44876</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44057</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>44951</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>44103</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>44785</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>44489</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>45254</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>45791.4415625</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>45118</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>44827</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>44575</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>44853</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>44802</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45044</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>45105</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>45114</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>45575.39890046296</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>45703.67907407408</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>44785</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>44302.41612268519</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45832.47028935186</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>45874.5900462963</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>45874.58605324074</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>44951</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>44069</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44378.55797453703</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44489</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>44279</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>44991.50229166666</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44784</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>45007</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>44517.4756712963</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>45243</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>45748.43087962963</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>45719.50027777778</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>44466</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>44482</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>45475</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>45544.57532407407</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45775.89171296296</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>44915</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>45117</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>45275</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>44740</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>45799.45077546296</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>45167</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>45574.59858796297</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>45684</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>44246</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>45856.41157407407</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>45868.60506944444</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>44575.43100694445</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44260</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>45007</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>44931</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>44230</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44230</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>44089</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>44643</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44421</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44629</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44482.49607638889</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>44823</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>44089</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44215</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44192</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>44264</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44497.4675462963</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>44285</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>44460.55954861111</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44210</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44505.47354166667</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>44327</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44209</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44475</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44273</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>44852</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44684</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44312</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44435</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>44456</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>44457</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>44539.35644675926</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44498</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>44498</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>44407.35048611111</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44489</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44382</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>44062</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>44525.32100694445</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>44823</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>44790</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44273.86541666667</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>44151.51568287037</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>44531</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>44053</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>44517.67465277778</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>44364.74199074074</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>44055</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>44872.77071759259</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>44602</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>44623.42868055555</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44417</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>44151</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>44858.57224537037</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>44419</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>44084</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44077</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>44264</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44214</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>44522</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44151</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>44823.44712962963</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>44111</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>44098</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44818</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>44858.5893287037</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>44858.68984953704</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44852.45520833333</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44858.69229166667</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>44243.63636574074</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>44615</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>44432</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>44302</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>44271.41609953704</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>44230</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>44230</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>44586</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>44287</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>44082</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44348.69079861111</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44447</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>44267</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>44502</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>44454</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>44090</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>44241</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>44095</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>44357</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>44552.58133101852</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>44482</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>44377.95908564814</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>44193</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>44301.35189814815</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>44178</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>44244</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>44574</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>44326.60537037037</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>44855.31458333333</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>44784</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>44120</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>44858.57855324074</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>44620</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>44858.58140046296</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>44351</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>44110</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>44098</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>44082</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         <v>44433.50366898148</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>44341.4290625</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>44302</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
         <v>44369</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>44138</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>44061</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>44061</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12851,7 +12851,7 @@
         <v>44437.35085648148</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>44386</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>44732</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>44075</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>44810</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44454</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>44448</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>44385</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>44238</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>44062</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>44151</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44461.4503587963</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44074</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>44326.34189814814</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>44625</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44461.44216435185</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>44654.98487268519</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>44214</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>44312.38436342592</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>44074</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>44147</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>44089</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>44210</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>44112</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>44385</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>44455.55739583333</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>44214</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>44230</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>44218</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>44139</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>44074</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>44511</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45205.48995370371</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>45044</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>45492.44469907408</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>45190.33980324074</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45090</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>44529</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>45341.6575</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45341.65902777778</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>45156</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45239</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>45771</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>45324.24875</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>45688.49143518518</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44993.63946759259</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44629</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>44955.57755787037</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>45267.64923611111</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>44581.86262731482</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
         <v>45069</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>45716.26175925926</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>45236.51583333333</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>45215.52277777778</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>45334.4872800926</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>45625</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>45212</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>45764.43362268519</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>45684</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44984</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>45688.48016203703</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>45180.38313657408</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45564.47452546296</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>44782.6562037037</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45540.46302083333</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>45209.56659722222</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>45209.57653935185</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>45091</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>45411.45290509259</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>45567</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>44131</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16908,7 +16908,7 @@
         <v>44502</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>44566</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>45097</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>45233.45891203704</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45067</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>44846</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45755.44684027778</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>44336</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>44152</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44939.49839120371</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>45246</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>44882.86710648148</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>44407.34855324074</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>44236</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>45243</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>44418.68163194445</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         <v>44438</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>44846.5583449074</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>45646</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45264</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>45378.46670138889</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>44053</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>44895.64876157408</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>45063</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>44154</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45250.63819444444</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45092.66958333334</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>44182</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44914.32637731481</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>45099.64581018518</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>44095</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>45628.6009837963</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>45706.35223379629</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45034.48248842593</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
         <v>45173.65185185185</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>45268.50543981481</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18985,7 +18985,7 @@
         <v>45174.29445601852</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>44963</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>45387.4628125</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>45387.46427083333</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>44914.51458333333</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>45083</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45097</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45219.37208333334</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45628.58701388889</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45272</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45097</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45113</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>45104.61077546296</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>45104.61489583334</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>45104</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>45173.50910879629</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>44971</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>44924</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45306</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>45363.41396990741</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>45096.42900462963</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45118</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45141</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45086</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45202</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45338</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>44405</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>44855</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>45741.65971064815</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
         <v>45735.29974537037</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>45254.37960648148</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>44979</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>45175</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45387.46362268519</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45387.46494212963</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45099.63752314815</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>45163</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>44477.44094907407</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45476.32041666667</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45764</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         <v>45188.38238425926</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>45181.53854166667</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>44075</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>44544.66945601852</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45439.49431712963</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45273.86098379629</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>45246.60998842592</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>45246.61422453704</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>44895.65763888889</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         <v>45246</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>44564.34321759259</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45551.45412037037</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>45558.55011574074</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45775.89869212963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>45727.44655092592</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44522</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45443.49804398148</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>44988.67706018518</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45758</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>45782.56037037037</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45782.59019675926</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45779.64450231481</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>44862</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>44144</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>45782.59994212963</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>45086.58806712963</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>45544.57149305556</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45783.42328703704</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45104</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>45575.41082175926</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>45566.42055555555</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>45664.58763888889</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>45153</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>44991.5237037037</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>45363.44701388889</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>45050</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>44909</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>45785.59967592593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>44924</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>45786.35510416667</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>45664.40896990741</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>44914.45517361111</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>45260</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>44413</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45713.33792824074</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>45756.33833333333</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>45741.64989583333</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>45548.55480324074</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>45551.46702546296</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>45785.36744212963</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>45785.73490740741</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>45076</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24319,7 +24319,7 @@
         <v>45454.56966435185</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>45400.36533564814</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>44595</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>44595</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>45730.39450231481</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>45028</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>44502</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>45755.82037037037</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45